--- a/deliverables/deliverables-20260120-0030/Drill_1_CCGT.xlsx
+++ b/deliverables/deliverables-20260120-0030/Drill_1_CCGT.xlsx
@@ -3258,6 +3258,63 @@
         <v/>
       </c>
     </row>
+    <row r="93">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>Scheduled DS (for DSRA)</t>
+        </is>
+      </c>
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>Based on straight-line amort, no sweep</t>
+        </is>
+      </c>
+      <c r="E93" s="18">
+        <f>MAX(0,$D$55-(1-1)*$D$57)*$D$40+$D$57</f>
+        <v/>
+      </c>
+      <c r="F93" s="18">
+        <f>MAX(0,$D$55-(2-1)*$D$57)*$D$40+$D$57</f>
+        <v/>
+      </c>
+      <c r="G93" s="18">
+        <f>MAX(0,$D$55-(3-1)*$D$57)*$D$40+$D$57</f>
+        <v/>
+      </c>
+      <c r="H93" s="18">
+        <f>MAX(0,$D$55-(4-1)*$D$57)*$D$40+$D$57</f>
+        <v/>
+      </c>
+      <c r="I93" s="18">
+        <f>MAX(0,$D$55-(5-1)*$D$57)*$D$40+$D$57</f>
+        <v/>
+      </c>
+      <c r="J93" s="18">
+        <f>MAX(0,$D$55-(6-1)*$D$57)*$D$40+$D$57</f>
+        <v/>
+      </c>
+      <c r="K93" s="18">
+        <f>MAX(0,$D$55-(7-1)*$D$57)*$D$40+$D$57</f>
+        <v/>
+      </c>
+      <c r="L93" s="18">
+        <f>MAX(0,$D$55-(8-1)*$D$57)*$D$40+$D$57</f>
+        <v/>
+      </c>
+      <c r="M93" s="18">
+        <f>MAX(0,$D$55-(9-1)*$D$57)*$D$40+$D$57</f>
+        <v/>
+      </c>
+      <c r="N93" s="18">
+        <f>MAX(0,$D$55-(10-1)*$D$57)*$D$40+$D$57</f>
+        <v/>
+      </c>
+    </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
@@ -3291,47 +3348,47 @@
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>Next Yr DS × DSRA Months / 12</t>
+          <t>Next Yr Scheduled DS × DSRA Months / 12</t>
         </is>
       </c>
       <c r="D96" s="18">
-        <f>E87*$D$42/12</f>
+        <f>E93*$D$42/12</f>
         <v/>
       </c>
       <c r="E96" s="18">
-        <f>F87*$D$42/12</f>
+        <f>F93*$D$42/12</f>
         <v/>
       </c>
       <c r="F96" s="18">
-        <f>G87*$D$42/12</f>
+        <f>G93*$D$42/12</f>
         <v/>
       </c>
       <c r="G96" s="18">
-        <f>H87*$D$42/12</f>
+        <f>H93*$D$42/12</f>
         <v/>
       </c>
       <c r="H96" s="18">
-        <f>I87*$D$42/12</f>
+        <f>I93*$D$42/12</f>
         <v/>
       </c>
       <c r="I96" s="18">
-        <f>J87*$D$42/12</f>
+        <f>J93*$D$42/12</f>
         <v/>
       </c>
       <c r="J96" s="18">
-        <f>K87*$D$42/12</f>
+        <f>K93*$D$42/12</f>
         <v/>
       </c>
       <c r="K96" s="18">
-        <f>L87*$D$42/12</f>
+        <f>L93*$D$42/12</f>
         <v/>
       </c>
       <c r="L96" s="18">
-        <f>M87*$D$42/12</f>
+        <f>M93*$D$42/12</f>
         <v/>
       </c>
       <c r="M96" s="18">
-        <f>N87*$D$42/12</f>
+        <f>N93*$D$42/12</f>
         <v/>
       </c>
       <c r="N96" s="18">

--- a/deliverables/deliverables-20260120-0030/Drill_1_CCGT.xlsx
+++ b/deliverables/deliverables-20260120-0030/Drill_1_CCGT.xlsx
@@ -2278,43 +2278,43 @@
         </is>
       </c>
       <c r="E69" s="18">
-        <f>$D$54*$D$24*E63/1000000000</f>
+        <f>$D$54*$D$24*E63/1E9</f>
         <v/>
       </c>
       <c r="F69" s="18">
-        <f>$D$54*$D$24*F63/1000000000</f>
+        <f>$D$54*$D$24*F63/1E9</f>
         <v/>
       </c>
       <c r="G69" s="18">
-        <f>$D$54*$D$24*G63/1000000000</f>
+        <f>$D$54*$D$24*G63/1E9</f>
         <v/>
       </c>
       <c r="H69" s="18">
-        <f>$D$54*$D$24*H63/1000000000</f>
+        <f>$D$54*$D$24*H63/1E9</f>
         <v/>
       </c>
       <c r="I69" s="18">
-        <f>$D$54*$D$24*I63/1000000000</f>
+        <f>$D$54*$D$24*I63/1E9</f>
         <v/>
       </c>
       <c r="J69" s="18">
-        <f>$D$54*$D$24*J63/1000000000</f>
+        <f>$D$54*$D$24*J63/1E9</f>
         <v/>
       </c>
       <c r="K69" s="18">
-        <f>$D$54*$D$24*K63/1000000000</f>
+        <f>$D$54*$D$24*K63/1E9</f>
         <v/>
       </c>
       <c r="L69" s="18">
-        <f>$D$54*$D$24*L63/1000000000</f>
+        <f>$D$54*$D$24*L63/1E9</f>
         <v/>
       </c>
       <c r="M69" s="18">
-        <f>$D$54*$D$24*M63/1000000000</f>
+        <f>$D$54*$D$24*M63/1E9</f>
         <v/>
       </c>
       <c r="N69" s="18">
-        <f>$D$54*$D$24*N63/1000000000</f>
+        <f>$D$54*$D$24*N63/1E9</f>
         <v/>
       </c>
     </row>

--- a/deliverables/deliverables-20260120-0030/Drill_1_CCGT.xlsx
+++ b/deliverables/deliverables-20260120-0030/Drill_1_CCGT.xlsx
@@ -232,6 +232,96 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Lotus Infrastructure</author>
+  </authors>
+  <commentList>
+    <comment ref="C10" authorId="0" shapeId="0">
+      <text>
+        <t>Enterprise Value = Equity + Debt. Represents total asset value regardless of financing structure. Key input for returns analysis.</t>
+      </text>
+    </comment>
+    <comment ref="C11" authorId="0" shapeId="0">
+      <text>
+        <t>Maximum output rating. Used to calculate generation and capacity revenue. Actual dispatch varies with economics.</t>
+      </text>
+    </comment>
+    <comment ref="C12" authorId="0" shapeId="0">
+      <text>
+        <t>Measures thermal efficiency. 7,000 Btu/kWh is efficient modern CCGT. Higher HR = less efficient = higher fuel cost per MWh.</t>
+      </text>
+    </comment>
+    <comment ref="C13" authorId="0" shapeId="0">
+      <text>
+        <t>Maximum output rating. Used to calculate generation and capacity revenue. Actual dispatch varies with economics.</t>
+      </text>
+    </comment>
+    <comment ref="C14" authorId="0" shapeId="0">
+      <text>
+        <t>Reduces UCAP (capacity revenue). Lenders/buyers discount nameplate by this factor. 5% is typical well-maintained plant.</t>
+      </text>
+    </comment>
+    <comment ref="C15" authorId="0" shapeId="0">
+      <text>
+        <t>Higher leverage amplifies equity returns but increases risk. Merchant assets: 40-50%. Contracted: 60-70%.</t>
+      </text>
+    </comment>
+    <comment ref="C16" authorId="0" shapeId="0">
+      <text>
+        <t>Mandatory prepayment from excess cash. Lenders require this for merchant assets to accelerate deleveraging.</t>
+      </text>
+    </comment>
+    <comment ref="C19" authorId="0" shapeId="0">
+      <text>
+        <t>Unforced Capacity — what you can sell into capacity market. FOR reflects forced outages outside your control.</t>
+      </text>
+    </comment>
+    <comment ref="C20" authorId="0" shapeId="0">
+      <text>
+        <t>Annual MWh output. CF reflects expected dispatch based on merit order. 8760 = hours/year. 55% CF = ~4800 hrs/yr.</t>
+      </text>
+    </comment>
+    <comment ref="C24" authorId="0" shapeId="0">
+      <text>
+        <t>Merchant energy revenue from selling MWh into wholesale market. Divide by 1E6 to convert $ to $mm.</t>
+      </text>
+    </comment>
+    <comment ref="C25" authorId="0" shapeId="0">
+      <text>
+        <t>Maximum output rating. Used to calculate generation and capacity revenue. Actual dispatch varies with economics.</t>
+      </text>
+    </comment>
+    <comment ref="C26" authorId="0" shapeId="0">
+      <text>
+        <t>Largest variable cost for thermal plants. HR measures efficiency. Divide by 1E9: MWh × Btu/kWh × $/mmBtu → $mm.</t>
+      </text>
+    </comment>
+    <comment ref="C29" authorId="0" shapeId="0">
+      <text>
+        <t>Mandatory prepayment from excess cash. Lenders require this for merchant assets to accelerate deleveraging.</t>
+      </text>
+    </comment>
+    <comment ref="C34" authorId="0" shapeId="0">
+      <text>
+        <t>Multiple on Invested Capital. Cash-on-cash return. 2.0x = doubled money. Less sensitive to timing than IRR.</t>
+      </text>
+    </comment>
+    <comment ref="C36" authorId="0" shapeId="0">
+      <text>
+        <t>Earnings Before Interest, Taxes, Depreciation, Amortization. Cash earnings available to service debt and pay equity.</t>
+      </text>
+    </comment>
+    <comment ref="C41" authorId="0" shapeId="0">
+      <text>
+        <t>Higher leverage amplifies equity returns but increases risk. Merchant assets: 40-50%. Contracted: 60-70%.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -523,7 +613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:C159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -615,6 +705,11 @@
           <t>Purchase price. EV = Equity + Debt, represents total asset value regardless of financing.</t>
         </is>
       </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Purchase price for asset</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="23" t="inlineStr">
@@ -627,6 +722,11 @@
           <t>Nameplate rating - maximum output. Used to calculate generation and capacity revenue.</t>
         </is>
       </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Nameplate MW</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="23" t="inlineStr">
@@ -639,6 +739,11 @@
           <t>Fuel efficiency - how much gas needed per kWh. Lower = better. 7,000 is efficient CCGT; peakers are 10,000+.</t>
         </is>
       </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Btu/kWh efficiency</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="23" t="inlineStr">
@@ -651,6 +756,11 @@
           <t>Actual generation / max possible generation. 55% is typical merchant CCGT - runs when profitable but not always.</t>
         </is>
       </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Nameplate MW</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="23" t="inlineStr">
@@ -663,6 +773,11 @@
           <t>Unplanned downtime. Reduces UCAP (capacity revenue) because you're paid for reliable capacity, not nameplate.</t>
         </is>
       </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Unplanned downtime %</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="23" t="inlineStr">
@@ -675,6 +790,11 @@
           <t>Debt / EV. 45% is moderate for merchant power - balances returns enhancement with covenant headroom.</t>
         </is>
       </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Debt / EV</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="23" t="inlineStr">
@@ -685,6 +805,11 @@
       <c r="B16" s="24" t="inlineStr">
         <is>
           <t>Mandatory prepayment of debt from excess cash flow. Higher sweep = faster paydown = lower refinancing risk.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>% of excess cash to prepay</t>
         </is>
       </c>
     </row>
@@ -711,6 +836,10 @@
           <t>Unforced Capacity = Nameplate × (1 - FOR). This is what you get paid for in capacity markets - your reliable capacity.</t>
         </is>
       </c>
+      <c r="C19">
+        <f> Capacity × (1 − FOR)</f>
+        <v/>
+      </c>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="23" t="inlineStr">
@@ -722,6 +851,10 @@
         <is>
           <t>Annual output = Capacity × CF × 8,760 hours/year. This drives energy revenue.</t>
         </is>
+      </c>
+      <c r="C20">
+        <f> Capacity × CF × 8760</f>
+        <v/>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
@@ -759,6 +892,10 @@
           <t>Generation × Power Price / 1,000,000. Converting MWh × $/MWh to $mm.</t>
         </is>
       </c>
+      <c r="C24">
+        <f> Gen × Price / 1E6</f>
+        <v/>
+      </c>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="23" t="inlineStr">
@@ -769,6 +906,11 @@
       <c r="B25" s="24" t="inlineStr">
         <is>
           <t>UCAP (MW) × $/kW-yr × 1,000 kW/MW / 1,000,000. Note: capacity price is per kW, not MW.</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Nameplate MW</t>
         </is>
       </c>
     </row>
@@ -785,6 +927,10 @@
 This is the #1 error candidates make - always verify the divisor.</t>
         </is>
       </c>
+      <c r="C26">
+        <f> Gen × HR × Gas / 1E9</f>
+        <v/>
+      </c>
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="23" t="inlineStr"/>
@@ -809,6 +955,11 @@
           <t>Merchant assets have volatile CFADS. Sweep structure pays down debt faster during good years, providing cushion for bad years. Alternative is sculpting (seen in contracted assets).</t>
         </is>
       </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>% of excess cash to prepay</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="23" t="inlineStr">
@@ -857,6 +1008,10 @@
           <t>IRR measures time-weighted return (sensitive to timing). MOIC measures total cash-on-cash return (ignores timing). Both matter.</t>
         </is>
       </c>
+      <c r="C34">
+        <f> Total In / Total Out</f>
+        <v/>
+      </c>
     </row>
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="23" t="inlineStr">
@@ -880,6 +1035,10 @@
         <is>
           <t>Standard infrastructure exit assumption. Buyer universe: other PE funds, utilities, infrastructure yield vehicles.</t>
         </is>
+      </c>
+      <c r="C36">
+        <f> Revenue − OpEx</f>
+        <v/>
       </c>
     </row>
     <row r="37" ht="30" customHeight="1">
@@ -929,9 +1088,133 @@
           <t>Balances return enhancement with covenant headroom. Higher leverage = higher returns but less cushion for volatility.</t>
         </is>
       </c>
-    </row>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Debt / EV</t>
+        </is>
+      </c>
+    </row>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71"/>
+    <row r="72"/>
+    <row r="73"/>
+    <row r="74"/>
+    <row r="75"/>
+    <row r="76"/>
+    <row r="77"/>
+    <row r="78"/>
+    <row r="79"/>
+    <row r="80"/>
+    <row r="81"/>
+    <row r="82"/>
+    <row r="83"/>
+    <row r="84"/>
+    <row r="85"/>
+    <row r="86"/>
+    <row r="87"/>
+    <row r="88"/>
+    <row r="89"/>
+    <row r="90"/>
+    <row r="91"/>
+    <row r="92"/>
+    <row r="93"/>
+    <row r="94"/>
+    <row r="95"/>
+    <row r="96"/>
+    <row r="97"/>
+    <row r="98"/>
+    <row r="99"/>
+    <row r="100"/>
+    <row r="101"/>
+    <row r="102"/>
+    <row r="103"/>
+    <row r="104"/>
+    <row r="105"/>
+    <row r="106"/>
+    <row r="107"/>
+    <row r="108"/>
+    <row r="109"/>
+    <row r="110"/>
+    <row r="111"/>
+    <row r="112"/>
+    <row r="113"/>
+    <row r="114"/>
+    <row r="115"/>
+    <row r="116"/>
+    <row r="117"/>
+    <row r="118"/>
+    <row r="119"/>
+    <row r="120"/>
+    <row r="121"/>
+    <row r="122"/>
+    <row r="123"/>
+    <row r="124"/>
+    <row r="125"/>
+    <row r="126"/>
+    <row r="127"/>
+    <row r="128"/>
+    <row r="129"/>
+    <row r="130"/>
+    <row r="131"/>
+    <row r="132"/>
+    <row r="133"/>
+    <row r="134"/>
+    <row r="135"/>
+    <row r="136"/>
+    <row r="137"/>
+    <row r="138"/>
+    <row r="139"/>
+    <row r="140"/>
+    <row r="141"/>
+    <row r="142"/>
+    <row r="143"/>
+    <row r="144"/>
+    <row r="145"/>
+    <row r="146"/>
+    <row r="147"/>
+    <row r="148"/>
+    <row r="149"/>
+    <row r="150"/>
+    <row r="151"/>
+    <row r="152"/>
+    <row r="153"/>
+    <row r="154"/>
+    <row r="155"/>
+    <row r="156"/>
+    <row r="157"/>
+    <row r="158"/>
+    <row r="159"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 

--- a/deliverables/deliverables-20260120-0030/Drill_1_CCGT.xlsx
+++ b/deliverables/deliverables-20260120-0030/Drill_1_CCGT.xlsx
@@ -242,82 +242,32 @@
   <commentList>
     <comment ref="C10" authorId="0" shapeId="0">
       <text>
-        <t>Enterprise Value = Equity + Debt. Represents total asset value regardless of financing structure. Key input for returns analysis.</t>
-      </text>
-    </comment>
-    <comment ref="C11" authorId="0" shapeId="0">
-      <text>
-        <t>Maximum output rating. Used to calculate generation and capacity revenue. Actual dispatch varies with economics.</t>
-      </text>
-    </comment>
-    <comment ref="C12" authorId="0" shapeId="0">
-      <text>
-        <t>Measures thermal efficiency. 7,000 Btu/kWh is efficient modern CCGT. Higher HR = less efficient = higher fuel cost per MWh.</t>
-      </text>
-    </comment>
-    <comment ref="C13" authorId="0" shapeId="0">
-      <text>
-        <t>Maximum output rating. Used to calculate generation and capacity revenue. Actual dispatch varies with economics.</t>
-      </text>
-    </comment>
-    <comment ref="C14" authorId="0" shapeId="0">
-      <text>
-        <t>Reduces UCAP (capacity revenue). Lenders/buyers discount nameplate by this factor. 5% is typical well-maintained plant.</t>
-      </text>
-    </comment>
-    <comment ref="C15" authorId="0" shapeId="0">
-      <text>
-        <t>Higher leverage amplifies equity returns but increases risk. Merchant assets: 40-50%. Contracted: 60-70%.</t>
+        <t>Enterprise Value = Equity + Debt. Represents total asset value regardless of financing structure.</t>
       </text>
     </comment>
     <comment ref="C16" authorId="0" shapeId="0">
       <text>
-        <t>Mandatory prepayment from excess cash. Lenders require this for merchant assets to accelerate deleveraging.</t>
-      </text>
-    </comment>
-    <comment ref="C19" authorId="0" shapeId="0">
-      <text>
-        <t>Unforced Capacity — what you can sell into capacity market. FOR reflects forced outages outside your control.</t>
-      </text>
-    </comment>
-    <comment ref="C20" authorId="0" shapeId="0">
-      <text>
-        <t>Annual MWh output. CF reflects expected dispatch based on merit order. 8760 = hours/year. 55% CF = ~4800 hrs/yr.</t>
-      </text>
-    </comment>
-    <comment ref="C24" authorId="0" shapeId="0">
-      <text>
-        <t>Merchant energy revenue from selling MWh into wholesale market. Divide by 1E6 to convert $ to $mm.</t>
-      </text>
-    </comment>
-    <comment ref="C25" authorId="0" shapeId="0">
-      <text>
-        <t>Maximum output rating. Used to calculate generation and capacity revenue. Actual dispatch varies with economics.</t>
+        <t>Mandatory prepayment from excess cash. Lenders require this for merchant assets.</t>
       </text>
     </comment>
     <comment ref="C26" authorId="0" shapeId="0">
       <text>
-        <t>Largest variable cost for thermal plants. HR measures efficiency. Divide by 1E9: MWh × Btu/kWh × $/mmBtu → $mm.</t>
+        <t>Largest variable cost for thermal plants. Divide by 1E9 to convert to $mm.</t>
       </text>
     </comment>
     <comment ref="C29" authorId="0" shapeId="0">
       <text>
-        <t>Mandatory prepayment from excess cash. Lenders require this for merchant assets to accelerate deleveraging.</t>
+        <t>Mandatory prepayment from excess cash. Lenders require this for merchant assets.</t>
       </text>
     </comment>
     <comment ref="C34" authorId="0" shapeId="0">
       <text>
-        <t>Multiple on Invested Capital. Cash-on-cash return. 2.0x = doubled money. Less sensitive to timing than IRR.</t>
+        <t>Multiple on Invested Capital. Cash-on-cash return. 2.0x = doubled money.</t>
       </text>
     </comment>
     <comment ref="C36" authorId="0" shapeId="0">
       <text>
-        <t>Earnings Before Interest, Taxes, Depreciation, Amortization. Cash earnings available to service debt and pay equity.</t>
-      </text>
-    </comment>
-    <comment ref="C41" authorId="0" shapeId="0">
-      <text>
-        <t>Higher leverage amplifies equity returns but increases risk. Merchant assets: 40-50%. Contracted: 60-70%.</t>
+        <t>Cash earnings before financing. What is available to service debt and pay equity.</t>
       </text>
     </comment>
   </commentList>
@@ -722,11 +672,6 @@
           <t>Nameplate rating - maximum output. Used to calculate generation and capacity revenue.</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Nameplate MW</t>
-        </is>
-      </c>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="23" t="inlineStr">
@@ -739,11 +684,6 @@
           <t>Fuel efficiency - how much gas needed per kWh. Lower = better. 7,000 is efficient CCGT; peakers are 10,000+.</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Btu/kWh efficiency</t>
-        </is>
-      </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="23" t="inlineStr">
@@ -756,11 +696,6 @@
           <t>Actual generation / max possible generation. 55% is typical merchant CCGT - runs when profitable but not always.</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Nameplate MW</t>
-        </is>
-      </c>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="23" t="inlineStr">
@@ -773,11 +708,6 @@
           <t>Unplanned downtime. Reduces UCAP (capacity revenue) because you're paid for reliable capacity, not nameplate.</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Unplanned downtime %</t>
-        </is>
-      </c>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="23" t="inlineStr">
@@ -790,11 +720,6 @@
           <t>Debt / EV. 45% is moderate for merchant power - balances returns enhancement with covenant headroom.</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Debt / EV</t>
-        </is>
-      </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="23" t="inlineStr">
@@ -809,7 +734,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>% of excess cash to prepay</t>
+          <t>MIN(Excess×%, Bal−Sched)</t>
         </is>
       </c>
     </row>
@@ -836,10 +761,6 @@
           <t>Unforced Capacity = Nameplate × (1 - FOR). This is what you get paid for in capacity markets - your reliable capacity.</t>
         </is>
       </c>
-      <c r="C19">
-        <f> Capacity × (1 − FOR)</f>
-        <v/>
-      </c>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="23" t="inlineStr">
@@ -851,10 +772,6 @@
         <is>
           <t>Annual output = Capacity × CF × 8,760 hours/year. This drives energy revenue.</t>
         </is>
-      </c>
-      <c r="C20">
-        <f> Capacity × CF × 8760</f>
-        <v/>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
@@ -892,10 +809,6 @@
           <t>Generation × Power Price / 1,000,000. Converting MWh × $/MWh to $mm.</t>
         </is>
       </c>
-      <c r="C24">
-        <f> Gen × Price / 1E6</f>
-        <v/>
-      </c>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="23" t="inlineStr">
@@ -906,11 +819,6 @@
       <c r="B25" s="24" t="inlineStr">
         <is>
           <t>UCAP (MW) × $/kW-yr × 1,000 kW/MW / 1,000,000. Note: capacity price is per kW, not MW.</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Nameplate MW</t>
         </is>
       </c>
     </row>
@@ -927,9 +835,10 @@
 This is the #1 error candidates make - always verify the divisor.</t>
         </is>
       </c>
-      <c r="C26">
-        <f> Gen × HR × Gas / 1E9</f>
-        <v/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Gen × HR × Gas / 1E9</t>
+        </is>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1">
@@ -957,7 +866,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>% of excess cash to prepay</t>
+          <t>MIN(Excess×%, Bal−Sched)</t>
         </is>
       </c>
     </row>
@@ -1008,9 +917,10 @@
           <t>IRR measures time-weighted return (sensitive to timing). MOIC measures total cash-on-cash return (ignores timing). Both matter.</t>
         </is>
       </c>
-      <c r="C34">
-        <f> Total In / Total Out</f>
-        <v/>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Total In / Total Out</t>
+        </is>
       </c>
     </row>
     <row r="35" ht="30" customHeight="1">
@@ -1036,9 +946,10 @@
           <t>Standard infrastructure exit assumption. Buyer universe: other PE funds, utilities, infrastructure yield vehicles.</t>
         </is>
       </c>
-      <c r="C36">
-        <f> Revenue − OpEx</f>
-        <v/>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Revenue minus OpEx</t>
+        </is>
       </c>
     </row>
     <row r="37" ht="30" customHeight="1">
@@ -1086,11 +997,6 @@
       <c r="B41" s="29" t="inlineStr">
         <is>
           <t>Balances return enhancement with covenant headroom. Higher leverage = higher returns but less cushion for volatility.</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Debt / EV</t>
         </is>
       </c>
     </row>

--- a/deliverables/deliverables-20260120-0030/Drill_1_CCGT.xlsx
+++ b/deliverables/deliverables-20260120-0030/Drill_1_CCGT.xlsx
@@ -8,7 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Intuition Guide" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case Prompt" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC Memo" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,7 +25,7 @@
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -53,6 +55,13 @@
     <font>
       <b val="1"/>
       <color rgb="000000FF"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="000066CC"/>
     </font>
   </fonts>
   <fills count="7">
@@ -111,7 +120,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -158,6 +167,8 @@
     <xf numFmtId="166" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -563,7 +574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C159"/>
+  <dimension ref="A1:C41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1000,124 +1011,6 @@
         </is>
       </c>
     </row>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
-    <row r="100"/>
-    <row r="101"/>
-    <row r="102"/>
-    <row r="103"/>
-    <row r="104"/>
-    <row r="105"/>
-    <row r="106"/>
-    <row r="107"/>
-    <row r="108"/>
-    <row r="109"/>
-    <row r="110"/>
-    <row r="111"/>
-    <row r="112"/>
-    <row r="113"/>
-    <row r="114"/>
-    <row r="115"/>
-    <row r="116"/>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
-    <row r="120"/>
-    <row r="121"/>
-    <row r="122"/>
-    <row r="123"/>
-    <row r="124"/>
-    <row r="125"/>
-    <row r="126"/>
-    <row r="127"/>
-    <row r="128"/>
-    <row r="129"/>
-    <row r="130"/>
-    <row r="131"/>
-    <row r="132"/>
-    <row r="133"/>
-    <row r="134"/>
-    <row r="135"/>
-    <row r="136"/>
-    <row r="137"/>
-    <row r="138"/>
-    <row r="139"/>
-    <row r="140"/>
-    <row r="141"/>
-    <row r="142"/>
-    <row r="143"/>
-    <row r="144"/>
-    <row r="145"/>
-    <row r="146"/>
-    <row r="147"/>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
-    <row r="155"/>
-    <row r="156"/>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -1125,6 +1018,257 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="80" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>CASE STUDY: CCGT ACQUISITION</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Time: 4 hours | Deliverables: Model + IC Memo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="34" t="inlineStr">
+        <is>
+          <t>SITUATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>365 MW CCGT in PJM West. Seller seeks $520mm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="34" t="inlineStr">
+        <is>
+          <t>KEY QUESTIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1. What levered IRR at indicative price?</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2. Downside DSCR under stress?</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>3. Key diligence items?</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>4. Protections to negotiate?</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="80" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>IC MEMO - COACHING FRAMEWORK</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="34" t="inlineStr">
+        <is>
+          <t>1. EXECUTIVE SUMMARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="35" t="inlineStr">
+        <is>
+          <t>Tip: Lead with IRR and recommendation</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>[Your answer: ___________]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="34" t="inlineStr">
+        <is>
+          <t>2. TRANSACTION OVERVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="35" t="inlineStr">
+        <is>
+          <t>Tip: Sources &amp; uses, debt terms</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>[Your answer: ___________]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="34" t="inlineStr">
+        <is>
+          <t>3. INVESTMENT THESIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="35" t="inlineStr">
+        <is>
+          <t>Tip: 3-4 bullets on attractiveness</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>[Your answer: ___________]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="34" t="inlineStr">
+        <is>
+          <t>4. KEY RISKS</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="35" t="inlineStr">
+        <is>
+          <t>Tip: Market, operational, regulatory</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>[Your answer: ___________]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="34" t="inlineStr">
+        <is>
+          <t>5. MITIGANTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="35" t="inlineStr">
+        <is>
+          <t>Tip: Hedging, contracts, structure</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>[Your answer: ___________]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="34" t="inlineStr">
+        <is>
+          <t>6. SENSITIVITIES</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="35" t="inlineStr">
+        <is>
+          <t>Tip: ±10-20% on key inputs</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>[Your answer: ___________]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="34" t="inlineStr">
+        <is>
+          <t>7. RECOMMENDATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="35" t="inlineStr">
+        <is>
+          <t>Tip: Clear yes/no with walk-away price</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>[Your answer: ___________]</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1273,7 +1417,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr"/>
       <c r="D6" s="30">
-        <f>MIN(E92:K92)</f>
+        <f>IF(COUNTIF(E92:K92,"&gt;0")&gt;0,MINIFS(E92:K92,E92:K92,"&gt;0"),0)</f>
         <v/>
       </c>
     </row>

--- a/deliverables/deliverables-20260120-0030/Drill_1_CCGT.xlsx
+++ b/deliverables/deliverables-20260120-0030/Drill_1_CCGT.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Intuition Guide" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case Prompt" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IC Memo" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model" sheetId="4" state="visible" r:id="rId4"/>
@@ -120,7 +120,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -169,6 +169,12 @@
     <xf numFmtId="165" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -243,46 +249,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Lotus Infrastructure</author>
-  </authors>
-  <commentList>
-    <comment ref="C10" authorId="0" shapeId="0">
-      <text>
-        <t>Enterprise Value = Equity + Debt. Represents total asset value regardless of financing structure.</t>
-      </text>
-    </comment>
-    <comment ref="C16" authorId="0" shapeId="0">
-      <text>
-        <t>Mandatory prepayment from excess cash. Lenders require this for merchant assets.</t>
-      </text>
-    </comment>
-    <comment ref="C26" authorId="0" shapeId="0">
-      <text>
-        <t>Largest variable cost for thermal plants. Divide by 1E9 to convert to $mm.</t>
-      </text>
-    </comment>
-    <comment ref="C29" authorId="0" shapeId="0">
-      <text>
-        <t>Mandatory prepayment from excess cash. Lenders require this for merchant assets.</t>
-      </text>
-    </comment>
-    <comment ref="C34" authorId="0" shapeId="0">
-      <text>
-        <t>Multiple on Invested Capital. Cash-on-cash return. 2.0x = doubled money.</t>
-      </text>
-    </comment>
-    <comment ref="C36" authorId="0" shapeId="0">
-      <text>
-        <t>Cash earnings before financing. What is available to service debt and pay equity.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -574,446 +540,716 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:A119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="95" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="23" t="inlineStr">
-        <is>
-          <t>CCGT MODEL - INTUITION GUIDE</t>
-        </is>
-      </c>
-      <c r="B1" s="24" t="inlineStr"/>
-    </row>
-    <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="23" t="inlineStr"/>
-      <c r="B2" s="24" t="inlineStr"/>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="23" t="inlineStr">
-        <is>
-          <t>SECTION</t>
-        </is>
-      </c>
-      <c r="B3" s="25" t="inlineStr">
-        <is>
-          <t>WHY IT MATTERS / KEY LOGIC</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="23" t="inlineStr"/>
-      <c r="B4" s="24" t="inlineStr"/>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="26" t="inlineStr">
-        <is>
-          <t>═══ BUSINESS CONTEXT ═══</t>
-        </is>
-      </c>
-      <c r="B5" s="27" t="n"/>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="23" t="inlineStr">
-        <is>
-          <t>What is a CCGT?</t>
-        </is>
-      </c>
-      <c r="B6" s="24" t="inlineStr">
-        <is>
-          <t>Combined Cycle Gas Turbine - efficient baseload gas plant that uses waste heat from gas turbines to power steam turbines. 'Combined' refers to combining gas and steam cycles for ~60% efficiency vs ~35% for simple cycle.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="23" t="inlineStr">
-        <is>
-          <t>Revenue Streams</t>
-        </is>
-      </c>
-      <c r="B7" s="24" t="inlineStr">
-        <is>
-          <t>1) Energy revenue (selling power at spot/contract prices) - driven by spark spread (power price - fuel cost)
-2) Capacity revenue (payment for being available) - driven by capacity auction prices
-Revenue volatility justifies cash sweep structure to accelerate debt paydown during good years.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="23" t="inlineStr"/>
-      <c r="B8" s="24" t="inlineStr"/>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="26" t="inlineStr">
-        <is>
-          <t>═══ INPUTS LOGIC ═══</t>
-        </is>
-      </c>
-      <c r="B9" s="27" t="n"/>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="23" t="inlineStr">
-        <is>
-          <t>Entry EV ($520mm)</t>
-        </is>
-      </c>
-      <c r="B10" s="24" t="inlineStr">
-        <is>
-          <t>Purchase price. EV = Equity + Debt, represents total asset value regardless of financing.</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Purchase price for asset</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="23" t="inlineStr">
-        <is>
-          <t>Capacity (365 MW)</t>
-        </is>
-      </c>
-      <c r="B11" s="24" t="inlineStr">
-        <is>
-          <t>Nameplate rating - maximum output. Used to calculate generation and capacity revenue.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="23" t="inlineStr">
-        <is>
-          <t>Heat Rate (7,000 Btu/kWh)</t>
-        </is>
-      </c>
-      <c r="B12" s="24" t="inlineStr">
-        <is>
-          <t>Fuel efficiency - how much gas needed per kWh. Lower = better. 7,000 is efficient CCGT; peakers are 10,000+.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="23" t="inlineStr">
-        <is>
-          <t>Capacity Factor (55%)</t>
-        </is>
-      </c>
-      <c r="B13" s="24" t="inlineStr">
-        <is>
-          <t>Actual generation / max possible generation. 55% is typical merchant CCGT - runs when profitable but not always.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="23" t="inlineStr">
-        <is>
-          <t>Forced Outage Rate (5%)</t>
-        </is>
-      </c>
-      <c r="B14" s="24" t="inlineStr">
-        <is>
-          <t>Unplanned downtime. Reduces UCAP (capacity revenue) because you're paid for reliable capacity, not nameplate.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="23" t="inlineStr">
-        <is>
-          <t>Leverage (45%)</t>
-        </is>
-      </c>
-      <c r="B15" s="24" t="inlineStr">
-        <is>
-          <t>Debt / EV. 45% is moderate for merchant power - balances returns enhancement with covenant headroom.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="23" t="inlineStr">
-        <is>
-          <t>Cash Sweep (75%)</t>
-        </is>
-      </c>
-      <c r="B16" s="24" t="inlineStr">
-        <is>
-          <t>Mandatory prepayment of debt from excess cash flow. Higher sweep = faster paydown = lower refinancing risk.</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>MIN(Excess×%, Bal−Sched)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="23" t="inlineStr"/>
-      <c r="B17" s="24" t="inlineStr"/>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="26" t="inlineStr">
-        <is>
-          <t>═══ CALCULATED ITEMS ═══</t>
-        </is>
-      </c>
-      <c r="B18" s="27" t="n"/>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="23" t="inlineStr">
-        <is>
-          <t>UCAP (346.75 MW)</t>
-        </is>
-      </c>
-      <c r="B19" s="24" t="inlineStr">
-        <is>
-          <t>Unforced Capacity = Nameplate × (1 - FOR). This is what you get paid for in capacity markets - your reliable capacity.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="23" t="inlineStr">
-        <is>
-          <t>Generation (1,758,390 MWh)</t>
-        </is>
-      </c>
-      <c r="B20" s="24" t="inlineStr">
-        <is>
-          <t>Annual output = Capacity × CF × 8,760 hours/year. This drives energy revenue.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="23" t="inlineStr"/>
-      <c r="B21" s="24" t="inlineStr"/>
-    </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="26" t="inlineStr">
-        <is>
-          <t>═══ OPERATING MODEL ═══</t>
-        </is>
-      </c>
-      <c r="B22" s="27" t="n"/>
-    </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="23" t="inlineStr">
-        <is>
-          <t>Price Escalation</t>
-        </is>
-      </c>
-      <c r="B23" s="24" t="inlineStr">
-        <is>
-          <t>All prices/costs grow at escalation rate (2.5%). Reflects inflation and market dynamics.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="23" t="inlineStr">
-        <is>
-          <t>Energy Revenue</t>
-        </is>
-      </c>
-      <c r="B24" s="24" t="inlineStr">
-        <is>
-          <t>Generation × Power Price / 1,000,000. Converting MWh × $/MWh to $mm.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="23" t="inlineStr">
-        <is>
-          <t>Capacity Revenue</t>
-        </is>
-      </c>
-      <c r="B25" s="24" t="inlineStr">
-        <is>
-          <t>UCAP (MW) × $/kW-yr × 1,000 kW/MW / 1,000,000. Note: capacity price is per kW, not MW.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="23" t="inlineStr">
-        <is>
-          <t>Fuel Cost (CRITICAL)</t>
-        </is>
-      </c>
-      <c r="B26" s="24" t="inlineStr">
-        <is>
-          <t>Generation × Heat Rate × Gas Price / 1,000,000,000.
-Dimensional analysis: MWh × Btu/kWh × $/mmBtu / 10^9 = $mm
-This is the #1 error candidates make - always verify the divisor.</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Gen × HR × Gas / 1E9</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="23" t="inlineStr"/>
-      <c r="B27" s="24" t="inlineStr"/>
-    </row>
-    <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="26" t="inlineStr">
-        <is>
-          <t>═══ DEBT MECHANICS ═══</t>
-        </is>
-      </c>
-      <c r="B28" s="27" t="n"/>
-    </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="23" t="inlineStr">
-        <is>
-          <t>Why Cash Sweep?</t>
-        </is>
-      </c>
-      <c r="B29" s="24" t="inlineStr">
-        <is>
-          <t>Merchant assets have volatile CFADS. Sweep structure pays down debt faster during good years, providing cushion for bad years. Alternative is sculpting (seen in contracted assets).</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>MIN(Excess×%, Bal−Sched)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="23" t="inlineStr">
-        <is>
-          <t>DSRA Purpose</t>
-        </is>
-      </c>
-      <c r="B30" s="24" t="inlineStr">
-        <is>
-          <t>6 months of debt service held in reserve. If CFADS drops, DSRA provides liquidity to make debt payments and avoid covenant breach.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="23" t="inlineStr">
-        <is>
-          <t>Lock-up Test</t>
-        </is>
-      </c>
-      <c r="B31" s="24" t="inlineStr">
-        <is>
-          <t>If DSCR &lt; 1.10x, distributions are 'locked up' - all cash goes to debt paydown. Protects lenders.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="23" t="inlineStr"/>
-      <c r="B32" s="24" t="inlineStr"/>
-    </row>
-    <row r="33" ht="30" customHeight="1">
-      <c r="A33" s="26" t="inlineStr">
-        <is>
-          <t>═══ RETURNS ═══</t>
-        </is>
-      </c>
-      <c r="B33" s="27" t="n"/>
-    </row>
-    <row r="34" ht="30" customHeight="1">
-      <c r="A34" s="23" t="inlineStr">
-        <is>
-          <t>IRR vs MOIC</t>
-        </is>
-      </c>
-      <c r="B34" s="24" t="inlineStr">
-        <is>
-          <t>IRR measures time-weighted return (sensitive to timing). MOIC measures total cash-on-cash return (ignores timing). Both matter.</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Total In / Total Out</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="23" t="inlineStr">
-        <is>
-          <t>Levered vs Unlevered</t>
-        </is>
-      </c>
-      <c r="B35" s="24" t="inlineStr">
-        <is>
-          <t>Levered IRR = return to equity. Unlevered IRR = return to total capital. Difference is the 'leverage benefit.'</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="30" customHeight="1">
-      <c r="A36" s="23" t="inlineStr">
-        <is>
-          <t>Exit at 7.0x EBITDA</t>
-        </is>
-      </c>
-      <c r="B36" s="24" t="inlineStr">
-        <is>
-          <t>Standard infrastructure exit assumption. Buyer universe: other PE funds, utilities, infrastructure yield vehicles.</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Revenue minus OpEx</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="30" customHeight="1">
-      <c r="A37" s="23" t="inlineStr"/>
-      <c r="B37" s="24" t="inlineStr"/>
-    </row>
-    <row r="38" ht="30" customHeight="1">
-      <c r="A38" s="26" t="inlineStr">
-        <is>
-          <t>═══ COMMON IC QUESTIONS ═══</t>
-        </is>
-      </c>
-      <c r="B38" s="27" t="n"/>
-    </row>
-    <row r="39" ht="30" customHeight="1">
-      <c r="A39" s="28" t="inlineStr">
-        <is>
-          <t>Q: Walk me through IRR bridge</t>
-        </is>
-      </c>
-      <c r="B39" s="29" t="inlineStr">
-        <is>
-          <t>Start with unlevered IRR, add leverage benefit (cheaper debt vs equity), subtract financing costs (interest, fees).</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="30" customHeight="1">
-      <c r="A40" s="28" t="inlineStr">
-        <is>
-          <t>Q: What if gas prices spike?</t>
-        </is>
-      </c>
-      <c r="B40" s="29" t="inlineStr">
-        <is>
-          <t>Higher fuel costs reduce spark spread and EBITDA. Run sensitivity showing EBITDA and DSCR impact.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="30" customHeight="1">
-      <c r="A41" s="28" t="inlineStr">
-        <is>
-          <t>Q: Why 45% leverage?</t>
-        </is>
-      </c>
-      <c r="B41" s="29" t="inlineStr">
-        <is>
-          <t>Balances return enhancement with covenant headroom. Higher leverage = higher returns but less cushion for volatility.</t>
+    <row r="1">
+      <c r="A1">
+        <f>==========================================================================</f>
+        <v/>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>LOTUS INFRASTRUCTURE PARTNERS</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>CASE STUDY: COMBINED CYCLE GAS TURBINE ACQUISITION</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <f>==========================================================================</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>TIME: 4 Hours | DATE: January 2026 | DELIVERABLES: Model + IC Memo</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="34" t="inlineStr">
+        <is>
+          <t>--- MODEL TIMELINE ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Year 0 (2025): Transaction close Q4; debt funding at close</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Year 1 (2026): First full operating year under Lotus ownership</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Year 7 (2032): Target exit / debt maturity (75% cash sweep structure)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Year 10 (2035): Model horizon end</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="34" t="inlineStr">
+        <is>
+          <t>--- SITUATION ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="37" t="inlineStr">
+        <is>
+          <t>Lotus Infrastructure Partners has been approached by GenCo Partners regarding
+the potential acquisition of a 365 MW combined-cycle gas turbine power plant
+located in PJM West (AEP zone). The facility achieved commercial operation in
+2015 and has approximately 15 years of remaining useful life.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="37" t="inlineStr">
+        <is>
+          <t>The plant operates as a fully merchant facility, selling energy into PJM's
+day-ahead and real-time markets and clearing in the RPM capacity auction.
+Historical capacity factors have averaged 50-60%. The 7,000 Btu/kWh heat rate
+makes it competitive against older thermal generation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="37" t="inlineStr">
+        <is>
+          <t>GenCo is divesting non-core assets to fund renewable development. They are
+seeking $520mm with final bids expected by February 15, 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="34" t="inlineStr">
+        <is>
+          <t>--- KEY VALUE DRIVERS ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>* Spark Spread: Power price minus (Heat Rate x Gas Price) - core margin driver</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>* Capacity Factor: Drives MWh generation; modeled NET of outages</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>* Capacity Accreditation: UCAP rating determines capacity revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>* Gas Basis: Spread between Henry Hub and local delivery point</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="34" t="inlineStr">
+        <is>
+          <t>--- STEP-BY-STEP MODEL BUILDING GUIDE ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="37" t="inlineStr">
+        <is>
+          <t>STEP-BY-STEP MODEL BUILDING GUIDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="37" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="37" t="inlineStr">
+        <is>
+          <t>1. SET UP INPUTS (Column D)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Transaction: Entry EV ($520mm), fees (1.5%), exit multiple (7x), exit year (7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Asset: Capacity (365 MW), heat rate (7,000), CF (55%), FOR (5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Pricing: Power ($48/MWh), capacity ($110/kW-yr), gas ($3/MMBtu), esc (2.5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Financing: Leverage (45%), rate (6.5%), tenor (7 yrs), DSRA (6 mo), sweep (75%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="37" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="37" t="inlineStr">
+        <is>
+          <t>2. BUILD CALCULATED ITEMS</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - UCAP = Capacity x (1 - FOR) = 365 x 0.95 = 346.75 MW</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Generation = Capacity x CF x 8,760 = 1,758,900 MWh</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Debt Amount = Entry EV x Leverage = $234mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="37" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="37" t="inlineStr">
+        <is>
+          <t>3. BUILD OPERATING MODEL (Columns E-N)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Escalate prices: Yn = Y1 x (1 + esc)^(n-1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Energy Revenue = Generation x Power Price / 1,000,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Capacity Revenue = UCAP x Cap Price x 1,000 / 1,000,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Fuel Cost = Generation x Heat Rate x Gas / 1,000,000,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - EBITDA = Revenue - OpEx</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="37" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="37" t="inlineStr">
+        <is>
+          <t>4. BUILD CASH FLOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - EBIT = EBITDA - Depreciation</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Taxes = MAX(0, EBIT) x Tax Rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - CFADS = EBITDA - Taxes</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="37" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="37" t="inlineStr">
+        <is>
+          <t>5. BUILD DEBT SCHEDULE (CASH SWEEP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   a) Beginning Balance: Y1 = Debt; Yn = Prior End Bal</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   b) Interest = Beg Bal x Rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   c) Scheduled Principal = MIN(Debt/Tenor, Beg Bal)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   d) Debt Service (Pre-Sweep) = Interest + Sched Prin</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   e) Scheduled DS (for DSRA) = Independent calc using straight-line</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   f) DSRA Target = NEXT Year's Sched DS x (DSRA Mo / 12)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   g) Excess Cash = CFADS - DS - DSRA Funding</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   h) Cash Sweep = MIN(Excess x 75%, Beg Bal - Sched Prin)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   i) Ending Balance = MAX(0, Beg - Total Principal)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   j) DSCR = CFADS / DS (Pre-Sweep)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="37" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="37" t="inlineStr">
+        <is>
+          <t>6. BUILD S&amp;U, EXIT, RETURNS</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - S&amp;U must balance (Uses = Sources)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Exit EV = EBITDA x Multiple</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Levered IRR = IRR of equity cash flows</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="34" t="inlineStr">
+        <is>
+          <t>--- HOW TO AVOID CIRCULARITY ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>HOW TO AVOID DSRA CIRCULARITY</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>The Problem:</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>DSRA Target -&gt; Debt Service -&gt; Sweep -&gt; Excess Cash -&gt; DSRA Funding -&gt; DSRA Target</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>The Solution:</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Use "Scheduled DS" (straight-line, no sweep) for DSRA sizing:</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>- Scheduled DS assumes NO cash sweep, just scheduled payments</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>- It's calculated INDEPENDENTLY of actual debt paydown</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>- DSRA Target references this independent row</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Formula: Scheduled DS = MAX(0, Debt - (Yr-1) x Sched Prin) x Rate + Sched Prin</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="34" t="inlineStr">
+        <is>
+          <t>--- ALTERNATIVE SCENARIOS ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>ALTERNATIVE SCENARIOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>A. Sculpted Debt (not sweep):</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Principal = CFADS / Target DSCR - Interest</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - No sweep mechanics needed</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>B. Contracted Revenue (PPA/Hedge):</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Use contract price, not merchant</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - More debt capacity</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>C. Major Maintenance Reserve:</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Add MRA similar to DSRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - Funds hot gas path inspection</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="34" t="inlineStr">
+        <is>
+          <t>--- QA CHECKS ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>QA CHECKS TO VERIFY MODEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>1. S&amp;U Balance: =IF(ABS(Uses-Sources)&lt;0.01,"PASS","FAIL")</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2. Debt Payoff: Ending Bal near $0 by tenor end</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>3. Min DSCR: Use MINIFS to exclude post-payoff zeros</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>4. DSRA: Never negative; releases at debt payoff</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>5. Sign Convention: Outflows negative, inflows positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>6. No Circular Refs: Excel shouldn't show warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="34" t="inlineStr">
+        <is>
+          <t>--- HINTS &amp; PITFALLS ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="35" t="inlineStr">
+        <is>
+          <t>* Spark spread: $1/MWh x 1.76M MWh = $1.76mm EBITDA impact</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="35" t="inlineStr">
+        <is>
+          <t>* CF is NET of outages - don't double-count FOR in generation</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="35" t="inlineStr">
+        <is>
+          <t>* FOR only derates UCAP for capacity revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="35" t="inlineStr">
+        <is>
+          <t>* Fuel divisor is 1E9 (billion), not 1E6 (million)</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="34" t="inlineStr">
+        <is>
+          <t>--- INTERVIEW QUESTIONS ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Q: Walk me through how $5/MWh power price change affects IRR.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Q: Why cash sweep instead of sculpted debt?</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Q: What would make you walk away from this deal?</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Q: How would you hedge the spark spread exposure?</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -1299,38 +1535,60 @@
           <t>CCGT Model - Lotus Infrastructure Partners</t>
         </is>
       </c>
-      <c r="D1" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E1" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F1" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G1" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H1" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="I1" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J1" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="K1" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="L1" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="M1" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="N1" s="2" t="n">
-        <v>10</v>
+      <c r="D1" s="36" t="inlineStr">
+        <is>
+          <t>Y0 (2025)</t>
+        </is>
+      </c>
+      <c r="E1" s="36" t="inlineStr">
+        <is>
+          <t>Y1 (2026)</t>
+        </is>
+      </c>
+      <c r="F1" s="36" t="inlineStr">
+        <is>
+          <t>Y2 (2027)</t>
+        </is>
+      </c>
+      <c r="G1" s="36" t="inlineStr">
+        <is>
+          <t>Y3 (2028)</t>
+        </is>
+      </c>
+      <c r="H1" s="36" t="inlineStr">
+        <is>
+          <t>Y4 (2029)</t>
+        </is>
+      </c>
+      <c r="I1" s="36" t="inlineStr">
+        <is>
+          <t>Y5 (2030)</t>
+        </is>
+      </c>
+      <c r="J1" s="36" t="inlineStr">
+        <is>
+          <t>Y6 (2031)</t>
+        </is>
+      </c>
+      <c r="K1" s="36" t="inlineStr">
+        <is>
+          <t>Y7 (2032)</t>
+        </is>
+      </c>
+      <c r="L1" s="36" t="inlineStr">
+        <is>
+          <t>Y8 (2033)</t>
+        </is>
+      </c>
+      <c r="M1" s="36" t="inlineStr">
+        <is>
+          <t>Y9 (2034)</t>
+        </is>
+      </c>
+      <c r="N1" s="36" t="inlineStr">
+        <is>
+          <t>Y10 (2035)</t>
+        </is>
       </c>
     </row>
     <row r="2">

--- a/deliverables/deliverables-20260120-0030/Drill_1_CCGT.xlsx
+++ b/deliverables/deliverables-20260120-0030/Drill_1_CCGT.xlsx
@@ -27,7 +27,7 @@
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -92,6 +92,11 @@
       <i val="1"/>
       <color rgb="00666666"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -149,7 +154,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -227,6 +232,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -309,7 +315,7 @@
     <author>Claude</author>
   </authors>
   <commentList>
-    <comment ref="A81" authorId="0" shapeId="0">
+    <comment ref="A82" authorId="0" shapeId="0">
       <text>
         <t xml:space="preserve">SPARK SPREAD
 Profit per MWh after fuel cost.
@@ -3167,7 +3173,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N151"/>
+  <dimension ref="A1:N148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -3249,46 +3255,36 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="57" t="inlineStr">
+        <is>
+          <t>═══ DRILL MODE: Key formulas blanked. Rebuild using Formula Logic hints in Column C. ═══</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>═══ AUDIT STRIP ═══</t>
         </is>
       </c>
-      <c r="B2" s="4" t="n"/>
-      <c r="C2" s="4" t="n"/>
-      <c r="D2" s="4" t="n"/>
-      <c r="E2" s="4" t="n"/>
-      <c r="F2" s="4" t="n"/>
-      <c r="G2" s="4" t="n"/>
-      <c r="H2" s="4" t="n"/>
-      <c r="I2" s="4" t="n"/>
-      <c r="J2" s="4" t="n"/>
-      <c r="K2" s="4" t="n"/>
-      <c r="L2" s="4" t="n"/>
-      <c r="M2" s="4" t="n"/>
-      <c r="N2" s="4" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>Entry EV</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="inlineStr"/>
-      <c r="D3" s="7">
-        <f>$D$17</f>
-        <v/>
-      </c>
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="n"/>
+      <c r="F3" s="4" t="n"/>
+      <c r="G3" s="4" t="n"/>
+      <c r="H3" s="4" t="n"/>
+      <c r="I3" s="4" t="n"/>
+      <c r="J3" s="4" t="n"/>
+      <c r="K3" s="4" t="n"/>
+      <c r="L3" s="4" t="n"/>
+      <c r="M3" s="4" t="n"/>
+      <c r="N3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Y1 EBITDA</t>
+          <t>Entry EV</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -3298,680 +3294,671 @@
       </c>
       <c r="C4" s="6" t="inlineStr"/>
       <c r="D4" s="7">
-        <f>E74</f>
+        <f>$D$17</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="38" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Y1 EBITDA</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr"/>
+      <c r="D5" s="7" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="38" t="inlineStr">
         <is>
           <t>═══════════ CONTROL PANEL ═══════════</t>
         </is>
       </c>
-      <c r="B5" s="49" t="n"/>
-      <c r="C5" s="49" t="n"/>
-      <c r="D5" s="49" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="49" t="n"/>
       <c r="B6" s="49" t="n"/>
       <c r="C6" s="49" t="n"/>
       <c r="D6" s="49" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="50" t="inlineStr">
-        <is>
-          <t>REVENUE</t>
-        </is>
-      </c>
+      <c r="A7" s="49" t="n"/>
       <c r="B7" s="49" t="n"/>
       <c r="C7" s="49" t="n"/>
       <c r="D7" s="49" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="34" t="inlineStr">
-        <is>
-          <t>Revenue Mode</t>
+      <c r="A8" s="50" t="inlineStr">
+        <is>
+          <t>REVENUE</t>
         </is>
       </c>
       <c r="B8" s="49" t="n"/>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Merchant / Contracted / Hybrid</t>
-        </is>
-      </c>
-      <c r="D8" s="47" t="inlineStr">
-        <is>
-          <t>Merchant</t>
-        </is>
-      </c>
+      <c r="C8" s="49" t="n"/>
+      <c r="D8" s="49" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="34" t="inlineStr">
         <is>
-          <t>Contract End Year</t>
+          <t>Revenue Mode</t>
         </is>
       </c>
       <c r="B9" s="49" t="n"/>
       <c r="C9" s="6" t="inlineStr">
         <is>
+          <t>Merchant / Contracted / Hybrid</t>
+        </is>
+      </c>
+      <c r="D9" s="47" t="inlineStr">
+        <is>
+          <t>Merchant</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="34" t="inlineStr">
+        <is>
+          <t>Contract End Year</t>
+        </is>
+      </c>
+      <c r="B10" s="49" t="n"/>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
           <t>0 = pure merchant; else year PPA ends</t>
         </is>
       </c>
-      <c r="D9" s="47" t="n">
+      <c r="D10" s="47" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="49" t="n"/>
-      <c r="B10" s="49" t="n"/>
-      <c r="C10" s="49" t="n"/>
-      <c r="D10" s="49" t="n"/>
-    </row>
     <row r="11">
-      <c r="A11" s="50" t="inlineStr">
-        <is>
-          <t>TIMING</t>
-        </is>
-      </c>
+      <c r="A11" s="49" t="n"/>
       <c r="B11" s="49" t="n"/>
       <c r="C11" s="49" t="n"/>
       <c r="D11" s="49" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="34" t="inlineStr">
-        <is>
-          <t>Exit Year</t>
+      <c r="A12" s="50" t="inlineStr">
+        <is>
+          <t>TIMING</t>
         </is>
       </c>
       <c r="B12" s="49" t="n"/>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>5 / 7 / 10</t>
-        </is>
-      </c>
-      <c r="D12" s="47" t="n">
-        <v>7</v>
-      </c>
+      <c r="C12" s="49" t="n"/>
+      <c r="D12" s="49" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="34" t="inlineStr">
         <is>
-          <t>Tax Credit End Year</t>
+          <t>Exit Year</t>
         </is>
       </c>
       <c r="B13" s="49" t="n"/>
       <c r="C13" s="6" t="inlineStr">
         <is>
+          <t>5 / 7 / 10</t>
+        </is>
+      </c>
+      <c r="D13" s="47" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="34" t="inlineStr">
+        <is>
+          <t>Tax Credit End Year</t>
+        </is>
+      </c>
+      <c r="B14" s="49" t="n"/>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
           <t>0 = N/A; else last year of PTC/ITC</t>
         </is>
       </c>
-      <c r="D13" s="47" t="n">
+      <c r="D14" s="47" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="49" t="n"/>
-      <c r="B14" s="49" t="n"/>
-      <c r="C14" s="49" t="n"/>
-      <c r="D14" s="49" t="n"/>
-    </row>
     <row r="15">
-      <c r="A15" s="50" t="inlineStr">
-        <is>
-          <t>DEBT</t>
-        </is>
-      </c>
+      <c r="A15" s="49" t="n"/>
       <c r="B15" s="49" t="n"/>
       <c r="C15" s="49" t="n"/>
-      <c r="D15" s="51" t="n"/>
+      <c r="D15" s="49" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="34" t="inlineStr">
-        <is>
-          <t>Debt Sweep</t>
+      <c r="A16" s="50" t="inlineStr">
+        <is>
+          <t>DEBT</t>
         </is>
       </c>
       <c r="B16" s="49" t="n"/>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>ON / OFF (for sweep assets)</t>
-        </is>
-      </c>
-      <c r="D16" s="33" t="inlineStr">
-        <is>
-          <t>ON</t>
-        </is>
-      </c>
+      <c r="C16" s="49" t="n"/>
+      <c r="D16" s="51" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="34" t="inlineStr">
         <is>
-          <t>Sweep %</t>
+          <t>Debt Sweep</t>
         </is>
       </c>
       <c r="B17" s="49" t="n"/>
       <c r="C17" s="6" t="inlineStr">
         <is>
+          <t>ON / OFF (for sweep assets)</t>
+        </is>
+      </c>
+      <c r="D17" s="33" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="34" t="inlineStr">
+        <is>
+          <t>Sweep %</t>
+        </is>
+      </c>
+      <c r="B18" s="49" t="n"/>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
           <t>Active when Sweep = ON</t>
         </is>
       </c>
-      <c r="D17" s="32" t="inlineStr">
+      <c r="D18" s="32" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="49" t="n"/>
-      <c r="B18" s="49" t="n"/>
-      <c r="C18" s="49" t="n"/>
-      <c r="D18" s="52" t="n"/>
-    </row>
     <row r="19">
-      <c r="A19" s="50" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
+      <c r="A19" s="49" t="n"/>
       <c r="B19" s="49" t="n"/>
       <c r="C19" s="49" t="n"/>
-      <c r="D19" s="53" t="n"/>
+      <c r="D19" s="52" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="34" t="inlineStr">
+      <c r="A20" s="50" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="B20" s="49" t="n"/>
+      <c r="C20" s="49" t="n"/>
+      <c r="D20" s="53" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="34" t="inlineStr">
         <is>
           <t>Carbon Region</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>None / CARB / RGGI (thermal only)</t>
         </is>
       </c>
-      <c r="D20" s="47" t="inlineStr">
+      <c r="D21" s="47" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="54" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="54" t="inlineStr">
         <is>
           <t>Exit Method</t>
         </is>
       </c>
-      <c r="B21" s="49" t="n"/>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="B22" s="49" t="n"/>
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>Multiple / DCF</t>
         </is>
       </c>
-      <c r="D21" s="47" t="inlineStr">
+      <c r="D22" s="47" t="inlineStr">
         <is>
           <t>Multiple</t>
         </is>
       </c>
-      <c r="E21" s="4" t="n"/>
-      <c r="F21" s="4" t="n"/>
-      <c r="G21" s="4" t="n"/>
-      <c r="H21" s="4" t="n"/>
-      <c r="I21" s="4" t="n"/>
-      <c r="J21" s="4" t="n"/>
-      <c r="K21" s="4" t="n"/>
-      <c r="L21" s="4" t="n"/>
-      <c r="M21" s="4" t="n"/>
-      <c r="N21" s="4" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="38" t="inlineStr">
+      <c r="E22" s="4" t="n"/>
+      <c r="F22" s="4" t="n"/>
+      <c r="G22" s="4" t="n"/>
+      <c r="H22" s="4" t="n"/>
+      <c r="I22" s="4" t="n"/>
+      <c r="J22" s="4" t="n"/>
+      <c r="K22" s="4" t="n"/>
+      <c r="L22" s="4" t="n"/>
+      <c r="M22" s="4" t="n"/>
+      <c r="N22" s="4" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="38" t="inlineStr">
         <is>
           <t>════════════════════════════════════</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="inlineStr"/>
-      <c r="C22" s="6" t="inlineStr"/>
-      <c r="D22" s="10">
-        <f>D119</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>Debt Payoff Y7</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr"/>
       <c r="C23" s="6" t="inlineStr"/>
       <c r="D23" s="10">
-        <f>IF(K91&lt;1,"PASS","FAIL")</f>
+        <f>D119</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Min DSCR ≥ 1.25x</t>
+          <t>Debt Payoff Y7</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr"/>
       <c r="C24" s="6" t="inlineStr"/>
       <c r="D24" s="10">
-        <f>IF(D6&gt;=1.25,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25"/>
+        <f>IF(K91&lt;1,"PASS","FAIL")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Min DSCR ≥ 1.25x</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr"/>
+      <c r="C25" s="6" t="inlineStr"/>
+      <c r="D25" s="10" t="inlineStr"/>
+    </row>
     <row r="26"/>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>TRANSACTION INPUTS</t>
         </is>
       </c>
-      <c r="B27" s="4" t="n"/>
-      <c r="C27" s="4" t="n"/>
-      <c r="D27" s="4" t="n"/>
-      <c r="E27" s="4" t="n"/>
-      <c r="F27" s="4" t="n"/>
-      <c r="G27" s="4" t="n"/>
-      <c r="H27" s="4" t="n"/>
-      <c r="I27" s="4" t="n"/>
-      <c r="J27" s="4" t="n"/>
-      <c r="K27" s="4" t="n"/>
-      <c r="L27" s="4" t="n"/>
-      <c r="M27" s="4" t="n"/>
-      <c r="N27" s="4" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>Entry EV</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>Purchase price</t>
-        </is>
-      </c>
-      <c r="D28" s="11" t="n">
-        <v>520</v>
-      </c>
+      <c r="B28" s="4" t="n"/>
+      <c r="C28" s="4" t="n"/>
+      <c r="D28" s="4" t="n"/>
+      <c r="E28" s="4" t="n"/>
+      <c r="F28" s="4" t="n"/>
+      <c r="G28" s="4" t="n"/>
+      <c r="H28" s="4" t="n"/>
+      <c r="I28" s="4" t="n"/>
+      <c r="J28" s="4" t="n"/>
+      <c r="K28" s="4" t="n"/>
+      <c r="L28" s="4" t="n"/>
+      <c r="M28" s="4" t="n"/>
+      <c r="N28" s="4" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Transaction Fees</t>
+          <t>Entry EV</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>$mm</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Legal, advisory, financing</t>
-        </is>
-      </c>
-      <c r="D29" s="32" t="n">
-        <v>0.015</v>
+          <t>Purchase price</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="n">
+        <v>520</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Exit Multiple</t>
+          <t>Transaction Fees</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>%</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>On exit year EBITDA</t>
-        </is>
-      </c>
-      <c r="D30" s="33" t="n">
-        <v>7</v>
+          <t>Legal, advisory, financing</t>
+        </is>
+      </c>
+      <c r="D30" s="32" t="n">
+        <v>0.015</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
+          <t>Exit Multiple</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>On exit year EBITDA</t>
+        </is>
+      </c>
+      <c r="D31" s="33" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
           <t>Exit Year</t>
         </is>
       </c>
-      <c r="B31" s="6" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>Hold period</t>
         </is>
       </c>
-      <c r="D31" s="14" t="n">
+      <c r="D32" s="14" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="32"/>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
+    <row r="33"/>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>ASSET INPUTS</t>
         </is>
       </c>
-      <c r="B33" s="4" t="n"/>
-      <c r="C33" s="4" t="n"/>
-      <c r="D33" s="4" t="n"/>
-      <c r="E33" s="4" t="n"/>
-      <c r="F33" s="4" t="n"/>
-      <c r="G33" s="4" t="n"/>
-      <c r="H33" s="4" t="n"/>
-      <c r="I33" s="4" t="n"/>
-      <c r="J33" s="4" t="n"/>
-      <c r="K33" s="4" t="n"/>
-      <c r="L33" s="4" t="n"/>
-      <c r="M33" s="4" t="n"/>
-      <c r="N33" s="4" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>Capacity</t>
-        </is>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
-        <is>
-          <t>MW</t>
-        </is>
-      </c>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t>Nameplate rating</t>
-        </is>
-      </c>
-      <c r="D34" s="14" t="n">
-        <v>365</v>
-      </c>
+      <c r="B34" s="4" t="n"/>
+      <c r="C34" s="4" t="n"/>
+      <c r="D34" s="4" t="n"/>
+      <c r="E34" s="4" t="n"/>
+      <c r="F34" s="4" t="n"/>
+      <c r="G34" s="4" t="n"/>
+      <c r="H34" s="4" t="n"/>
+      <c r="I34" s="4" t="n"/>
+      <c r="J34" s="4" t="n"/>
+      <c r="K34" s="4" t="n"/>
+      <c r="L34" s="4" t="n"/>
+      <c r="M34" s="4" t="n"/>
+      <c r="N34" s="4" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>Heat Rate</t>
+          <t>Capacity</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>Btu/kWh</t>
+          <t>MW</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>Efficiency (lower = better)</t>
+          <t>Nameplate rating</t>
         </is>
       </c>
       <c r="D35" s="14" t="n">
-        <v>7000</v>
+        <v>365</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>Capacity Factor</t>
+          <t>Heat Rate</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>Btu/kWh</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>Annual utilization</t>
-        </is>
-      </c>
-      <c r="D36" s="32" t="n">
-        <v>0.55</v>
+          <t>Efficiency (lower = better)</t>
+        </is>
+      </c>
+      <c r="D36" s="14" t="n">
+        <v>7000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
+          <t>Capacity Factor</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>Annual utilization</t>
+        </is>
+      </c>
+      <c r="D37" s="32" t="n">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
           <t>Forced Outage Rate</t>
         </is>
       </c>
-      <c r="B37" s="6" t="inlineStr">
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="C37" s="6" t="inlineStr">
+      <c r="C38" s="6" t="inlineStr">
         <is>
           <t>Unplanned downtime</t>
         </is>
       </c>
-      <c r="D37" s="32" t="n">
+      <c r="D38" s="32" t="n">
         <v>0.05</v>
       </c>
     </row>
-    <row r="38"/>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
+    <row r="39"/>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
         <is>
           <t>PRICING INPUTS</t>
         </is>
       </c>
-      <c r="B39" s="4" t="n"/>
-      <c r="C39" s="4" t="n"/>
-      <c r="D39" s="4" t="n"/>
-      <c r="E39" s="4" t="n"/>
-      <c r="F39" s="4" t="n"/>
-      <c r="G39" s="4" t="n"/>
-      <c r="H39" s="4" t="n"/>
-      <c r="I39" s="4" t="n"/>
-      <c r="J39" s="4" t="n"/>
-      <c r="K39" s="4" t="n"/>
-      <c r="L39" s="4" t="n"/>
-      <c r="M39" s="4" t="n"/>
-      <c r="N39" s="4" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>Power Price Y1</t>
-        </is>
-      </c>
-      <c r="B40" s="6" t="inlineStr">
-        <is>
-          <t>$/MWh</t>
-        </is>
-      </c>
-      <c r="C40" s="6" t="inlineStr">
-        <is>
-          <t>Energy clearing price</t>
-        </is>
-      </c>
-      <c r="D40" s="11" t="n">
-        <v>48</v>
-      </c>
+      <c r="B40" s="4" t="n"/>
+      <c r="C40" s="4" t="n"/>
+      <c r="D40" s="4" t="n"/>
+      <c r="E40" s="4" t="n"/>
+      <c r="F40" s="4" t="n"/>
+      <c r="G40" s="4" t="n"/>
+      <c r="H40" s="4" t="n"/>
+      <c r="I40" s="4" t="n"/>
+      <c r="J40" s="4" t="n"/>
+      <c r="K40" s="4" t="n"/>
+      <c r="L40" s="4" t="n"/>
+      <c r="M40" s="4" t="n"/>
+      <c r="N40" s="4" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>Capacity Price Y1</t>
+          <t>Power Price Y1</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>$/kW-yr</t>
+          <t>$/MWh</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>ICAP/RPM auction result</t>
+          <t>Energy clearing price</t>
         </is>
       </c>
       <c r="D41" s="11" t="n">
-        <v>110</v>
+        <v>48</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>Gas Price Y1</t>
+          <t>Capacity Price Y1</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>$/mmBtu</t>
+          <t>$/kW-yr</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>Henry Hub + basis</t>
-        </is>
-      </c>
-      <c r="D42" s="15" t="n">
-        <v>3</v>
+          <t>ICAP/RPM auction result</t>
+        </is>
+      </c>
+      <c r="D42" s="11" t="n">
+        <v>110</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
+          <t>Gas Price Y1</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>$/mmBtu</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>Henry Hub + basis</t>
+        </is>
+      </c>
+      <c r="D43" s="15" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
           <t>Escalation</t>
         </is>
       </c>
-      <c r="B43" s="6" t="inlineStr">
+      <c r="B44" s="6" t="inlineStr">
         <is>
           <t>%/yr</t>
         </is>
       </c>
-      <c r="C43" s="6" t="inlineStr">
+      <c r="C44" s="6" t="inlineStr">
         <is>
           <t>Applied to all prices/costs</t>
         </is>
       </c>
-      <c r="D43" s="32" t="n">
+      <c r="D44" s="32" t="n">
         <v>0.025</v>
       </c>
     </row>
-    <row r="44"/>
-    <row r="45">
-      <c r="A45" s="3" t="inlineStr">
+    <row r="45"/>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
         <is>
           <t>COST INPUTS</t>
         </is>
       </c>
-      <c r="B45" s="4" t="n"/>
-      <c r="C45" s="4" t="n"/>
-      <c r="D45" s="4" t="n"/>
-      <c r="E45" s="4" t="n"/>
-      <c r="F45" s="4" t="n"/>
-      <c r="G45" s="4" t="n"/>
-      <c r="H45" s="4" t="n"/>
-      <c r="I45" s="4" t="n"/>
-      <c r="J45" s="4" t="n"/>
-      <c r="K45" s="4" t="n"/>
-      <c r="L45" s="4" t="n"/>
-      <c r="M45" s="4" t="n"/>
-      <c r="N45" s="4" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>VOM</t>
-        </is>
-      </c>
-      <c r="B46" s="6" t="inlineStr">
-        <is>
-          <t>$/MWh</t>
-        </is>
-      </c>
-      <c r="C46" s="6" t="inlineStr">
-        <is>
-          <t>Variable O&amp;M</t>
-        </is>
-      </c>
-      <c r="D46" s="15" t="n">
-        <v>3.5</v>
-      </c>
+      <c r="B46" s="4" t="n"/>
+      <c r="C46" s="4" t="n"/>
+      <c r="D46" s="4" t="n"/>
+      <c r="E46" s="4" t="n"/>
+      <c r="F46" s="4" t="n"/>
+      <c r="G46" s="4" t="n"/>
+      <c r="H46" s="4" t="n"/>
+      <c r="I46" s="4" t="n"/>
+      <c r="J46" s="4" t="n"/>
+      <c r="K46" s="4" t="n"/>
+      <c r="L46" s="4" t="n"/>
+      <c r="M46" s="4" t="n"/>
+      <c r="N46" s="4" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
+          <t>VOM</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>$/MWh</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>Variable O&amp;M</t>
+        </is>
+      </c>
+      <c r="D47" s="15" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
           <t>FOM</t>
         </is>
       </c>
-      <c r="B47" s="6" t="inlineStr">
+      <c r="B48" s="6" t="inlineStr">
         <is>
           <t>$/kW-yr</t>
         </is>
       </c>
-      <c r="C47" s="6" t="inlineStr">
+      <c r="C48" s="6" t="inlineStr">
         <is>
           <t>Fixed O&amp;M</t>
         </is>
       </c>
-      <c r="D47" s="15" t="n">
+      <c r="D48" s="15" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="48"/>
-    <row r="49">
-      <c r="A49" s="3" t="inlineStr">
+    <row r="49"/>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
         <is>
           <t>FINANCING INPUTS</t>
         </is>
       </c>
-      <c r="B49" s="4" t="n"/>
-      <c r="C49" s="4" t="n"/>
-      <c r="D49" s="4" t="n"/>
-      <c r="E49" s="4" t="n"/>
-      <c r="F49" s="4" t="n"/>
-      <c r="G49" s="4" t="n"/>
-      <c r="H49" s="4" t="n"/>
-      <c r="I49" s="4" t="n"/>
-      <c r="J49" s="4" t="n"/>
-      <c r="K49" s="4" t="n"/>
-      <c r="L49" s="4" t="n"/>
-      <c r="M49" s="4" t="n"/>
-      <c r="N49" s="4" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t>Leverage</t>
-        </is>
-      </c>
-      <c r="B50" s="6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C50" s="6" t="inlineStr">
-        <is>
-          <t>Debt / Entry EV</t>
-        </is>
-      </c>
-      <c r="D50" s="32" t="n">
-        <v>0.45</v>
-      </c>
+      <c r="B50" s="4" t="n"/>
+      <c r="C50" s="4" t="n"/>
+      <c r="D50" s="4" t="n"/>
+      <c r="E50" s="4" t="n"/>
+      <c r="F50" s="4" t="n"/>
+      <c r="G50" s="4" t="n"/>
+      <c r="H50" s="4" t="n"/>
+      <c r="I50" s="4" t="n"/>
+      <c r="J50" s="4" t="n"/>
+      <c r="K50" s="4" t="n"/>
+      <c r="L50" s="4" t="n"/>
+      <c r="M50" s="4" t="n"/>
+      <c r="N50" s="4" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>Interest Rate</t>
+          <t>Leverage</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
@@ -3981,138 +3968,138 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>All-in borrowing cost</t>
+          <t>Debt / Entry EV</t>
         </is>
       </c>
       <c r="D51" s="32" t="n">
-        <v>0.065</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>Debt Tenor</t>
+          <t>Interest Rate</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>years</t>
+          <t>%</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>Amortization period</t>
-        </is>
-      </c>
-      <c r="D52" s="14" t="n">
-        <v>7</v>
+          <t>All-in borrowing cost</t>
+        </is>
+      </c>
+      <c r="D52" s="32" t="n">
+        <v>0.065</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>DSRA Months</t>
+          <t>Debt Tenor</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>months</t>
+          <t>years</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>Debt service reserve</t>
+          <t>Amortization period</t>
         </is>
       </c>
       <c r="D53" s="14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>Cash Sweep %</t>
+          <t>DSRA Months</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>months</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>Mandatory excess CF prepay</t>
-        </is>
-      </c>
-      <c r="D54" s="32" t="n">
-        <v>0.75</v>
+          <t>Debt service reserve</t>
+        </is>
+      </c>
+      <c r="D54" s="14" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
+          <t>Cash Sweep %</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>Mandatory excess CF prepay</t>
+        </is>
+      </c>
+      <c r="D55" s="32" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
           <t>Lock-up DSCR</t>
         </is>
       </c>
-      <c r="B55" s="6" t="inlineStr">
+      <c r="B56" s="6" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="C55" s="6" t="inlineStr">
+      <c r="C56" s="6" t="inlineStr">
         <is>
           <t>Distribution threshold</t>
         </is>
       </c>
-      <c r="D55" s="33" t="n">
+      <c r="D56" s="33" t="n">
         <v>1.1</v>
       </c>
     </row>
-    <row r="56"/>
-    <row r="57">
-      <c r="A57" s="3" t="inlineStr">
+    <row r="57"/>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
         <is>
           <t>TAX INPUTS</t>
         </is>
       </c>
-      <c r="B57" s="4" t="n"/>
-      <c r="C57" s="4" t="n"/>
-      <c r="D57" s="4" t="n"/>
-      <c r="E57" s="4" t="n"/>
-      <c r="F57" s="4" t="n"/>
-      <c r="G57" s="4" t="n"/>
-      <c r="H57" s="4" t="n"/>
-      <c r="I57" s="4" t="n"/>
-      <c r="J57" s="4" t="n"/>
-      <c r="K57" s="4" t="n"/>
-      <c r="L57" s="4" t="n"/>
-      <c r="M57" s="4" t="n"/>
-      <c r="N57" s="4" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>Tax Rate</t>
-        </is>
-      </c>
-      <c r="B58" s="6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C58" s="6" t="inlineStr">
-        <is>
-          <t>Blended federal + state</t>
-        </is>
-      </c>
-      <c r="D58" s="32" t="n">
-        <v>0.25</v>
-      </c>
+      <c r="B58" s="4" t="n"/>
+      <c r="C58" s="4" t="n"/>
+      <c r="D58" s="4" t="n"/>
+      <c r="E58" s="4" t="n"/>
+      <c r="F58" s="4" t="n"/>
+      <c r="G58" s="4" t="n"/>
+      <c r="H58" s="4" t="n"/>
+      <c r="I58" s="4" t="n"/>
+      <c r="J58" s="4" t="n"/>
+      <c r="K58" s="4" t="n"/>
+      <c r="L58" s="4" t="n"/>
+      <c r="M58" s="4" t="n"/>
+      <c r="N58" s="4" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>Depreciable Basis</t>
+          <t>Tax Rate</t>
         </is>
       </c>
       <c r="B59" s="6" t="inlineStr">
@@ -4122,122 +4109,121 @@
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>% of EV for depreciation</t>
+          <t>Blended federal + state</t>
         </is>
       </c>
       <c r="D59" s="32" t="n">
-        <v>0.85</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
+          <t>Depreciable Basis</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>% of EV for depreciation</t>
+        </is>
+      </c>
+      <c r="D60" s="32" t="n">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
           <t>Depreciation Life</t>
         </is>
       </c>
-      <c r="B60" s="6" t="inlineStr">
+      <c r="B61" s="6" t="inlineStr">
         <is>
           <t>years</t>
         </is>
       </c>
-      <c r="C60" s="6" t="inlineStr">
+      <c r="C61" s="6" t="inlineStr">
         <is>
           <t>Straight-line</t>
         </is>
       </c>
-      <c r="D60" s="14" t="n">
+      <c r="D61" s="14" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="61"/>
     <row r="62"/>
-    <row r="63">
-      <c r="A63" s="3" t="inlineStr">
+    <row r="63"/>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
         <is>
           <t>CALCULATED ITEMS</t>
         </is>
       </c>
-      <c r="B63" s="4" t="n"/>
-      <c r="C63" s="4" t="n"/>
-      <c r="D63" s="4" t="n"/>
-      <c r="E63" s="4" t="n"/>
-      <c r="F63" s="4" t="n"/>
-      <c r="G63" s="4" t="n"/>
-      <c r="H63" s="4" t="n"/>
-      <c r="I63" s="4" t="n"/>
-      <c r="J63" s="4" t="n"/>
-      <c r="K63" s="4" t="n"/>
-      <c r="L63" s="4" t="n"/>
-      <c r="M63" s="4" t="n"/>
-      <c r="N63" s="4" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>UCAP (Unforced Capacity)</t>
-        </is>
-      </c>
-      <c r="B64" s="6" t="inlineStr">
-        <is>
-          <t>MW</t>
-        </is>
-      </c>
-      <c r="C64" s="6" t="inlineStr">
-        <is>
-          <t>Capacity × (1 - FOR)</t>
-        </is>
-      </c>
-      <c r="D64" s="16">
-        <f>$D$23*(1-$D$26)</f>
-        <v/>
-      </c>
+      <c r="B64" s="4" t="n"/>
+      <c r="C64" s="4" t="n"/>
+      <c r="D64" s="4" t="n"/>
+      <c r="E64" s="4" t="n"/>
+      <c r="F64" s="4" t="n"/>
+      <c r="G64" s="4" t="n"/>
+      <c r="H64" s="4" t="n"/>
+      <c r="I64" s="4" t="n"/>
+      <c r="J64" s="4" t="n"/>
+      <c r="K64" s="4" t="n"/>
+      <c r="L64" s="4" t="n"/>
+      <c r="M64" s="4" t="n"/>
+      <c r="N64" s="4" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>Annual Generation</t>
+          <t>UCAP (Unforced Capacity)</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>MWh</t>
+          <t>MW</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>Capacity × CF × 8,760</t>
-        </is>
-      </c>
-      <c r="D65" s="17">
-        <f>$D$23*$D$25*8760</f>
+          <t>Capacity × (1 - FOR)</t>
+        </is>
+      </c>
+      <c r="D65" s="16">
+        <f>$D$23*(1-$D$26)</f>
         <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>Debt Amount</t>
+          <t>Annual Generation</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>$mm</t>
+          <t>MWh</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>Entry EV × Leverage</t>
-        </is>
-      </c>
-      <c r="D66" s="18">
-        <f>$D$17*$D$39</f>
+          <t>Capacity × CF × 8,760</t>
+        </is>
+      </c>
+      <c r="D66" s="17">
+        <f>$D$23*$D$25*8760</f>
         <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>Annual Depreciation</t>
+          <t>Debt Amount</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
@@ -4247,123 +4233,84 @@
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>EV × Basis / Life</t>
+          <t>Entry EV × Leverage</t>
         </is>
       </c>
       <c r="D67" s="18">
-        <f>$D$17*$D$48/$D$49</f>
+        <f>$D$17*$D$39</f>
         <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
+          <t>Annual Depreciation</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>EV × Basis / Life</t>
+        </is>
+      </c>
+      <c r="D68" s="18">
+        <f>$D$17*$D$48/$D$49</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
           <t>Scheduled Principal</t>
         </is>
       </c>
-      <c r="B68" s="6" t="inlineStr">
+      <c r="B69" s="6" t="inlineStr">
         <is>
           <t>$mm/yr</t>
         </is>
       </c>
-      <c r="C68" s="6" t="inlineStr">
+      <c r="C69" s="6" t="inlineStr">
         <is>
           <t>Debt / Tenor</t>
         </is>
       </c>
-      <c r="D68" s="18">
-        <f>$D$55/$D$41</f>
-        <v/>
-      </c>
-    </row>
-    <row r="69"/>
+      <c r="D69" s="18" t="inlineStr"/>
+    </row>
     <row r="70"/>
-    <row r="71">
-      <c r="A71" s="3" t="inlineStr">
+    <row r="71"/>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
         <is>
           <t>OPERATING MODEL</t>
         </is>
       </c>
-      <c r="B71" s="4" t="n"/>
-      <c r="C71" s="4" t="n"/>
-      <c r="D71" s="4" t="n"/>
-      <c r="E71" s="4" t="n"/>
-      <c r="F71" s="4" t="n"/>
-      <c r="G71" s="4" t="n"/>
-      <c r="H71" s="4" t="n"/>
-      <c r="I71" s="4" t="n"/>
-      <c r="J71" s="4" t="n"/>
-      <c r="K71" s="4" t="n"/>
-      <c r="L71" s="4" t="n"/>
-      <c r="M71" s="4" t="n"/>
-      <c r="N71" s="4" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="5" t="inlineStr">
-        <is>
-          <t>Power Price</t>
-        </is>
-      </c>
-      <c r="B72" s="6" t="inlineStr">
-        <is>
-          <t>$/MWh</t>
-        </is>
-      </c>
-      <c r="C72" s="6" t="inlineStr">
-        <is>
-          <t>Escalated</t>
-        </is>
-      </c>
-      <c r="E72" s="18">
-        <f>$D$29*(1+$D$32)^(1-1)</f>
-        <v/>
-      </c>
-      <c r="F72" s="18">
-        <f>$D$29*(1+$D$32)^(2-1)</f>
-        <v/>
-      </c>
-      <c r="G72" s="18">
-        <f>$D$29*(1+$D$32)^(3-1)</f>
-        <v/>
-      </c>
-      <c r="H72" s="18">
-        <f>$D$29*(1+$D$32)^(4-1)</f>
-        <v/>
-      </c>
-      <c r="I72" s="18">
-        <f>$D$29*(1+$D$32)^(5-1)</f>
-        <v/>
-      </c>
-      <c r="J72" s="18">
-        <f>$D$29*(1+$D$32)^(6-1)</f>
-        <v/>
-      </c>
-      <c r="K72" s="18">
-        <f>$D$29*(1+$D$32)^(7-1)</f>
-        <v/>
-      </c>
-      <c r="L72" s="18">
-        <f>$D$29*(1+$D$32)^(8-1)</f>
-        <v/>
-      </c>
-      <c r="M72" s="18">
-        <f>$D$29*(1+$D$32)^(9-1)</f>
-        <v/>
-      </c>
-      <c r="N72" s="18">
-        <f>$D$29*(1+$D$32)^(10-1)</f>
-        <v/>
-      </c>
+      <c r="B72" s="4" t="n"/>
+      <c r="C72" s="4" t="n"/>
+      <c r="D72" s="4" t="n"/>
+      <c r="E72" s="4" t="n"/>
+      <c r="F72" s="4" t="n"/>
+      <c r="G72" s="4" t="n"/>
+      <c r="H72" s="4" t="n"/>
+      <c r="I72" s="4" t="n"/>
+      <c r="J72" s="4" t="n"/>
+      <c r="K72" s="4" t="n"/>
+      <c r="L72" s="4" t="n"/>
+      <c r="M72" s="4" t="n"/>
+      <c r="N72" s="4" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>Capacity Price</t>
+          <t>Power Price</t>
         </is>
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>$/kW-yr</t>
+          <t>$/MWh</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
@@ -4372,165 +4319,165 @@
         </is>
       </c>
       <c r="E73" s="18">
-        <f>$D$30*(1+$D$32)^(1-1)</f>
+        <f>$D$29*(1+$D$32)^(1-1)</f>
         <v/>
       </c>
       <c r="F73" s="18">
-        <f>$D$30*(1+$D$32)^(2-1)</f>
+        <f>$D$29*(1+$D$32)^(2-1)</f>
         <v/>
       </c>
       <c r="G73" s="18">
-        <f>$D$30*(1+$D$32)^(3-1)</f>
+        <f>$D$29*(1+$D$32)^(3-1)</f>
         <v/>
       </c>
       <c r="H73" s="18">
-        <f>$D$30*(1+$D$32)^(4-1)</f>
+        <f>$D$29*(1+$D$32)^(4-1)</f>
         <v/>
       </c>
       <c r="I73" s="18">
-        <f>$D$30*(1+$D$32)^(5-1)</f>
+        <f>$D$29*(1+$D$32)^(5-1)</f>
         <v/>
       </c>
       <c r="J73" s="18">
-        <f>$D$30*(1+$D$32)^(6-1)</f>
+        <f>$D$29*(1+$D$32)^(6-1)</f>
         <v/>
       </c>
       <c r="K73" s="18">
-        <f>$D$30*(1+$D$32)^(7-1)</f>
+        <f>$D$29*(1+$D$32)^(7-1)</f>
         <v/>
       </c>
       <c r="L73" s="18">
-        <f>$D$30*(1+$D$32)^(8-1)</f>
+        <f>$D$29*(1+$D$32)^(8-1)</f>
         <v/>
       </c>
       <c r="M73" s="18">
-        <f>$D$30*(1+$D$32)^(9-1)</f>
+        <f>$D$29*(1+$D$32)^(9-1)</f>
         <v/>
       </c>
       <c r="N73" s="18">
-        <f>$D$30*(1+$D$32)^(10-1)</f>
+        <f>$D$29*(1+$D$32)^(10-1)</f>
         <v/>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
+          <t>Capacity Price</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>$/kW-yr</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>Escalated</t>
+        </is>
+      </c>
+      <c r="E74" s="18">
+        <f>$D$30*(1+$D$32)^(1-1)</f>
+        <v/>
+      </c>
+      <c r="F74" s="18">
+        <f>$D$30*(1+$D$32)^(2-1)</f>
+        <v/>
+      </c>
+      <c r="G74" s="18">
+        <f>$D$30*(1+$D$32)^(3-1)</f>
+        <v/>
+      </c>
+      <c r="H74" s="18">
+        <f>$D$30*(1+$D$32)^(4-1)</f>
+        <v/>
+      </c>
+      <c r="I74" s="18">
+        <f>$D$30*(1+$D$32)^(5-1)</f>
+        <v/>
+      </c>
+      <c r="J74" s="18">
+        <f>$D$30*(1+$D$32)^(6-1)</f>
+        <v/>
+      </c>
+      <c r="K74" s="18">
+        <f>$D$30*(1+$D$32)^(7-1)</f>
+        <v/>
+      </c>
+      <c r="L74" s="18">
+        <f>$D$30*(1+$D$32)^(8-1)</f>
+        <v/>
+      </c>
+      <c r="M74" s="18">
+        <f>$D$30*(1+$D$32)^(9-1)</f>
+        <v/>
+      </c>
+      <c r="N74" s="18">
+        <f>$D$30*(1+$D$32)^(10-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
           <t>Gas Price</t>
         </is>
       </c>
-      <c r="B74" s="6" t="inlineStr">
+      <c r="B75" s="6" t="inlineStr">
         <is>
           <t>$/mmBtu</t>
         </is>
       </c>
-      <c r="C74" s="6" t="inlineStr">
+      <c r="C75" s="6" t="inlineStr">
         <is>
           <t>Escalated</t>
         </is>
       </c>
-      <c r="E74" s="19">
+      <c r="E75" s="19">
         <f>$D$31*(1+$D$32)^(1-1)</f>
         <v/>
       </c>
-      <c r="F74" s="19">
+      <c r="F75" s="19">
         <f>$D$31*(1+$D$32)^(2-1)</f>
         <v/>
       </c>
-      <c r="G74" s="19">
+      <c r="G75" s="19">
         <f>$D$31*(1+$D$32)^(3-1)</f>
         <v/>
       </c>
-      <c r="H74" s="19">
+      <c r="H75" s="19">
         <f>$D$31*(1+$D$32)^(4-1)</f>
         <v/>
       </c>
-      <c r="I74" s="19">
+      <c r="I75" s="19">
         <f>$D$31*(1+$D$32)^(5-1)</f>
         <v/>
       </c>
-      <c r="J74" s="19">
+      <c r="J75" s="19">
         <f>$D$31*(1+$D$32)^(6-1)</f>
         <v/>
       </c>
-      <c r="K74" s="19">
+      <c r="K75" s="19">
         <f>$D$31*(1+$D$32)^(7-1)</f>
         <v/>
       </c>
-      <c r="L74" s="19">
+      <c r="L75" s="19">
         <f>$D$31*(1+$D$32)^(8-1)</f>
         <v/>
       </c>
-      <c r="M74" s="19">
+      <c r="M75" s="19">
         <f>$D$31*(1+$D$32)^(9-1)</f>
         <v/>
       </c>
-      <c r="N74" s="19">
+      <c r="N75" s="19">
         <f>$D$31*(1+$D$32)^(10-1)</f>
         <v/>
       </c>
     </row>
-    <row r="75"/>
-    <row r="76">
-      <c r="A76" s="5" t="inlineStr">
-        <is>
-          <t>Energy Revenue</t>
-        </is>
-      </c>
-      <c r="B76" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C76" s="6" t="inlineStr">
-        <is>
-          <t>Generation × Power Price / 1M</t>
-        </is>
-      </c>
-      <c r="E76" s="18">
-        <f>$D$54*E61/1000000</f>
-        <v/>
-      </c>
-      <c r="F76" s="18">
-        <f>$D$54*F61/1000000</f>
-        <v/>
-      </c>
-      <c r="G76" s="18">
-        <f>$D$54*G61/1000000</f>
-        <v/>
-      </c>
-      <c r="H76" s="18">
-        <f>$D$54*H61/1000000</f>
-        <v/>
-      </c>
-      <c r="I76" s="18">
-        <f>$D$54*I61/1000000</f>
-        <v/>
-      </c>
-      <c r="J76" s="18">
-        <f>$D$54*J61/1000000</f>
-        <v/>
-      </c>
-      <c r="K76" s="18">
-        <f>$D$54*K61/1000000</f>
-        <v/>
-      </c>
-      <c r="L76" s="18">
-        <f>$D$54*L61/1000000</f>
-        <v/>
-      </c>
-      <c r="M76" s="18">
-        <f>$D$54*M61/1000000</f>
-        <v/>
-      </c>
-      <c r="N76" s="18">
-        <f>$D$54*N61/1000000</f>
-        <v/>
-      </c>
-    </row>
+    <row r="76"/>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>Capacity Revenue</t>
+          <t>Energy Revenue</t>
         </is>
       </c>
       <c r="B77" s="6" t="inlineStr">
@@ -4540,173 +4487,110 @@
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>UCAP × Cap Price × 1000 / 1M</t>
-        </is>
-      </c>
-      <c r="E77" s="18">
-        <f>$D$53*E62*1000/1000000</f>
-        <v/>
-      </c>
-      <c r="F77" s="18">
-        <f>$D$53*F62*1000/1000000</f>
-        <v/>
-      </c>
-      <c r="G77" s="18">
-        <f>$D$53*G62*1000/1000000</f>
-        <v/>
-      </c>
-      <c r="H77" s="18">
-        <f>$D$53*H62*1000/1000000</f>
-        <v/>
-      </c>
-      <c r="I77" s="18">
-        <f>$D$53*I62*1000/1000000</f>
-        <v/>
-      </c>
-      <c r="J77" s="18">
-        <f>$D$53*J62*1000/1000000</f>
-        <v/>
-      </c>
-      <c r="K77" s="18">
-        <f>$D$53*K62*1000/1000000</f>
-        <v/>
-      </c>
-      <c r="L77" s="18">
-        <f>$D$53*L62*1000/1000000</f>
-        <v/>
-      </c>
-      <c r="M77" s="18">
-        <f>$D$53*M62*1000/1000000</f>
-        <v/>
-      </c>
-      <c r="N77" s="18">
-        <f>$D$53*N62*1000/1000000</f>
-        <v/>
-      </c>
+          <t>Generation × Power Price / 1M</t>
+        </is>
+      </c>
+      <c r="E77" s="18" t="inlineStr"/>
+      <c r="F77" s="18" t="inlineStr"/>
+      <c r="G77" s="18" t="inlineStr"/>
+      <c r="H77" s="18" t="inlineStr"/>
+      <c r="I77" s="18" t="inlineStr"/>
+      <c r="J77" s="18" t="inlineStr"/>
+      <c r="K77" s="18" t="inlineStr"/>
+      <c r="L77" s="18" t="inlineStr"/>
+      <c r="M77" s="18" t="inlineStr"/>
+      <c r="N77" s="18" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
+          <t>Capacity Revenue</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>UCAP × Cap Price × 1000 / 1M</t>
+        </is>
+      </c>
+      <c r="E78" s="18" t="inlineStr"/>
+      <c r="F78" s="18" t="inlineStr"/>
+      <c r="G78" s="18" t="inlineStr"/>
+      <c r="H78" s="18" t="inlineStr"/>
+      <c r="I78" s="18" t="inlineStr"/>
+      <c r="J78" s="18" t="inlineStr"/>
+      <c r="K78" s="18" t="inlineStr"/>
+      <c r="L78" s="18" t="inlineStr"/>
+      <c r="M78" s="18" t="inlineStr"/>
+      <c r="N78" s="18" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
           <t>Total Revenue</t>
         </is>
       </c>
-      <c r="B78" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C78" s="6" t="inlineStr"/>
-      <c r="E78" s="20">
-        <f>E65+E66</f>
-        <v/>
-      </c>
-      <c r="F78" s="20">
-        <f>F65+F66</f>
-        <v/>
-      </c>
-      <c r="G78" s="20">
-        <f>G65+G66</f>
-        <v/>
-      </c>
-      <c r="H78" s="20">
-        <f>H65+H66</f>
-        <v/>
-      </c>
-      <c r="I78" s="20">
-        <f>I65+I66</f>
-        <v/>
-      </c>
-      <c r="J78" s="20">
-        <f>J65+J66</f>
-        <v/>
-      </c>
-      <c r="K78" s="20">
-        <f>K65+K66</f>
-        <v/>
-      </c>
-      <c r="L78" s="20">
-        <f>L65+L66</f>
-        <v/>
-      </c>
-      <c r="M78" s="20">
-        <f>M65+M66</f>
-        <v/>
-      </c>
-      <c r="N78" s="20">
-        <f>N65+N66</f>
-        <v/>
-      </c>
-    </row>
-    <row r="79"/>
-    <row r="80">
-      <c r="A80" s="5" t="inlineStr">
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr"/>
+      <c r="E79" s="20" t="inlineStr"/>
+      <c r="F79" s="20" t="inlineStr"/>
+      <c r="G79" s="20" t="inlineStr"/>
+      <c r="H79" s="20" t="inlineStr"/>
+      <c r="I79" s="20" t="inlineStr"/>
+      <c r="J79" s="20" t="inlineStr"/>
+      <c r="K79" s="20" t="inlineStr"/>
+      <c r="L79" s="20" t="inlineStr"/>
+      <c r="M79" s="20" t="inlineStr"/>
+      <c r="N79" s="20" t="inlineStr"/>
+    </row>
+    <row r="80"/>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
         <is>
           <t>Fuel Cost</t>
         </is>
       </c>
-      <c r="B80" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C80" s="6" t="inlineStr">
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
         <is>
           <t>Gen × HR × Gas / 1B</t>
         </is>
       </c>
-      <c r="E80" s="18">
-        <f>$D$54*$D$24*E63/1E9</f>
-        <v/>
-      </c>
-      <c r="F80" s="18">
-        <f>$D$54*$D$24*F63/1E9</f>
-        <v/>
-      </c>
-      <c r="G80" s="18">
-        <f>$D$54*$D$24*G63/1E9</f>
-        <v/>
-      </c>
-      <c r="H80" s="18">
-        <f>$D$54*$D$24*H63/1E9</f>
-        <v/>
-      </c>
-      <c r="I80" s="18">
-        <f>$D$54*$D$24*I63/1E9</f>
-        <v/>
-      </c>
-      <c r="J80" s="18">
-        <f>$D$54*$D$24*J63/1E9</f>
-        <v/>
-      </c>
-      <c r="K80" s="18">
-        <f>$D$54*$D$24*K63/1E9</f>
-        <v/>
-      </c>
-      <c r="L80" s="18">
-        <f>$D$54*$D$24*L63/1E9</f>
-        <v/>
-      </c>
-      <c r="M80" s="18">
-        <f>$D$54*$D$24*M63/1E9</f>
-        <v/>
-      </c>
-      <c r="N80" s="18">
-        <f>$D$54*$D$24*N63/1E9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="34" t="inlineStr">
+      <c r="E81" s="18" t="inlineStr"/>
+      <c r="F81" s="18" t="inlineStr"/>
+      <c r="G81" s="18" t="inlineStr"/>
+      <c r="H81" s="18" t="inlineStr"/>
+      <c r="I81" s="18" t="inlineStr"/>
+      <c r="J81" s="18" t="inlineStr"/>
+      <c r="K81" s="18" t="inlineStr"/>
+      <c r="L81" s="18" t="inlineStr"/>
+      <c r="M81" s="18" t="inlineStr"/>
+      <c r="N81" s="18" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="34" t="inlineStr">
         <is>
           <t>Spark Spread</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B82" t="inlineStr">
         <is>
           <t>$/MWh</t>
         </is>
       </c>
-      <c r="C81" s="55" t="inlineStr">
+      <c r="C82" s="55" t="inlineStr">
         <is>
           <t>[WHAT] Spark Spread = Power Price - (Plant HR × Gas / 1000)
 [WHY] Gross margin per MWh after fuel. Core driver of thermal profitability.
@@ -4724,108 +4608,51 @@
 [UNITS] $/MWh - (Btu/kWh × $/MMBtu / 1000) = $/MWh ✓</t>
         </is>
       </c>
-      <c r="E81" s="56">
+      <c r="E82" s="56">
         <f>E71-($D$34/1000)*E73</f>
         <v/>
       </c>
-      <c r="F81" s="56">
+      <c r="F82" s="56">
         <f>F71-($D$34/1000)*F73</f>
         <v/>
       </c>
-      <c r="G81" s="56">
+      <c r="G82" s="56">
         <f>G71-($D$34/1000)*G73</f>
         <v/>
       </c>
-      <c r="H81" s="56">
+      <c r="H82" s="56">
         <f>H71-($D$34/1000)*H73</f>
         <v/>
       </c>
-      <c r="I81" s="56">
+      <c r="I82" s="56">
         <f>I71-($D$34/1000)*I73</f>
         <v/>
       </c>
-      <c r="J81" s="56">
+      <c r="J82" s="56">
         <f>J71-($D$34/1000)*J73</f>
         <v/>
       </c>
-      <c r="K81" s="56">
+      <c r="K82" s="56">
         <f>K71-($D$34/1000)*K73</f>
         <v/>
       </c>
-      <c r="L81" s="56">
+      <c r="L82" s="56">
         <f>L71-($D$34/1000)*L73</f>
         <v/>
       </c>
-      <c r="M81" s="56">
+      <c r="M82" s="56">
         <f>M71-($D$34/1000)*M73</f>
         <v/>
       </c>
-      <c r="N81" s="56">
+      <c r="N82" s="56">
         <f>N71-($D$34/1000)*N73</f>
-        <v/>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="5" t="inlineStr">
-        <is>
-          <t>VOM</t>
-        </is>
-      </c>
-      <c r="B82" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C82" s="6" t="inlineStr">
-        <is>
-          <t>Generation × VOM rate / 1M</t>
-        </is>
-      </c>
-      <c r="E82" s="18">
-        <f>$D$54*$D$35/1000000</f>
-        <v/>
-      </c>
-      <c r="F82" s="18">
-        <f>$D$54*$D$35/1000000</f>
-        <v/>
-      </c>
-      <c r="G82" s="18">
-        <f>$D$54*$D$35/1000000</f>
-        <v/>
-      </c>
-      <c r="H82" s="18">
-        <f>$D$54*$D$35/1000000</f>
-        <v/>
-      </c>
-      <c r="I82" s="18">
-        <f>$D$54*$D$35/1000000</f>
-        <v/>
-      </c>
-      <c r="J82" s="18">
-        <f>$D$54*$D$35/1000000</f>
-        <v/>
-      </c>
-      <c r="K82" s="18">
-        <f>$D$54*$D$35/1000000</f>
-        <v/>
-      </c>
-      <c r="L82" s="18">
-        <f>$D$54*$D$35/1000000</f>
-        <v/>
-      </c>
-      <c r="M82" s="18">
-        <f>$D$54*$D$35/1000000</f>
-        <v/>
-      </c>
-      <c r="N82" s="18">
-        <f>$D$54*$D$35/1000000</f>
         <v/>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>FOM</t>
+          <t>VOM</t>
         </is>
       </c>
       <c r="B83" s="6" t="inlineStr">
@@ -4835,240 +4662,210 @@
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>Capacity × FOM × esc × 1000 / 1M</t>
+          <t>Generation × VOM rate / 1M</t>
         </is>
       </c>
       <c r="E83" s="18">
-        <f>$D$23*$D$36*(1+$D$32)^(1-1)*1000/1000000</f>
+        <f>$D$54*$D$35/1000000</f>
         <v/>
       </c>
       <c r="F83" s="18">
-        <f>$D$23*$D$36*(1+$D$32)^(2-1)*1000/1000000</f>
+        <f>$D$54*$D$35/1000000</f>
         <v/>
       </c>
       <c r="G83" s="18">
-        <f>$D$23*$D$36*(1+$D$32)^(3-1)*1000/1000000</f>
+        <f>$D$54*$D$35/1000000</f>
         <v/>
       </c>
       <c r="H83" s="18">
-        <f>$D$23*$D$36*(1+$D$32)^(4-1)*1000/1000000</f>
+        <f>$D$54*$D$35/1000000</f>
         <v/>
       </c>
       <c r="I83" s="18">
-        <f>$D$23*$D$36*(1+$D$32)^(5-1)*1000/1000000</f>
+        <f>$D$54*$D$35/1000000</f>
         <v/>
       </c>
       <c r="J83" s="18">
-        <f>$D$23*$D$36*(1+$D$32)^(6-1)*1000/1000000</f>
+        <f>$D$54*$D$35/1000000</f>
         <v/>
       </c>
       <c r="K83" s="18">
-        <f>$D$23*$D$36*(1+$D$32)^(7-1)*1000/1000000</f>
+        <f>$D$54*$D$35/1000000</f>
         <v/>
       </c>
       <c r="L83" s="18">
-        <f>$D$23*$D$36*(1+$D$32)^(8-1)*1000/1000000</f>
+        <f>$D$54*$D$35/1000000</f>
         <v/>
       </c>
       <c r="M83" s="18">
-        <f>$D$23*$D$36*(1+$D$32)^(9-1)*1000/1000000</f>
+        <f>$D$54*$D$35/1000000</f>
         <v/>
       </c>
       <c r="N83" s="18">
-        <f>$D$23*$D$36*(1+$D$32)^(10-1)*1000/1000000</f>
+        <f>$D$54*$D$35/1000000</f>
         <v/>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
+          <t>FOM</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>Capacity × FOM × esc × 1000 / 1M</t>
+        </is>
+      </c>
+      <c r="E84" s="18">
+        <f>$D$23*$D$36*(1+$D$32)^(1-1)*1000/1000000</f>
+        <v/>
+      </c>
+      <c r="F84" s="18">
+        <f>$D$23*$D$36*(1+$D$32)^(2-1)*1000/1000000</f>
+        <v/>
+      </c>
+      <c r="G84" s="18">
+        <f>$D$23*$D$36*(1+$D$32)^(3-1)*1000/1000000</f>
+        <v/>
+      </c>
+      <c r="H84" s="18">
+        <f>$D$23*$D$36*(1+$D$32)^(4-1)*1000/1000000</f>
+        <v/>
+      </c>
+      <c r="I84" s="18">
+        <f>$D$23*$D$36*(1+$D$32)^(5-1)*1000/1000000</f>
+        <v/>
+      </c>
+      <c r="J84" s="18">
+        <f>$D$23*$D$36*(1+$D$32)^(6-1)*1000/1000000</f>
+        <v/>
+      </c>
+      <c r="K84" s="18">
+        <f>$D$23*$D$36*(1+$D$32)^(7-1)*1000/1000000</f>
+        <v/>
+      </c>
+      <c r="L84" s="18">
+        <f>$D$23*$D$36*(1+$D$32)^(8-1)*1000/1000000</f>
+        <v/>
+      </c>
+      <c r="M84" s="18">
+        <f>$D$23*$D$36*(1+$D$32)^(9-1)*1000/1000000</f>
+        <v/>
+      </c>
+      <c r="N84" s="18">
+        <f>$D$23*$D$36*(1+$D$32)^(10-1)*1000/1000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
           <t>Total Operating Costs</t>
         </is>
       </c>
-      <c r="B84" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C84" s="6" t="inlineStr"/>
-      <c r="E84" s="18">
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="inlineStr"/>
+      <c r="E85" s="18">
         <f>E69+E70+E71</f>
         <v/>
       </c>
-      <c r="F84" s="18">
+      <c r="F85" s="18">
         <f>F69+F70+F71</f>
         <v/>
       </c>
-      <c r="G84" s="18">
+      <c r="G85" s="18">
         <f>G69+G70+G71</f>
         <v/>
       </c>
-      <c r="H84" s="18">
+      <c r="H85" s="18">
         <f>H69+H70+H71</f>
         <v/>
       </c>
-      <c r="I84" s="18">
+      <c r="I85" s="18">
         <f>I69+I70+I71</f>
         <v/>
       </c>
-      <c r="J84" s="18">
+      <c r="J85" s="18">
         <f>J69+J70+J71</f>
         <v/>
       </c>
-      <c r="K84" s="18">
+      <c r="K85" s="18">
         <f>K69+K70+K71</f>
         <v/>
       </c>
-      <c r="L84" s="18">
+      <c r="L85" s="18">
         <f>L69+L70+L71</f>
         <v/>
       </c>
-      <c r="M84" s="18">
+      <c r="M85" s="18">
         <f>M69+M70+M71</f>
         <v/>
       </c>
-      <c r="N84" s="18">
+      <c r="N85" s="18">
         <f>N69+N70+N71</f>
         <v/>
       </c>
     </row>
-    <row r="85"/>
-    <row r="86">
-      <c r="A86" s="5" t="inlineStr">
+    <row r="86"/>
+    <row r="87">
+      <c r="A87" s="5" t="inlineStr">
         <is>
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B86" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C86" s="6" t="inlineStr"/>
-      <c r="E86" s="7">
-        <f>E67-E72</f>
-        <v/>
-      </c>
-      <c r="F86" s="7">
-        <f>F67-F72</f>
-        <v/>
-      </c>
-      <c r="G86" s="7">
-        <f>G67-G72</f>
-        <v/>
-      </c>
-      <c r="H86" s="7">
-        <f>H67-H72</f>
-        <v/>
-      </c>
-      <c r="I86" s="7">
-        <f>I67-I72</f>
-        <v/>
-      </c>
-      <c r="J86" s="7">
-        <f>J67-J72</f>
-        <v/>
-      </c>
-      <c r="K86" s="7">
-        <f>K67-K72</f>
-        <v/>
-      </c>
-      <c r="L86" s="7">
-        <f>L67-L72</f>
-        <v/>
-      </c>
-      <c r="M86" s="7">
-        <f>M67-M72</f>
-        <v/>
-      </c>
-      <c r="N86" s="7">
-        <f>N67-N72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="87"/>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr"/>
+      <c r="E87" s="7" t="inlineStr"/>
+      <c r="F87" s="7" t="inlineStr"/>
+      <c r="G87" s="7" t="inlineStr"/>
+      <c r="H87" s="7" t="inlineStr"/>
+      <c r="I87" s="7" t="inlineStr"/>
+      <c r="J87" s="7" t="inlineStr"/>
+      <c r="K87" s="7" t="inlineStr"/>
+      <c r="L87" s="7" t="inlineStr"/>
+      <c r="M87" s="7" t="inlineStr"/>
+      <c r="N87" s="7" t="inlineStr"/>
+    </row>
     <row r="88"/>
-    <row r="89">
-      <c r="A89" s="3" t="inlineStr">
+    <row r="89"/>
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
         <is>
           <t>CASH FLOW</t>
         </is>
       </c>
-      <c r="B89" s="4" t="n"/>
-      <c r="C89" s="4" t="n"/>
-      <c r="D89" s="4" t="n"/>
-      <c r="E89" s="4" t="n"/>
-      <c r="F89" s="4" t="n"/>
-      <c r="G89" s="4" t="n"/>
-      <c r="H89" s="4" t="n"/>
-      <c r="I89" s="4" t="n"/>
-      <c r="J89" s="4" t="n"/>
-      <c r="K89" s="4" t="n"/>
-      <c r="L89" s="4" t="n"/>
-      <c r="M89" s="4" t="n"/>
-      <c r="N89" s="4" t="n"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="5" t="inlineStr">
-        <is>
-          <t>EBIT</t>
-        </is>
-      </c>
-      <c r="B90" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C90" s="6" t="inlineStr">
-        <is>
-          <t>EBITDA - Depreciation</t>
-        </is>
-      </c>
-      <c r="E90" s="18">
-        <f>E74-$D$56</f>
-        <v/>
-      </c>
-      <c r="F90" s="18">
-        <f>F74-$D$56</f>
-        <v/>
-      </c>
-      <c r="G90" s="18">
-        <f>G74-$D$56</f>
-        <v/>
-      </c>
-      <c r="H90" s="18">
-        <f>H74-$D$56</f>
-        <v/>
-      </c>
-      <c r="I90" s="18">
-        <f>I74-$D$56</f>
-        <v/>
-      </c>
-      <c r="J90" s="18">
-        <f>J74-$D$56</f>
-        <v/>
-      </c>
-      <c r="K90" s="18">
-        <f>K74-$D$56</f>
-        <v/>
-      </c>
-      <c r="L90" s="18">
-        <f>L74-$D$56</f>
-        <v/>
-      </c>
-      <c r="M90" s="18">
-        <f>M74-$D$56</f>
-        <v/>
-      </c>
-      <c r="N90" s="18">
-        <f>N74-$D$56</f>
-        <v/>
-      </c>
+      <c r="B90" s="4" t="n"/>
+      <c r="C90" s="4" t="n"/>
+      <c r="D90" s="4" t="n"/>
+      <c r="E90" s="4" t="n"/>
+      <c r="F90" s="4" t="n"/>
+      <c r="G90" s="4" t="n"/>
+      <c r="H90" s="4" t="n"/>
+      <c r="I90" s="4" t="n"/>
+      <c r="J90" s="4" t="n"/>
+      <c r="K90" s="4" t="n"/>
+      <c r="L90" s="4" t="n"/>
+      <c r="M90" s="4" t="n"/>
+      <c r="N90" s="4" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>Taxes</t>
+          <t>EBIT</t>
         </is>
       </c>
       <c r="B91" s="6" t="inlineStr">
@@ -5078,186 +4875,100 @@
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>MAX(0, EBIT) × Tax Rate</t>
-        </is>
-      </c>
-      <c r="E91" s="18">
-        <f>MAX(0,E78)*$D$47</f>
-        <v/>
-      </c>
-      <c r="F91" s="18">
-        <f>MAX(0,F78)*$D$47</f>
-        <v/>
-      </c>
-      <c r="G91" s="18">
-        <f>MAX(0,G78)*$D$47</f>
-        <v/>
-      </c>
-      <c r="H91" s="18">
-        <f>MAX(0,H78)*$D$47</f>
-        <v/>
-      </c>
-      <c r="I91" s="18">
-        <f>MAX(0,I78)*$D$47</f>
-        <v/>
-      </c>
-      <c r="J91" s="18">
-        <f>MAX(0,J78)*$D$47</f>
-        <v/>
-      </c>
-      <c r="K91" s="18">
-        <f>MAX(0,K78)*$D$47</f>
-        <v/>
-      </c>
-      <c r="L91" s="18">
-        <f>MAX(0,L78)*$D$47</f>
-        <v/>
-      </c>
-      <c r="M91" s="18">
-        <f>MAX(0,M78)*$D$47</f>
-        <v/>
-      </c>
-      <c r="N91" s="18">
-        <f>MAX(0,N78)*$D$47</f>
-        <v/>
-      </c>
+          <t>EBITDA - Depreciation</t>
+        </is>
+      </c>
+      <c r="E91" s="18" t="inlineStr"/>
+      <c r="F91" s="18" t="inlineStr"/>
+      <c r="G91" s="18" t="inlineStr"/>
+      <c r="H91" s="18" t="inlineStr"/>
+      <c r="I91" s="18" t="inlineStr"/>
+      <c r="J91" s="18" t="inlineStr"/>
+      <c r="K91" s="18" t="inlineStr"/>
+      <c r="L91" s="18" t="inlineStr"/>
+      <c r="M91" s="18" t="inlineStr"/>
+      <c r="N91" s="18" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
         <is>
+          <t>Taxes</t>
+        </is>
+      </c>
+      <c r="B92" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C92" s="6" t="inlineStr">
+        <is>
+          <t>MAX(0, EBIT) × Tax Rate</t>
+        </is>
+      </c>
+      <c r="E92" s="18" t="inlineStr"/>
+      <c r="F92" s="18" t="inlineStr"/>
+      <c r="G92" s="18" t="inlineStr"/>
+      <c r="H92" s="18" t="inlineStr"/>
+      <c r="I92" s="18" t="inlineStr"/>
+      <c r="J92" s="18" t="inlineStr"/>
+      <c r="K92" s="18" t="inlineStr"/>
+      <c r="L92" s="18" t="inlineStr"/>
+      <c r="M92" s="18" t="inlineStr"/>
+      <c r="N92" s="18" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
           <t>CFADS</t>
         </is>
       </c>
-      <c r="B92" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C92" s="6" t="inlineStr">
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="inlineStr">
         <is>
           <t>EBITDA - Taxes</t>
         </is>
       </c>
-      <c r="E92" s="7">
-        <f>E74-E79</f>
-        <v/>
-      </c>
-      <c r="F92" s="7">
-        <f>F74-F79</f>
-        <v/>
-      </c>
-      <c r="G92" s="7">
-        <f>G74-G79</f>
-        <v/>
-      </c>
-      <c r="H92" s="7">
-        <f>H74-H79</f>
-        <v/>
-      </c>
-      <c r="I92" s="7">
-        <f>I74-I79</f>
-        <v/>
-      </c>
-      <c r="J92" s="7">
-        <f>J74-J79</f>
-        <v/>
-      </c>
-      <c r="K92" s="7">
-        <f>K74-K79</f>
-        <v/>
-      </c>
-      <c r="L92" s="7">
-        <f>L74-L79</f>
-        <v/>
-      </c>
-      <c r="M92" s="7">
-        <f>M74-M79</f>
-        <v/>
-      </c>
-      <c r="N92" s="7">
-        <f>N74-N79</f>
-        <v/>
-      </c>
-    </row>
-    <row r="93"/>
+      <c r="E93" s="7" t="inlineStr"/>
+      <c r="F93" s="7" t="inlineStr"/>
+      <c r="G93" s="7" t="inlineStr"/>
+      <c r="H93" s="7" t="inlineStr"/>
+      <c r="I93" s="7" t="inlineStr"/>
+      <c r="J93" s="7" t="inlineStr"/>
+      <c r="K93" s="7" t="inlineStr"/>
+      <c r="L93" s="7" t="inlineStr"/>
+      <c r="M93" s="7" t="inlineStr"/>
+      <c r="N93" s="7" t="inlineStr"/>
+    </row>
     <row r="94"/>
-    <row r="95">
-      <c r="A95" s="3" t="inlineStr">
+    <row r="95"/>
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
         <is>
           <t>DEBT SCHEDULE (75% Cash Sweep)</t>
         </is>
       </c>
-      <c r="B95" s="4" t="n"/>
-      <c r="C95" s="4" t="n"/>
-      <c r="D95" s="4" t="n"/>
-      <c r="E95" s="4" t="n"/>
-      <c r="F95" s="4" t="n"/>
-      <c r="G95" s="4" t="n"/>
-      <c r="H95" s="4" t="n"/>
-      <c r="I95" s="4" t="n"/>
-      <c r="J95" s="4" t="n"/>
-      <c r="K95" s="4" t="n"/>
-      <c r="L95" s="4" t="n"/>
-      <c r="M95" s="4" t="n"/>
-      <c r="N95" s="4" t="n"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="5" t="inlineStr">
-        <is>
-          <t>Beginning Balance</t>
-        </is>
-      </c>
-      <c r="B96" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C96" s="6" t="inlineStr"/>
-      <c r="E96" s="18">
-        <f>$D$55</f>
-        <v/>
-      </c>
-      <c r="F96" s="18">
-        <f>E91</f>
-        <v/>
-      </c>
-      <c r="G96" s="18">
-        <f>F91</f>
-        <v/>
-      </c>
-      <c r="H96" s="18">
-        <f>G91</f>
-        <v/>
-      </c>
-      <c r="I96" s="18">
-        <f>H91</f>
-        <v/>
-      </c>
-      <c r="J96" s="18">
-        <f>I91</f>
-        <v/>
-      </c>
-      <c r="K96" s="18">
-        <f>J91</f>
-        <v/>
-      </c>
-      <c r="L96" s="18">
-        <f>K91</f>
-        <v/>
-      </c>
-      <c r="M96" s="18">
-        <f>L91</f>
-        <v/>
-      </c>
-      <c r="N96" s="18">
-        <f>M91</f>
-        <v/>
-      </c>
+      <c r="B96" s="4" t="n"/>
+      <c r="C96" s="4" t="n"/>
+      <c r="D96" s="4" t="n"/>
+      <c r="E96" s="4" t="n"/>
+      <c r="F96" s="4" t="n"/>
+      <c r="G96" s="4" t="n"/>
+      <c r="H96" s="4" t="n"/>
+      <c r="I96" s="4" t="n"/>
+      <c r="J96" s="4" t="n"/>
+      <c r="K96" s="4" t="n"/>
+      <c r="L96" s="4" t="n"/>
+      <c r="M96" s="4" t="n"/>
+      <c r="N96" s="4" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>Interest</t>
+          <t>Beginning Balance</t>
         </is>
       </c>
       <c r="B97" s="6" t="inlineStr">
@@ -5265,56 +4976,52 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C97" s="6" t="inlineStr">
-        <is>
-          <t>Beg Bal × Int Rate</t>
-        </is>
-      </c>
+      <c r="C97" s="6" t="inlineStr"/>
       <c r="E97" s="18">
-        <f>E84*$D$40</f>
+        <f>$D$55</f>
         <v/>
       </c>
       <c r="F97" s="18">
-        <f>F84*$D$40</f>
+        <f>E91</f>
         <v/>
       </c>
       <c r="G97" s="18">
-        <f>G84*$D$40</f>
+        <f>F91</f>
         <v/>
       </c>
       <c r="H97" s="18">
-        <f>H84*$D$40</f>
+        <f>G91</f>
         <v/>
       </c>
       <c r="I97" s="18">
-        <f>I84*$D$40</f>
+        <f>H91</f>
         <v/>
       </c>
       <c r="J97" s="18">
-        <f>J84*$D$40</f>
+        <f>I91</f>
         <v/>
       </c>
       <c r="K97" s="18">
-        <f>K84*$D$40</f>
+        <f>J91</f>
         <v/>
       </c>
       <c r="L97" s="18">
-        <f>L84*$D$40</f>
+        <f>K91</f>
         <v/>
       </c>
       <c r="M97" s="18">
-        <f>M84*$D$40</f>
+        <f>L91</f>
         <v/>
       </c>
       <c r="N97" s="18">
-        <f>N84*$D$40</f>
+        <f>M91</f>
         <v/>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>Scheduled Principal</t>
+          <t>Interest</t>
         </is>
       </c>
       <c r="B98" s="6" t="inlineStr">
@@ -5324,54 +5031,24 @@
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>MIN(Sched, Beg Bal)</t>
-        </is>
-      </c>
-      <c r="E98" s="18">
-        <f>MIN($D$57,E84)</f>
-        <v/>
-      </c>
-      <c r="F98" s="18">
-        <f>MIN($D$57,F84)</f>
-        <v/>
-      </c>
-      <c r="G98" s="18">
-        <f>MIN($D$57,G84)</f>
-        <v/>
-      </c>
-      <c r="H98" s="18">
-        <f>MIN($D$57,H84)</f>
-        <v/>
-      </c>
-      <c r="I98" s="18">
-        <f>MIN($D$57,I84)</f>
-        <v/>
-      </c>
-      <c r="J98" s="18">
-        <f>MIN($D$57,J84)</f>
-        <v/>
-      </c>
-      <c r="K98" s="18">
-        <f>MIN($D$57,K84)</f>
-        <v/>
-      </c>
-      <c r="L98" s="18">
-        <f>MIN($D$57,L84)</f>
-        <v/>
-      </c>
-      <c r="M98" s="18">
-        <f>MIN($D$57,M84)</f>
-        <v/>
-      </c>
-      <c r="N98" s="18">
-        <f>MIN($D$57,N84)</f>
-        <v/>
-      </c>
+          <t>Beg Bal × Int Rate</t>
+        </is>
+      </c>
+      <c r="E98" s="18" t="inlineStr"/>
+      <c r="F98" s="18" t="inlineStr"/>
+      <c r="G98" s="18" t="inlineStr"/>
+      <c r="H98" s="18" t="inlineStr"/>
+      <c r="I98" s="18" t="inlineStr"/>
+      <c r="J98" s="18" t="inlineStr"/>
+      <c r="K98" s="18" t="inlineStr"/>
+      <c r="L98" s="18" t="inlineStr"/>
+      <c r="M98" s="18" t="inlineStr"/>
+      <c r="N98" s="18" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>Debt Service (Pre-Sweep)</t>
+          <t>Scheduled Principal</t>
         </is>
       </c>
       <c r="B99" s="6" t="inlineStr">
@@ -5381,54 +5058,24 @@
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>Interest + Sched Prin</t>
-        </is>
-      </c>
-      <c r="E99" s="18">
-        <f>E85+E86</f>
-        <v/>
-      </c>
-      <c r="F99" s="18">
-        <f>F85+F86</f>
-        <v/>
-      </c>
-      <c r="G99" s="18">
-        <f>G85+G86</f>
-        <v/>
-      </c>
-      <c r="H99" s="18">
-        <f>H85+H86</f>
-        <v/>
-      </c>
-      <c r="I99" s="18">
-        <f>I85+I86</f>
-        <v/>
-      </c>
-      <c r="J99" s="18">
-        <f>J85+J86</f>
-        <v/>
-      </c>
-      <c r="K99" s="18">
-        <f>K85+K86</f>
-        <v/>
-      </c>
-      <c r="L99" s="18">
-        <f>L85+L86</f>
-        <v/>
-      </c>
-      <c r="M99" s="18">
-        <f>M85+M86</f>
-        <v/>
-      </c>
-      <c r="N99" s="18">
-        <f>N85+N86</f>
-        <v/>
-      </c>
+          <t>MIN(Sched, Beg Bal)</t>
+        </is>
+      </c>
+      <c r="E99" s="18" t="inlineStr"/>
+      <c r="F99" s="18" t="inlineStr"/>
+      <c r="G99" s="18" t="inlineStr"/>
+      <c r="H99" s="18" t="inlineStr"/>
+      <c r="I99" s="18" t="inlineStr"/>
+      <c r="J99" s="18" t="inlineStr"/>
+      <c r="K99" s="18" t="inlineStr"/>
+      <c r="L99" s="18" t="inlineStr"/>
+      <c r="M99" s="18" t="inlineStr"/>
+      <c r="N99" s="18" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>Excess Cash</t>
+          <t>Debt Service (Pre-Sweep)</t>
         </is>
       </c>
       <c r="B100" s="6" t="inlineStr">
@@ -5438,54 +5085,54 @@
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>CFADS - DS - DSRA Funding</t>
+          <t>Interest + Sched Prin</t>
         </is>
       </c>
       <c r="E100" s="18">
-        <f>MAX(0,E80-E87-E98)</f>
+        <f>E85+E86</f>
         <v/>
       </c>
       <c r="F100" s="18">
-        <f>MAX(0,F80-F87-F98)</f>
+        <f>F85+F86</f>
         <v/>
       </c>
       <c r="G100" s="18">
-        <f>MAX(0,G80-G87-G98)</f>
+        <f>G85+G86</f>
         <v/>
       </c>
       <c r="H100" s="18">
-        <f>MAX(0,H80-H87-H98)</f>
+        <f>H85+H86</f>
         <v/>
       </c>
       <c r="I100" s="18">
-        <f>MAX(0,I80-I87-I98)</f>
+        <f>I85+I86</f>
         <v/>
       </c>
       <c r="J100" s="18">
-        <f>MAX(0,J80-J87-J98)</f>
+        <f>J85+J86</f>
         <v/>
       </c>
       <c r="K100" s="18">
-        <f>MAX(0,K80-K87-K98)</f>
+        <f>K85+K86</f>
         <v/>
       </c>
       <c r="L100" s="18">
-        <f>MAX(0,L80-L87-L98)</f>
+        <f>L85+L86</f>
         <v/>
       </c>
       <c r="M100" s="18">
-        <f>MAX(0,M80-M87-M98)</f>
+        <f>M85+M86</f>
         <v/>
       </c>
       <c r="N100" s="18">
-        <f>MAX(0,N80-N87-N98)</f>
+        <f>N85+N86</f>
         <v/>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>Cash Sweep</t>
+          <t>Excess Cash</t>
         </is>
       </c>
       <c r="B101" s="6" t="inlineStr">
@@ -5495,54 +5142,54 @@
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>MIN(Excess×Sweep%, Beg-Sched)</t>
-        </is>
-      </c>
-      <c r="E101" s="21">
-        <f>MIN(MAX(0,E88)*$D$43,MAX(0,E84-E86))</f>
-        <v/>
-      </c>
-      <c r="F101" s="21">
-        <f>MIN(MAX(0,F88)*$D$43,MAX(0,F84-F86))</f>
-        <v/>
-      </c>
-      <c r="G101" s="21">
-        <f>MIN(MAX(0,G88)*$D$43,MAX(0,G84-G86))</f>
-        <v/>
-      </c>
-      <c r="H101" s="21">
-        <f>MIN(MAX(0,H88)*$D$43,MAX(0,H84-H86))</f>
-        <v/>
-      </c>
-      <c r="I101" s="21">
-        <f>MIN(MAX(0,I88)*$D$43,MAX(0,I84-I86))</f>
-        <v/>
-      </c>
-      <c r="J101" s="21">
-        <f>MIN(MAX(0,J88)*$D$43,MAX(0,J84-J86))</f>
-        <v/>
-      </c>
-      <c r="K101" s="21">
-        <f>MIN(MAX(0,K88)*$D$43,MAX(0,K84-K86))</f>
-        <v/>
-      </c>
-      <c r="L101" s="21">
-        <f>MIN(MAX(0,L88)*$D$43,MAX(0,L84-L86))</f>
-        <v/>
-      </c>
-      <c r="M101" s="21">
-        <f>MIN(MAX(0,M88)*$D$43,MAX(0,M84-M86))</f>
-        <v/>
-      </c>
-      <c r="N101" s="21">
-        <f>MIN(MAX(0,N88)*$D$43,MAX(0,N84-N86))</f>
+          <t>CFADS - DS - DSRA Funding</t>
+        </is>
+      </c>
+      <c r="E101" s="18">
+        <f>MAX(0,E80-E87-E98)</f>
+        <v/>
+      </c>
+      <c r="F101" s="18">
+        <f>MAX(0,F80-F87-F98)</f>
+        <v/>
+      </c>
+      <c r="G101" s="18">
+        <f>MAX(0,G80-G87-G98)</f>
+        <v/>
+      </c>
+      <c r="H101" s="18">
+        <f>MAX(0,H80-H87-H98)</f>
+        <v/>
+      </c>
+      <c r="I101" s="18">
+        <f>MAX(0,I80-I87-I98)</f>
+        <v/>
+      </c>
+      <c r="J101" s="18">
+        <f>MAX(0,J80-J87-J98)</f>
+        <v/>
+      </c>
+      <c r="K101" s="18">
+        <f>MAX(0,K80-K87-K98)</f>
+        <v/>
+      </c>
+      <c r="L101" s="18">
+        <f>MAX(0,L80-L87-L98)</f>
+        <v/>
+      </c>
+      <c r="M101" s="18">
+        <f>MAX(0,M80-M87-M98)</f>
+        <v/>
+      </c>
+      <c r="N101" s="18">
+        <f>MAX(0,N80-N87-N98)</f>
         <v/>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>Total Principal</t>
+          <t>Cash Sweep</t>
         </is>
       </c>
       <c r="B102" s="6" t="inlineStr">
@@ -5552,54 +5199,24 @@
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>Scheduled + Sweep</t>
-        </is>
-      </c>
-      <c r="E102" s="18">
-        <f>E86+E89</f>
-        <v/>
-      </c>
-      <c r="F102" s="18">
-        <f>F86+F89</f>
-        <v/>
-      </c>
-      <c r="G102" s="18">
-        <f>G86+G89</f>
-        <v/>
-      </c>
-      <c r="H102" s="18">
-        <f>H86+H89</f>
-        <v/>
-      </c>
-      <c r="I102" s="18">
-        <f>I86+I89</f>
-        <v/>
-      </c>
-      <c r="J102" s="18">
-        <f>J86+J89</f>
-        <v/>
-      </c>
-      <c r="K102" s="18">
-        <f>K86+K89</f>
-        <v/>
-      </c>
-      <c r="L102" s="18">
-        <f>L86+L89</f>
-        <v/>
-      </c>
-      <c r="M102" s="18">
-        <f>M86+M89</f>
-        <v/>
-      </c>
-      <c r="N102" s="18">
-        <f>N86+N89</f>
-        <v/>
-      </c>
+          <t>MIN(Excess×Sweep%, Beg-Sched)</t>
+        </is>
+      </c>
+      <c r="E102" s="21" t="inlineStr"/>
+      <c r="F102" s="21" t="inlineStr"/>
+      <c r="G102" s="21" t="inlineStr"/>
+      <c r="H102" s="21" t="inlineStr"/>
+      <c r="I102" s="21" t="inlineStr"/>
+      <c r="J102" s="21" t="inlineStr"/>
+      <c r="K102" s="21" t="inlineStr"/>
+      <c r="L102" s="21" t="inlineStr"/>
+      <c r="M102" s="21" t="inlineStr"/>
+      <c r="N102" s="21" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>Ending Balance</t>
+          <t>Total Principal</t>
         </is>
       </c>
       <c r="B103" s="6" t="inlineStr">
@@ -5609,250 +5226,156 @@
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>MAX(0, Beg - Total Prin)</t>
-        </is>
-      </c>
-      <c r="E103" s="18">
-        <f>MAX(0,E84-E90)</f>
-        <v/>
-      </c>
-      <c r="F103" s="18">
-        <f>MAX(0,F84-F90)</f>
-        <v/>
-      </c>
-      <c r="G103" s="18">
-        <f>MAX(0,G84-G90)</f>
-        <v/>
-      </c>
-      <c r="H103" s="18">
-        <f>MAX(0,H84-H90)</f>
-        <v/>
-      </c>
-      <c r="I103" s="18">
-        <f>MAX(0,I84-I90)</f>
-        <v/>
-      </c>
-      <c r="J103" s="18">
-        <f>MAX(0,J84-J90)</f>
-        <v/>
-      </c>
-      <c r="K103" s="18">
-        <f>MAX(0,K84-K90)</f>
-        <v/>
-      </c>
-      <c r="L103" s="18">
-        <f>MAX(0,L84-L90)</f>
-        <v/>
-      </c>
-      <c r="M103" s="18">
-        <f>MAX(0,M84-M90)</f>
-        <v/>
-      </c>
-      <c r="N103" s="18">
-        <f>MAX(0,N84-N90)</f>
-        <v/>
-      </c>
+          <t>Scheduled + Sweep</t>
+        </is>
+      </c>
+      <c r="E103" s="18" t="inlineStr"/>
+      <c r="F103" s="18" t="inlineStr"/>
+      <c r="G103" s="18" t="inlineStr"/>
+      <c r="H103" s="18" t="inlineStr"/>
+      <c r="I103" s="18" t="inlineStr"/>
+      <c r="J103" s="18" t="inlineStr"/>
+      <c r="K103" s="18" t="inlineStr"/>
+      <c r="L103" s="18" t="inlineStr"/>
+      <c r="M103" s="18" t="inlineStr"/>
+      <c r="N103" s="18" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>DSCR</t>
+          <t>Ending Balance</t>
         </is>
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>$mm</t>
         </is>
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>CFADS / Debt Service</t>
-        </is>
-      </c>
-      <c r="E104" s="30">
-        <f>IF(E87&gt;0,E80/E87,0)</f>
-        <v/>
-      </c>
-      <c r="F104" s="30">
-        <f>IF(F87&gt;0,F80/F87,0)</f>
-        <v/>
-      </c>
-      <c r="G104" s="30">
-        <f>IF(G87&gt;0,G80/G87,0)</f>
-        <v/>
-      </c>
-      <c r="H104" s="30">
-        <f>IF(H87&gt;0,H80/H87,0)</f>
-        <v/>
-      </c>
-      <c r="I104" s="30">
-        <f>IF(I87&gt;0,I80/I87,0)</f>
-        <v/>
-      </c>
-      <c r="J104" s="30">
-        <f>IF(J87&gt;0,J80/J87,0)</f>
-        <v/>
-      </c>
-      <c r="K104" s="30">
-        <f>IF(K87&gt;0,K80/K87,0)</f>
-        <v/>
-      </c>
-      <c r="L104" s="30">
-        <f>IF(L87&gt;0,L80/L87,0)</f>
-        <v/>
-      </c>
-      <c r="M104" s="30">
-        <f>IF(M87&gt;0,M80/M87,0)</f>
-        <v/>
-      </c>
-      <c r="N104" s="30">
-        <f>IF(N87&gt;0,N80/N87,0)</f>
-        <v/>
-      </c>
+          <t>MAX(0, Beg - Total Prin)</t>
+        </is>
+      </c>
+      <c r="E104" s="18" t="inlineStr"/>
+      <c r="F104" s="18" t="inlineStr"/>
+      <c r="G104" s="18" t="inlineStr"/>
+      <c r="H104" s="18" t="inlineStr"/>
+      <c r="I104" s="18" t="inlineStr"/>
+      <c r="J104" s="18" t="inlineStr"/>
+      <c r="K104" s="18" t="inlineStr"/>
+      <c r="L104" s="18" t="inlineStr"/>
+      <c r="M104" s="18" t="inlineStr"/>
+      <c r="N104" s="18" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
+          <t>DSCR</t>
+        </is>
+      </c>
+      <c r="B105" s="6" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C105" s="6" t="inlineStr">
+        <is>
+          <t>CFADS / Debt Service</t>
+        </is>
+      </c>
+      <c r="E105" s="30" t="inlineStr"/>
+      <c r="F105" s="30" t="inlineStr"/>
+      <c r="G105" s="30" t="inlineStr"/>
+      <c r="H105" s="30" t="inlineStr"/>
+      <c r="I105" s="30" t="inlineStr"/>
+      <c r="J105" s="30" t="inlineStr"/>
+      <c r="K105" s="30" t="inlineStr"/>
+      <c r="L105" s="30" t="inlineStr"/>
+      <c r="M105" s="30" t="inlineStr"/>
+      <c r="N105" s="30" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="5" t="inlineStr">
+        <is>
           <t>Scheduled DS (for DSRA)</t>
         </is>
       </c>
-      <c r="B105" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C105" s="6" t="inlineStr">
+      <c r="B106" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C106" s="6" t="inlineStr">
         <is>
           <t>Based on straight-line amort, no sweep</t>
         </is>
       </c>
-      <c r="E105" s="18">
+      <c r="E106" s="18">
         <f>MAX(0,$D$55-(1-1)*$D$57)*$D$40+$D$57</f>
         <v/>
       </c>
-      <c r="F105" s="18">
+      <c r="F106" s="18">
         <f>MAX(0,$D$55-(2-1)*$D$57)*$D$40+$D$57</f>
         <v/>
       </c>
-      <c r="G105" s="18">
+      <c r="G106" s="18">
         <f>MAX(0,$D$55-(3-1)*$D$57)*$D$40+$D$57</f>
         <v/>
       </c>
-      <c r="H105" s="18">
+      <c r="H106" s="18">
         <f>MAX(0,$D$55-(4-1)*$D$57)*$D$40+$D$57</f>
         <v/>
       </c>
-      <c r="I105" s="18">
+      <c r="I106" s="18">
         <f>MAX(0,$D$55-(5-1)*$D$57)*$D$40+$D$57</f>
         <v/>
       </c>
-      <c r="J105" s="18">
+      <c r="J106" s="18">
         <f>MAX(0,$D$55-(6-1)*$D$57)*$D$40+$D$57</f>
         <v/>
       </c>
-      <c r="K105" s="18">
+      <c r="K106" s="18">
         <f>MAX(0,$D$55-(7-1)*$D$57)*$D$40+$D$57</f>
         <v/>
       </c>
-      <c r="L105" s="18">
+      <c r="L106" s="18">
         <f>MAX(0,$D$55-(8-1)*$D$57)*$D$40+$D$57</f>
         <v/>
       </c>
-      <c r="M105" s="18">
+      <c r="M106" s="18">
         <f>MAX(0,$D$55-(9-1)*$D$57)*$D$40+$D$57</f>
         <v/>
       </c>
-      <c r="N105" s="18">
+      <c r="N106" s="18">
         <f>MAX(0,$D$55-(10-1)*$D$57)*$D$40+$D$57</f>
         <v/>
       </c>
     </row>
-    <row r="106"/>
-    <row r="107">
-      <c r="A107" s="3" t="inlineStr">
+    <row r="107"/>
+    <row r="108">
+      <c r="A108" s="3" t="inlineStr">
         <is>
           <t>DSRA (Debt Service Reserve Account)</t>
         </is>
       </c>
-      <c r="B107" s="4" t="n"/>
-      <c r="C107" s="4" t="n"/>
-      <c r="D107" s="4" t="n"/>
-      <c r="E107" s="4" t="n"/>
-      <c r="F107" s="4" t="n"/>
-      <c r="G107" s="4" t="n"/>
-      <c r="H107" s="4" t="n"/>
-      <c r="I107" s="4" t="n"/>
-      <c r="J107" s="4" t="n"/>
-      <c r="K107" s="4" t="n"/>
-      <c r="L107" s="4" t="n"/>
-      <c r="M107" s="4" t="n"/>
-      <c r="N107" s="4" t="n"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="5" t="inlineStr">
-        <is>
-          <t>DSRA Target</t>
-        </is>
-      </c>
-      <c r="B108" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C108" s="6" t="inlineStr">
-        <is>
-          <t>Next Yr Scheduled DS × DSRA Months / 12</t>
-        </is>
-      </c>
-      <c r="D108" s="18">
-        <f>E93*$D$42/12</f>
-        <v/>
-      </c>
-      <c r="E108" s="18">
-        <f>F93*$D$42/12</f>
-        <v/>
-      </c>
-      <c r="F108" s="18">
-        <f>G93*$D$42/12</f>
-        <v/>
-      </c>
-      <c r="G108" s="18">
-        <f>H93*$D$42/12</f>
-        <v/>
-      </c>
-      <c r="H108" s="18">
-        <f>I93*$D$42/12</f>
-        <v/>
-      </c>
-      <c r="I108" s="18">
-        <f>J93*$D$42/12</f>
-        <v/>
-      </c>
-      <c r="J108" s="18">
-        <f>K93*$D$42/12</f>
-        <v/>
-      </c>
-      <c r="K108" s="18">
-        <f>L93*$D$42/12</f>
-        <v/>
-      </c>
-      <c r="L108" s="18">
-        <f>M93*$D$42/12</f>
-        <v/>
-      </c>
-      <c r="M108" s="18">
-        <f>N93*$D$42/12</f>
-        <v/>
-      </c>
-      <c r="N108" s="18">
-        <f>0</f>
-        <v/>
-      </c>
+      <c r="B108" s="4" t="n"/>
+      <c r="C108" s="4" t="n"/>
+      <c r="D108" s="4" t="n"/>
+      <c r="E108" s="4" t="n"/>
+      <c r="F108" s="4" t="n"/>
+      <c r="G108" s="4" t="n"/>
+      <c r="H108" s="4" t="n"/>
+      <c r="I108" s="4" t="n"/>
+      <c r="J108" s="4" t="n"/>
+      <c r="K108" s="4" t="n"/>
+      <c r="L108" s="4" t="n"/>
+      <c r="M108" s="4" t="n"/>
+      <c r="N108" s="4" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>DSRA Beginning</t>
+          <t>DSRA Target</t>
         </is>
       </c>
       <c r="B109" s="6" t="inlineStr">
@@ -5860,56 +5383,60 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C109" s="6" t="inlineStr"/>
+      <c r="C109" s="6" t="inlineStr">
+        <is>
+          <t>Next Yr Scheduled DS × DSRA Months / 12</t>
+        </is>
+      </c>
       <c r="D109" s="18">
+        <f>E93*$D$42/12</f>
+        <v/>
+      </c>
+      <c r="E109" s="18">
+        <f>F93*$D$42/12</f>
+        <v/>
+      </c>
+      <c r="F109" s="18">
+        <f>G93*$D$42/12</f>
+        <v/>
+      </c>
+      <c r="G109" s="18">
+        <f>H93*$D$42/12</f>
+        <v/>
+      </c>
+      <c r="H109" s="18">
+        <f>I93*$D$42/12</f>
+        <v/>
+      </c>
+      <c r="I109" s="18">
+        <f>J93*$D$42/12</f>
+        <v/>
+      </c>
+      <c r="J109" s="18">
+        <f>K93*$D$42/12</f>
+        <v/>
+      </c>
+      <c r="K109" s="18">
+        <f>L93*$D$42/12</f>
+        <v/>
+      </c>
+      <c r="L109" s="18">
+        <f>M93*$D$42/12</f>
+        <v/>
+      </c>
+      <c r="M109" s="18">
+        <f>N93*$D$42/12</f>
+        <v/>
+      </c>
+      <c r="N109" s="18">
         <f>0</f>
-        <v/>
-      </c>
-      <c r="E109" s="18">
-        <f>D99</f>
-        <v/>
-      </c>
-      <c r="F109" s="18">
-        <f>E99</f>
-        <v/>
-      </c>
-      <c r="G109" s="18">
-        <f>F99</f>
-        <v/>
-      </c>
-      <c r="H109" s="18">
-        <f>G99</f>
-        <v/>
-      </c>
-      <c r="I109" s="18">
-        <f>H99</f>
-        <v/>
-      </c>
-      <c r="J109" s="18">
-        <f>I99</f>
-        <v/>
-      </c>
-      <c r="K109" s="18">
-        <f>J99</f>
-        <v/>
-      </c>
-      <c r="L109" s="18">
-        <f>K99</f>
-        <v/>
-      </c>
-      <c r="M109" s="18">
-        <f>L99</f>
-        <v/>
-      </c>
-      <c r="N109" s="18">
-        <f>M99</f>
         <v/>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>DSRA Funding/(Release)</t>
+          <t>DSRA Beginning</t>
         </is>
       </c>
       <c r="B110" s="6" t="inlineStr">
@@ -5917,358 +5444,368 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C110" s="6" t="inlineStr">
-        <is>
-          <t>Target - Beginning</t>
-        </is>
-      </c>
+      <c r="C110" s="6" t="inlineStr"/>
       <c r="D110" s="18">
-        <f>D96-D97</f>
+        <f>0</f>
         <v/>
       </c>
       <c r="E110" s="18">
-        <f>E96-E97</f>
+        <f>D99</f>
         <v/>
       </c>
       <c r="F110" s="18">
-        <f>F96-F97</f>
+        <f>E99</f>
         <v/>
       </c>
       <c r="G110" s="18">
-        <f>G96-G97</f>
+        <f>F99</f>
         <v/>
       </c>
       <c r="H110" s="18">
-        <f>H96-H97</f>
+        <f>G99</f>
         <v/>
       </c>
       <c r="I110" s="18">
-        <f>I96-I97</f>
+        <f>H99</f>
         <v/>
       </c>
       <c r="J110" s="18">
-        <f>J96-J97</f>
+        <f>I99</f>
         <v/>
       </c>
       <c r="K110" s="18">
-        <f>K96-K97</f>
+        <f>J99</f>
         <v/>
       </c>
       <c r="L110" s="18">
-        <f>L96-L97</f>
+        <f>K99</f>
         <v/>
       </c>
       <c r="M110" s="18">
-        <f>M96-M97</f>
+        <f>L99</f>
         <v/>
       </c>
       <c r="N110" s="18">
-        <f>N96-N97</f>
+        <f>M99</f>
         <v/>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
+          <t>DSRA Funding/(Release)</t>
+        </is>
+      </c>
+      <c r="B111" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C111" s="6" t="inlineStr">
+        <is>
+          <t>Target - Beginning</t>
+        </is>
+      </c>
+      <c r="D111" s="18">
+        <f>D96-D97</f>
+        <v/>
+      </c>
+      <c r="E111" s="18">
+        <f>E96-E97</f>
+        <v/>
+      </c>
+      <c r="F111" s="18">
+        <f>F96-F97</f>
+        <v/>
+      </c>
+      <c r="G111" s="18">
+        <f>G96-G97</f>
+        <v/>
+      </c>
+      <c r="H111" s="18">
+        <f>H96-H97</f>
+        <v/>
+      </c>
+      <c r="I111" s="18">
+        <f>I96-I97</f>
+        <v/>
+      </c>
+      <c r="J111" s="18">
+        <f>J96-J97</f>
+        <v/>
+      </c>
+      <c r="K111" s="18">
+        <f>K96-K97</f>
+        <v/>
+      </c>
+      <c r="L111" s="18">
+        <f>L96-L97</f>
+        <v/>
+      </c>
+      <c r="M111" s="18">
+        <f>M96-M97</f>
+        <v/>
+      </c>
+      <c r="N111" s="18">
+        <f>N96-N97</f>
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="5" t="inlineStr">
+        <is>
           <t>DSRA Ending</t>
         </is>
       </c>
-      <c r="B111" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C111" s="6" t="inlineStr">
+      <c r="B112" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C112" s="6" t="inlineStr">
         <is>
           <t>Beginning + Funding</t>
         </is>
       </c>
-      <c r="D111" s="18">
+      <c r="D112" s="18">
         <f>D97+D98</f>
         <v/>
       </c>
-      <c r="E111" s="18">
+      <c r="E112" s="18">
         <f>E97+E98</f>
         <v/>
       </c>
-      <c r="F111" s="18">
+      <c r="F112" s="18">
         <f>F97+F98</f>
         <v/>
       </c>
-      <c r="G111" s="18">
+      <c r="G112" s="18">
         <f>G97+G98</f>
         <v/>
       </c>
-      <c r="H111" s="18">
+      <c r="H112" s="18">
         <f>H97+H98</f>
         <v/>
       </c>
-      <c r="I111" s="18">
+      <c r="I112" s="18">
         <f>I97+I98</f>
         <v/>
       </c>
-      <c r="J111" s="18">
+      <c r="J112" s="18">
         <f>J97+J98</f>
         <v/>
       </c>
-      <c r="K111" s="18">
+      <c r="K112" s="18">
         <f>K97+K98</f>
         <v/>
       </c>
-      <c r="L111" s="18">
+      <c r="L112" s="18">
         <f>L97+L98</f>
         <v/>
       </c>
-      <c r="M111" s="18">
+      <c r="M112" s="18">
         <f>M97+M98</f>
         <v/>
       </c>
-      <c r="N111" s="18">
+      <c r="N112" s="18">
         <f>N97+N98</f>
         <v/>
       </c>
     </row>
-    <row r="112"/>
     <row r="113"/>
-    <row r="114">
-      <c r="A114" s="3" t="inlineStr">
+    <row r="114"/>
+    <row r="115">
+      <c r="A115" s="3" t="inlineStr">
         <is>
           <t>DISTRIBUTION WATERFALL</t>
         </is>
       </c>
-      <c r="B114" s="4" t="n"/>
-      <c r="C114" s="4" t="n"/>
-      <c r="D114" s="4" t="n"/>
-      <c r="E114" s="4" t="n"/>
-      <c r="F114" s="4" t="n"/>
-      <c r="G114" s="4" t="n"/>
-      <c r="H114" s="4" t="n"/>
-      <c r="I114" s="4" t="n"/>
-      <c r="J114" s="4" t="n"/>
-      <c r="K114" s="4" t="n"/>
-      <c r="L114" s="4" t="n"/>
-      <c r="M114" s="4" t="n"/>
-      <c r="N114" s="4" t="n"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="5" t="inlineStr">
-        <is>
-          <t>Cash Available for Distribution</t>
-        </is>
-      </c>
-      <c r="B115" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C115" s="6" t="inlineStr">
-        <is>
-          <t>CFADS - Total DS - DSRA Fund</t>
-        </is>
-      </c>
-      <c r="E115" s="18">
-        <f>E80-(E85+E90)-E98</f>
-        <v/>
-      </c>
-      <c r="F115" s="18">
-        <f>F80-(F85+F90)-F98</f>
-        <v/>
-      </c>
-      <c r="G115" s="18">
-        <f>G80-(G85+G90)-G98</f>
-        <v/>
-      </c>
-      <c r="H115" s="18">
-        <f>H80-(H85+H90)-H98</f>
-        <v/>
-      </c>
-      <c r="I115" s="18">
-        <f>I80-(I85+I90)-I98</f>
-        <v/>
-      </c>
-      <c r="J115" s="18">
-        <f>J80-(J85+J90)-J98</f>
-        <v/>
-      </c>
-      <c r="K115" s="18">
-        <f>K80-(K85+K90)-K98</f>
-        <v/>
-      </c>
-      <c r="L115" s="18">
-        <f>L80-(L85+L90)-L98</f>
-        <v/>
-      </c>
-      <c r="M115" s="18">
-        <f>M80-(M85+M90)-M98</f>
-        <v/>
-      </c>
-      <c r="N115" s="18">
-        <f>N80-(N85+N90)-N98</f>
-        <v/>
-      </c>
+      <c r="B115" s="4" t="n"/>
+      <c r="C115" s="4" t="n"/>
+      <c r="D115" s="4" t="n"/>
+      <c r="E115" s="4" t="n"/>
+      <c r="F115" s="4" t="n"/>
+      <c r="G115" s="4" t="n"/>
+      <c r="H115" s="4" t="n"/>
+      <c r="I115" s="4" t="n"/>
+      <c r="J115" s="4" t="n"/>
+      <c r="K115" s="4" t="n"/>
+      <c r="L115" s="4" t="n"/>
+      <c r="M115" s="4" t="n"/>
+      <c r="N115" s="4" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>Lock-up Test</t>
-        </is>
-      </c>
-      <c r="B116" s="6" t="inlineStr"/>
+          <t>Cash Available for Distribution</t>
+        </is>
+      </c>
+      <c r="B116" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t>PASS if DSCR ≥ Lock-up</t>
-        </is>
-      </c>
-      <c r="E116" s="22">
-        <f>IF(E92&gt;=$D$44,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="F116" s="22">
-        <f>IF(F92&gt;=$D$44,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="G116" s="22">
-        <f>IF(G92&gt;=$D$44,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="H116" s="22">
-        <f>IF(H92&gt;=$D$44,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="I116" s="22">
-        <f>IF(I92&gt;=$D$44,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="J116" s="22">
-        <f>IF(J92&gt;=$D$44,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="K116" s="22">
-        <f>IF(K92&gt;=$D$44,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="L116" s="22">
-        <f>IF(L92&gt;=$D$44,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="M116" s="22">
-        <f>IF(M92&gt;=$D$44,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="N116" s="22">
-        <f>IF(N92&gt;=$D$44,"PASS","LOCKED")</f>
+          <t>CFADS - Total DS - DSRA Fund</t>
+        </is>
+      </c>
+      <c r="E116" s="18">
+        <f>E80-(E85+E90)-E98</f>
+        <v/>
+      </c>
+      <c r="F116" s="18">
+        <f>F80-(F85+F90)-F98</f>
+        <v/>
+      </c>
+      <c r="G116" s="18">
+        <f>G80-(G85+G90)-G98</f>
+        <v/>
+      </c>
+      <c r="H116" s="18">
+        <f>H80-(H85+H90)-H98</f>
+        <v/>
+      </c>
+      <c r="I116" s="18">
+        <f>I80-(I85+I90)-I98</f>
+        <v/>
+      </c>
+      <c r="J116" s="18">
+        <f>J80-(J85+J90)-J98</f>
+        <v/>
+      </c>
+      <c r="K116" s="18">
+        <f>K80-(K85+K90)-K98</f>
+        <v/>
+      </c>
+      <c r="L116" s="18">
+        <f>L80-(L85+L90)-L98</f>
+        <v/>
+      </c>
+      <c r="M116" s="18">
+        <f>M80-(M85+M90)-M98</f>
+        <v/>
+      </c>
+      <c r="N116" s="18">
+        <f>N80-(N85+N90)-N98</f>
         <v/>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
+          <t>Lock-up Test</t>
+        </is>
+      </c>
+      <c r="B117" s="6" t="inlineStr"/>
+      <c r="C117" s="6" t="inlineStr">
+        <is>
+          <t>PASS if DSCR ≥ Lock-up</t>
+        </is>
+      </c>
+      <c r="E117" s="22">
+        <f>IF(E92&gt;=$D$44,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="F117" s="22">
+        <f>IF(F92&gt;=$D$44,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="G117" s="22">
+        <f>IF(G92&gt;=$D$44,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="H117" s="22">
+        <f>IF(H92&gt;=$D$44,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="I117" s="22">
+        <f>IF(I92&gt;=$D$44,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="J117" s="22">
+        <f>IF(J92&gt;=$D$44,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="K117" s="22">
+        <f>IF(K92&gt;=$D$44,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="L117" s="22">
+        <f>IF(L92&gt;=$D$44,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="M117" s="22">
+        <f>IF(M92&gt;=$D$44,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="N117" s="22">
+        <f>IF(N92&gt;=$D$44,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="5" t="inlineStr">
+        <is>
           <t>Distributable Cash</t>
         </is>
       </c>
-      <c r="B117" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C117" s="6" t="inlineStr">
+      <c r="B118" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C118" s="6" t="inlineStr">
         <is>
           <t>If PASS, MAX(0, Cash Avail)</t>
         </is>
       </c>
-      <c r="E117" s="7">
-        <f>IF(E104="PASS",MAX(0,E103),0)</f>
-        <v/>
-      </c>
-      <c r="F117" s="7">
-        <f>IF(F104="PASS",MAX(0,F103),0)</f>
-        <v/>
-      </c>
-      <c r="G117" s="7">
-        <f>IF(G104="PASS",MAX(0,G103),0)</f>
-        <v/>
-      </c>
-      <c r="H117" s="7">
-        <f>IF(H104="PASS",MAX(0,H103),0)</f>
-        <v/>
-      </c>
-      <c r="I117" s="7">
-        <f>IF(I104="PASS",MAX(0,I103),0)</f>
-        <v/>
-      </c>
-      <c r="J117" s="7">
-        <f>IF(J104="PASS",MAX(0,J103),0)</f>
-        <v/>
-      </c>
-      <c r="K117" s="7">
-        <f>IF(K104="PASS",MAX(0,K103),0)</f>
-        <v/>
-      </c>
-      <c r="L117" s="7">
-        <f>IF(L104="PASS",MAX(0,L103),0)</f>
-        <v/>
-      </c>
-      <c r="M117" s="7">
-        <f>IF(M104="PASS",MAX(0,M103),0)</f>
-        <v/>
-      </c>
-      <c r="N117" s="7">
-        <f>IF(N104="PASS",MAX(0,N103),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="118"/>
+      <c r="E118" s="7" t="inlineStr"/>
+      <c r="F118" s="7" t="inlineStr"/>
+      <c r="G118" s="7" t="inlineStr"/>
+      <c r="H118" s="7" t="inlineStr"/>
+      <c r="I118" s="7" t="inlineStr"/>
+      <c r="J118" s="7" t="inlineStr"/>
+      <c r="K118" s="7" t="inlineStr"/>
+      <c r="L118" s="7" t="inlineStr"/>
+      <c r="M118" s="7" t="inlineStr"/>
+      <c r="N118" s="7" t="inlineStr"/>
+    </row>
     <row r="119"/>
-    <row r="120">
-      <c r="A120" s="3" t="inlineStr">
+    <row r="120"/>
+    <row r="121">
+      <c r="A121" s="3" t="inlineStr">
         <is>
           <t>SOURCES &amp; USES (Year 0)</t>
         </is>
       </c>
-      <c r="B120" s="4" t="n"/>
-      <c r="C120" s="4" t="n"/>
-      <c r="D120" s="4" t="n"/>
-      <c r="E120" s="4" t="n"/>
-      <c r="F120" s="4" t="n"/>
-      <c r="G120" s="4" t="n"/>
-      <c r="H120" s="4" t="n"/>
-      <c r="I120" s="4" t="n"/>
-      <c r="J120" s="4" t="n"/>
-      <c r="K120" s="4" t="n"/>
-      <c r="L120" s="4" t="n"/>
-      <c r="M120" s="4" t="n"/>
-      <c r="N120" s="4" t="n"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="23" t="inlineStr">
+      <c r="B121" s="4" t="n"/>
+      <c r="C121" s="4" t="n"/>
+      <c r="D121" s="4" t="n"/>
+      <c r="E121" s="4" t="n"/>
+      <c r="F121" s="4" t="n"/>
+      <c r="G121" s="4" t="n"/>
+      <c r="H121" s="4" t="n"/>
+      <c r="I121" s="4" t="n"/>
+      <c r="J121" s="4" t="n"/>
+      <c r="K121" s="4" t="n"/>
+      <c r="L121" s="4" t="n"/>
+      <c r="M121" s="4" t="n"/>
+      <c r="N121" s="4" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="23" t="inlineStr">
         <is>
           <t>USES</t>
         </is>
       </c>
-      <c r="B121" s="6" t="inlineStr"/>
-      <c r="C121" s="6" t="inlineStr"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Purchase Price</t>
-        </is>
-      </c>
-      <c r="B122" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
+      <c r="B122" s="6" t="inlineStr"/>
       <c r="C122" s="6" t="inlineStr"/>
-      <c r="D122" s="18">
-        <f>$D$17</f>
-        <v/>
-      </c>
     </row>
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Transaction Fees</t>
+          <t xml:space="preserve">  Purchase Price</t>
         </is>
       </c>
       <c r="B123" s="6" t="inlineStr">
@@ -6278,14 +5815,14 @@
       </c>
       <c r="C123" s="6" t="inlineStr"/>
       <c r="D123" s="18">
-        <f>$D$17*$D$18</f>
+        <f>$D$17</f>
         <v/>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  DSRA Funding</t>
+          <t xml:space="preserve">  Transaction Fees</t>
         </is>
       </c>
       <c r="B124" s="6" t="inlineStr">
@@ -6295,58 +5832,58 @@
       </c>
       <c r="C124" s="6" t="inlineStr"/>
       <c r="D124" s="18">
-        <f>D96</f>
+        <f>$D$17*$D$18</f>
         <v/>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">  DSRA Funding</t>
+        </is>
+      </c>
+      <c r="B125" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C125" s="6" t="inlineStr"/>
+      <c r="D125" s="18">
+        <f>D96</f>
+        <v/>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="5" t="inlineStr">
+        <is>
           <t>Total Uses</t>
         </is>
       </c>
-      <c r="B125" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C125" s="6" t="inlineStr"/>
-      <c r="D125" s="7">
+      <c r="B126" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C126" s="6" t="inlineStr"/>
+      <c r="D126" s="7">
         <f>D110+D111+D112</f>
         <v/>
       </c>
     </row>
-    <row r="126"/>
-    <row r="127">
-      <c r="A127" s="23" t="inlineStr">
+    <row r="127"/>
+    <row r="128">
+      <c r="A128" s="23" t="inlineStr">
         <is>
           <t>SOURCES</t>
         </is>
       </c>
-      <c r="B127" s="6" t="inlineStr"/>
-      <c r="C127" s="6" t="inlineStr"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Debt</t>
-        </is>
-      </c>
-      <c r="B128" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
+      <c r="B128" s="6" t="inlineStr"/>
       <c r="C128" s="6" t="inlineStr"/>
-      <c r="D128" s="18">
-        <f>$D$55</f>
-        <v/>
-      </c>
     </row>
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Equity</t>
+          <t xml:space="preserve">  Debt</t>
         </is>
       </c>
       <c r="B129" s="6" t="inlineStr">
@@ -6354,20 +5891,16 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C129" s="6" t="inlineStr">
-        <is>
-          <t>Plug to balance</t>
-        </is>
-      </c>
+      <c r="C129" s="6" t="inlineStr"/>
       <c r="D129" s="18">
-        <f>D113-D116</f>
+        <f>$D$55</f>
         <v/>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t>Total Sources</t>
+          <t xml:space="preserve">  Equity</t>
         </is>
       </c>
       <c r="B130" s="6" t="inlineStr">
@@ -6375,72 +5908,72 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C130" s="6" t="inlineStr"/>
-      <c r="D130" s="7">
-        <f>D116+D117</f>
+      <c r="C130" s="6" t="inlineStr">
+        <is>
+          <t>Plug to balance</t>
+        </is>
+      </c>
+      <c r="D130" s="18">
+        <f>D113-D116</f>
         <v/>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="5" t="inlineStr">
         <is>
+          <t>Total Sources</t>
+        </is>
+      </c>
+      <c r="B131" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C131" s="6" t="inlineStr"/>
+      <c r="D131" s="7">
+        <f>D116+D117</f>
+        <v/>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="5" t="inlineStr">
+        <is>
           <t>Balance Check</t>
         </is>
       </c>
-      <c r="B131" s="6" t="inlineStr"/>
-      <c r="C131" s="6" t="inlineStr"/>
-      <c r="D131" s="10">
+      <c r="B132" s="6" t="inlineStr"/>
+      <c r="C132" s="6" t="inlineStr"/>
+      <c r="D132" s="10">
         <f>IF(ABS(D113-D118)&lt;0.01,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
-    <row r="132"/>
     <row r="133"/>
-    <row r="134">
-      <c r="A134" s="3" t="inlineStr">
+    <row r="134"/>
+    <row r="135">
+      <c r="A135" s="3" t="inlineStr">
         <is>
           <t>EXIT CALCULATIONS</t>
         </is>
       </c>
-      <c r="B134" s="4" t="n"/>
-      <c r="C134" s="4" t="n"/>
-      <c r="D134" s="4" t="n"/>
-      <c r="E134" s="4" t="n"/>
-      <c r="F134" s="4" t="n"/>
-      <c r="G134" s="4" t="n"/>
-      <c r="H134" s="4" t="n"/>
-      <c r="I134" s="4" t="n"/>
-      <c r="J134" s="4" t="n"/>
-      <c r="K134" s="4" t="n"/>
-      <c r="L134" s="4" t="n"/>
-      <c r="M134" s="4" t="n"/>
-      <c r="N134" s="4" t="n"/>
-    </row>
-    <row r="135">
-      <c r="A135" s="5" t="inlineStr">
-        <is>
-          <t>Exit EV</t>
-        </is>
-      </c>
-      <c r="B135" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C135" s="6" t="inlineStr">
-        <is>
-          <t>Exit Multiple × Exit Yr EBITDA</t>
-        </is>
-      </c>
-      <c r="K135" s="18">
-        <f>$D$19*K74</f>
-        <v/>
-      </c>
+      <c r="B135" s="4" t="n"/>
+      <c r="C135" s="4" t="n"/>
+      <c r="D135" s="4" t="n"/>
+      <c r="E135" s="4" t="n"/>
+      <c r="F135" s="4" t="n"/>
+      <c r="G135" s="4" t="n"/>
+      <c r="H135" s="4" t="n"/>
+      <c r="I135" s="4" t="n"/>
+      <c r="J135" s="4" t="n"/>
+      <c r="K135" s="4" t="n"/>
+      <c r="L135" s="4" t="n"/>
+      <c r="M135" s="4" t="n"/>
+      <c r="N135" s="4" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="5" t="inlineStr">
         <is>
-          <t>Exit Debt Payoff</t>
+          <t>Exit EV</t>
         </is>
       </c>
       <c r="B136" s="6" t="inlineStr">
@@ -6450,18 +5983,15 @@
       </c>
       <c r="C136" s="6" t="inlineStr">
         <is>
-          <t>Ending Bal at Exit</t>
-        </is>
-      </c>
-      <c r="K136" s="18">
-        <f>K91</f>
-        <v/>
-      </c>
+          <t>Exit Multiple × Exit Yr EBITDA</t>
+        </is>
+      </c>
+      <c r="K136" s="18" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="5" t="inlineStr">
         <is>
-          <t>DSRA Release</t>
+          <t>Exit Debt Payoff</t>
         </is>
       </c>
       <c r="B137" s="6" t="inlineStr">
@@ -6471,239 +6001,211 @@
       </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
-          <t>DSRA Ending at Exit</t>
+          <t>Ending Bal at Exit</t>
         </is>
       </c>
       <c r="K137" s="18">
-        <f>K99</f>
+        <f>K91</f>
         <v/>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
         <is>
+          <t>DSRA Release</t>
+        </is>
+      </c>
+      <c r="B138" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C138" s="6" t="inlineStr">
+        <is>
+          <t>DSRA Ending at Exit</t>
+        </is>
+      </c>
+      <c r="K138" s="18">
+        <f>K99</f>
+        <v/>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="5" t="inlineStr">
+        <is>
           <t>Exit Equity Proceeds</t>
         </is>
       </c>
-      <c r="B138" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C138" s="6" t="inlineStr">
+      <c r="B139" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C139" s="6" t="inlineStr">
         <is>
           <t>Exit EV - Debt + DSRA</t>
         </is>
       </c>
-      <c r="K138" s="7">
-        <f>K123-K124+K125</f>
-        <v/>
-      </c>
-    </row>
-    <row r="139"/>
-    <row r="140">
-      <c r="A140" s="3" t="inlineStr">
+      <c r="K139" s="7" t="inlineStr"/>
+    </row>
+    <row r="140"/>
+    <row r="141">
+      <c r="A141" s="3" t="inlineStr">
         <is>
           <t>EQUITY RETURNS</t>
         </is>
       </c>
-      <c r="B140" s="4" t="n"/>
-      <c r="C140" s="4" t="n"/>
-      <c r="D140" s="4" t="n"/>
-      <c r="E140" s="4" t="n"/>
-      <c r="F140" s="4" t="n"/>
-      <c r="G140" s="4" t="n"/>
-      <c r="H140" s="4" t="n"/>
-      <c r="I140" s="4" t="n"/>
-      <c r="J140" s="4" t="n"/>
-      <c r="K140" s="4" t="n"/>
-      <c r="L140" s="4" t="n"/>
-      <c r="M140" s="4" t="n"/>
-      <c r="N140" s="4" t="n"/>
-    </row>
-    <row r="141">
-      <c r="A141" s="5" t="inlineStr">
-        <is>
-          <t>Equity Cash Flow</t>
-        </is>
-      </c>
-      <c r="B141" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C141" s="6" t="inlineStr"/>
-      <c r="D141" s="18">
-        <f>-D117</f>
-        <v/>
-      </c>
-      <c r="E141" s="18">
-        <f>E105</f>
-        <v/>
-      </c>
-      <c r="F141" s="18">
-        <f>F105</f>
-        <v/>
-      </c>
-      <c r="G141" s="18">
-        <f>G105</f>
-        <v/>
-      </c>
-      <c r="H141" s="18">
-        <f>H105</f>
-        <v/>
-      </c>
-      <c r="I141" s="18">
-        <f>I105</f>
-        <v/>
-      </c>
-      <c r="J141" s="18">
-        <f>J105</f>
-        <v/>
-      </c>
-      <c r="K141" s="18">
-        <f>K105+K126</f>
-        <v/>
-      </c>
-      <c r="L141" s="18">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="M141" s="18">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="N141" s="18">
-        <f>0</f>
-        <v/>
-      </c>
+      <c r="B141" s="4" t="n"/>
+      <c r="C141" s="4" t="n"/>
+      <c r="D141" s="4" t="n"/>
+      <c r="E141" s="4" t="n"/>
+      <c r="F141" s="4" t="n"/>
+      <c r="G141" s="4" t="n"/>
+      <c r="H141" s="4" t="n"/>
+      <c r="I141" s="4" t="n"/>
+      <c r="J141" s="4" t="n"/>
+      <c r="K141" s="4" t="n"/>
+      <c r="L141" s="4" t="n"/>
+      <c r="M141" s="4" t="n"/>
+      <c r="N141" s="4" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="5" t="inlineStr">
         <is>
-          <t>Levered IRR</t>
+          <t>Equity Cash Flow</t>
         </is>
       </c>
       <c r="B142" s="6" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>$mm</t>
         </is>
       </c>
       <c r="C142" s="6" t="inlineStr"/>
-      <c r="D142" s="31">
-        <f>IRR(D129:K129)</f>
-        <v/>
-      </c>
+      <c r="D142" s="18" t="inlineStr"/>
+      <c r="E142" s="18" t="inlineStr"/>
+      <c r="F142" s="18" t="inlineStr"/>
+      <c r="G142" s="18" t="inlineStr"/>
+      <c r="H142" s="18" t="inlineStr"/>
+      <c r="I142" s="18" t="inlineStr"/>
+      <c r="J142" s="18" t="inlineStr"/>
+      <c r="K142" s="18" t="inlineStr"/>
+      <c r="L142" s="18" t="inlineStr"/>
+      <c r="M142" s="18" t="inlineStr"/>
+      <c r="N142" s="18" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="5" t="inlineStr">
         <is>
+          <t>Levered IRR</t>
+        </is>
+      </c>
+      <c r="B143" s="6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C143" s="6" t="inlineStr"/>
+      <c r="D143" s="31" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="5" t="inlineStr">
+        <is>
           <t>MOIC</t>
         </is>
       </c>
-      <c r="B143" s="6" t="inlineStr">
+      <c r="B144" s="6" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="C143" s="6" t="inlineStr">
+      <c r="C144" s="6" t="inlineStr">
         <is>
           <t>Sum inflows / outflow</t>
         </is>
       </c>
-      <c r="D143" s="30">
-        <f>SUMIF(D129:K129,"&gt;0")/ABS(D129)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="144"/>
-    <row r="145">
-      <c r="A145" s="23" t="inlineStr">
+      <c r="D144" s="30" t="inlineStr"/>
+    </row>
+    <row r="145"/>
+    <row r="146">
+      <c r="A146" s="23" t="inlineStr">
         <is>
           <t>Unlevered Returns (for reference)</t>
         </is>
       </c>
-      <c r="B145" s="6" t="inlineStr"/>
-      <c r="C145" s="6" t="inlineStr"/>
-    </row>
-    <row r="146">
-      <c r="A146" s="5" t="inlineStr">
-        <is>
-          <t>Unlevered Cash Flow</t>
-        </is>
-      </c>
-      <c r="B146" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
+      <c r="B146" s="6" t="inlineStr"/>
       <c r="C146" s="6" t="inlineStr"/>
-      <c r="D146" s="18">
-        <f>-$D$17-D111</f>
-        <v/>
-      </c>
-      <c r="E146" s="18">
-        <f>E80</f>
-        <v/>
-      </c>
-      <c r="F146" s="18">
-        <f>F80</f>
-        <v/>
-      </c>
-      <c r="G146" s="18">
-        <f>G80</f>
-        <v/>
-      </c>
-      <c r="H146" s="18">
-        <f>H80</f>
-        <v/>
-      </c>
-      <c r="I146" s="18">
-        <f>I80</f>
-        <v/>
-      </c>
-      <c r="J146" s="18">
-        <f>J80</f>
-        <v/>
-      </c>
-      <c r="K146" s="18">
-        <f>K80+K123</f>
-        <v/>
-      </c>
-      <c r="L146" s="18">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="M146" s="18">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="N146" s="18">
-        <f>0</f>
-        <v/>
-      </c>
     </row>
     <row r="147">
       <c r="A147" s="5" t="inlineStr">
         <is>
+          <t>Unlevered Cash Flow</t>
+        </is>
+      </c>
+      <c r="B147" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C147" s="6" t="inlineStr"/>
+      <c r="D147" s="18">
+        <f>-$D$17-D111</f>
+        <v/>
+      </c>
+      <c r="E147" s="18">
+        <f>E80</f>
+        <v/>
+      </c>
+      <c r="F147" s="18">
+        <f>F80</f>
+        <v/>
+      </c>
+      <c r="G147" s="18">
+        <f>G80</f>
+        <v/>
+      </c>
+      <c r="H147" s="18">
+        <f>H80</f>
+        <v/>
+      </c>
+      <c r="I147" s="18">
+        <f>I80</f>
+        <v/>
+      </c>
+      <c r="J147" s="18">
+        <f>J80</f>
+        <v/>
+      </c>
+      <c r="K147" s="18">
+        <f>K80+K123</f>
+        <v/>
+      </c>
+      <c r="L147" s="18">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="M147" s="18">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="N147" s="18">
+        <f>0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="5" t="inlineStr">
+        <is>
           <t>Unlevered IRR</t>
         </is>
       </c>
-      <c r="B147" s="6" t="inlineStr">
+      <c r="B148" s="6" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="C147" s="6" t="inlineStr"/>
-      <c r="D147" s="31">
-        <f>IRR(D134:K134)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
+      <c r="C148" s="6" t="inlineStr"/>
+      <c r="D148" s="31" t="inlineStr"/>
+    </row>
   </sheetData>
   <dataValidations count="3">
     <dataValidation sqref="D7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
@@ -7122,8 +6624,6 @@
         <v/>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26"/>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
@@ -7224,7 +6724,6 @@
         <v>7</v>
       </c>
     </row>
-    <row r="32"/>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
@@ -7325,7 +6824,6 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="38"/>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
@@ -7426,7 +6924,6 @@
         <v>0.025</v>
       </c>
     </row>
-    <row r="44"/>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
@@ -7487,7 +6984,6 @@
         <v>15</v>
       </c>
     </row>
-    <row r="48"/>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
@@ -7628,7 +7124,6 @@
         <v>1.1</v>
       </c>
     </row>
-    <row r="56"/>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
@@ -7709,8 +7204,6 @@
         <v>15</v>
       </c>
     </row>
-    <row r="61"/>
-    <row r="62"/>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
@@ -7836,8 +7329,6 @@
         <v/>
       </c>
     </row>
-    <row r="69"/>
-    <row r="70"/>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
@@ -8029,7 +7520,6 @@
         <v/>
       </c>
     </row>
-    <row r="75"/>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
@@ -8197,7 +7687,6 @@
         <v/>
       </c>
     </row>
-    <row r="79"/>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
@@ -8492,7 +7981,6 @@
         <v/>
       </c>
     </row>
-    <row r="85"/>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
@@ -8546,8 +8034,6 @@
         <v/>
       </c>
     </row>
-    <row r="87"/>
-    <row r="88"/>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
@@ -8739,8 +8225,6 @@
         <v/>
       </c>
     </row>
-    <row r="93"/>
-    <row r="94"/>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
@@ -9327,7 +8811,6 @@
         <v/>
       </c>
     </row>
-    <row r="106"/>
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
@@ -9588,8 +9071,6 @@
         <v/>
       </c>
     </row>
-    <row r="112"/>
-    <row r="113"/>
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
@@ -9777,8 +9258,6 @@
         <v/>
       </c>
     </row>
-    <row r="118"/>
-    <row r="119"/>
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
@@ -9864,8 +9343,6 @@
         </is>
       </c>
     </row>
-    <row r="126"/>
-    <row r="127"/>
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
         <is>
@@ -9934,7 +9411,6 @@
         <v/>
       </c>
     </row>
-    <row r="132"/>
     <row r="133">
       <c r="A133" s="23" t="inlineStr">
         <is>
@@ -10012,8 +9488,6 @@
         <v/>
       </c>
     </row>
-    <row r="138"/>
-    <row r="139"/>
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
         <is>
@@ -10118,7 +9592,6 @@
         <v/>
       </c>
     </row>
-    <row r="145"/>
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
         <is>
@@ -10234,7 +9707,6 @@
         <v/>
       </c>
     </row>
-    <row r="150"/>
     <row r="151">
       <c r="A151" s="23" t="inlineStr">
         <is>

--- a/deliverables/deliverables-20260120-0030/Drill_1_CCGT.xlsx
+++ b/deliverables/deliverables-20260120-0030/Drill_1_CCGT.xlsx
@@ -27,7 +27,7 @@
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -97,6 +97,14 @@
       <color rgb="00C00000"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <color rgb="00666666"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -154,7 +162,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -233,6 +241,9 @@
     </xf>
     <xf numFmtId="4" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3173,7 +3184,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N148"/>
+  <dimension ref="A1:N160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -3255,21 +3266,45 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="57" t="inlineStr">
-        <is>
-          <t>═══ DRILL MODE: Key formulas blanked. Rebuild using Formula Logic hints in Column C. ═══</t>
-        </is>
-      </c>
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>═══ DRILL MODE - Fill in yellow cells ═══</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="n"/>
+      <c r="C2" s="4" t="n"/>
+      <c r="D2" s="4" t="n"/>
+      <c r="E2" s="4" t="n"/>
+      <c r="F2" s="4" t="n"/>
+      <c r="G2" s="4" t="n"/>
+      <c r="H2" s="4" t="n"/>
+      <c r="I2" s="4" t="n"/>
+      <c r="J2" s="4" t="n"/>
+      <c r="K2" s="4" t="n"/>
+      <c r="L2" s="4" t="n"/>
+      <c r="M2" s="4" t="n"/>
+      <c r="N2" s="4" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>═══ AUDIT STRIP ═══</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Entry EV</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Purchase price for asset</t>
+        </is>
+      </c>
+      <c r="D3" s="7">
+        <f>$D$28</f>
+        <v/>
+      </c>
       <c r="E3" s="4" t="n"/>
       <c r="F3" s="4" t="n"/>
       <c r="G3" s="4" t="n"/>
@@ -3278,13 +3313,17 @@
       <c r="J3" s="4" t="n"/>
       <c r="K3" s="4" t="n"/>
       <c r="L3" s="4" t="n"/>
-      <c r="M3" s="4" t="n"/>
+      <c r="M3" s="58" t="inlineStr">
+        <is>
+          <t>IRR Sensitivity:</t>
+        </is>
+      </c>
       <c r="N3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Entry EV</t>
+          <t>Y1 EBITDA</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -3292,235 +3331,259 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr"/>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Revenue minus OpEx</t>
+        </is>
+      </c>
       <c r="D4" s="7">
-        <f>$D$17</f>
-        <v/>
+        <f>E86</f>
+        <v/>
+      </c>
+      <c r="M4" s="59" t="inlineStr">
+        <is>
+          <t>+/- 5% Entry → ~+/- 1% IRR</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Y1 EBITDA</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr"/>
-      <c r="D5" s="7" t="inlineStr"/>
+      <c r="A5" s="38" t="inlineStr">
+        <is>
+          <t>═══════════ CONTROL PANEL ═══════════</t>
+        </is>
+      </c>
+      <c r="B5" s="49" t="n"/>
+      <c r="C5" s="49" t="n"/>
+      <c r="D5" s="49" t="n"/>
+      <c r="M5" s="59" t="inlineStr">
+        <is>
+          <t>+/- 0.5x Exit → ~+/- 1.5% IRR</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="38" t="inlineStr">
-        <is>
-          <t>═══════════ CONTROL PANEL ═══════════</t>
-        </is>
-      </c>
+      <c r="A6" s="49" t="n"/>
       <c r="B6" s="49" t="n"/>
       <c r="C6" s="49" t="n"/>
       <c r="D6" s="49" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="49" t="n"/>
+      <c r="A7" s="50" t="inlineStr">
+        <is>
+          <t>REVENUE</t>
+        </is>
+      </c>
       <c r="B7" s="49" t="n"/>
       <c r="C7" s="49" t="n"/>
       <c r="D7" s="49" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="50" t="inlineStr">
-        <is>
-          <t>REVENUE</t>
+      <c r="A8" s="34" t="inlineStr">
+        <is>
+          <t>Revenue Mode</t>
         </is>
       </c>
       <c r="B8" s="49" t="n"/>
-      <c r="C8" s="49" t="n"/>
-      <c r="D8" s="49" t="n"/>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Merchant / Contracted / Hybrid</t>
+        </is>
+      </c>
+      <c r="D8" s="47" t="inlineStr">
+        <is>
+          <t>Merchant</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="34" t="inlineStr">
         <is>
-          <t>Revenue Mode</t>
+          <t>Contract End Year</t>
         </is>
       </c>
       <c r="B9" s="49" t="n"/>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Merchant / Contracted / Hybrid</t>
-        </is>
-      </c>
-      <c r="D9" s="47" t="inlineStr">
-        <is>
-          <t>Merchant</t>
-        </is>
+          <t>0 = pure merchant; else year PPA ends</t>
+        </is>
+      </c>
+      <c r="D9" s="47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="34" t="inlineStr">
-        <is>
-          <t>Contract End Year</t>
-        </is>
-      </c>
+      <c r="A10" s="49" t="n"/>
       <c r="B10" s="49" t="n"/>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>0 = pure merchant; else year PPA ends</t>
-        </is>
-      </c>
-      <c r="D10" s="47" t="n">
-        <v>0</v>
-      </c>
+      <c r="C10" s="49" t="n"/>
+      <c r="D10" s="49" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="49" t="n"/>
+      <c r="A11" s="50" t="inlineStr">
+        <is>
+          <t>TIMING</t>
+        </is>
+      </c>
       <c r="B11" s="49" t="n"/>
       <c r="C11" s="49" t="n"/>
       <c r="D11" s="49" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="50" t="inlineStr">
-        <is>
-          <t>TIMING</t>
+      <c r="A12" s="34" t="inlineStr">
+        <is>
+          <t>Exit Year</t>
         </is>
       </c>
       <c r="B12" s="49" t="n"/>
-      <c r="C12" s="49" t="n"/>
-      <c r="D12" s="49" t="n"/>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>5 / 7 / 10</t>
+        </is>
+      </c>
+      <c r="D12" s="47" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="34" t="inlineStr">
         <is>
-          <t>Exit Year</t>
+          <t>Tax Credit End Year</t>
         </is>
       </c>
       <c r="B13" s="49" t="n"/>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>5 / 7 / 10</t>
+          <t>0 = N/A; else last year of PTC/ITC</t>
         </is>
       </c>
       <c r="D13" s="47" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="34" t="inlineStr">
-        <is>
-          <t>Tax Credit End Year</t>
-        </is>
-      </c>
+      <c r="A14" s="49" t="n"/>
       <c r="B14" s="49" t="n"/>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>0 = N/A; else last year of PTC/ITC</t>
-        </is>
-      </c>
-      <c r="D14" s="47" t="n">
-        <v>0</v>
-      </c>
+      <c r="C14" s="49" t="n"/>
+      <c r="D14" s="49" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="49" t="n"/>
+      <c r="A15" s="50" t="inlineStr">
+        <is>
+          <t>DEBT</t>
+        </is>
+      </c>
       <c r="B15" s="49" t="n"/>
       <c r="C15" s="49" t="n"/>
-      <c r="D15" s="49" t="n"/>
+      <c r="D15" s="51" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="50" t="inlineStr">
-        <is>
-          <t>DEBT</t>
+      <c r="A16" s="34" t="inlineStr">
+        <is>
+          <t>Debt Sweep</t>
         </is>
       </c>
       <c r="B16" s="49" t="n"/>
-      <c r="C16" s="49" t="n"/>
-      <c r="D16" s="51" t="n"/>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>ON / OFF (for sweep assets)</t>
+        </is>
+      </c>
+      <c r="D16" s="33" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="34" t="inlineStr">
         <is>
-          <t>Debt Sweep</t>
+          <t>Sweep %</t>
         </is>
       </c>
       <c r="B17" s="49" t="n"/>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>ON / OFF (for sweep assets)</t>
-        </is>
-      </c>
-      <c r="D17" s="33" t="inlineStr">
-        <is>
-          <t>ON</t>
+          <t>Active when Sweep = ON</t>
+        </is>
+      </c>
+      <c r="D17" s="32" t="inlineStr">
+        <is>
+          <t>75%</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="34" t="inlineStr">
-        <is>
-          <t>Sweep %</t>
-        </is>
-      </c>
+      <c r="A18" s="49" t="n"/>
       <c r="B18" s="49" t="n"/>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>Active when Sweep = ON</t>
-        </is>
-      </c>
-      <c r="D18" s="32" t="inlineStr">
-        <is>
-          <t>75%</t>
-        </is>
-      </c>
+      <c r="C18" s="49" t="n"/>
+      <c r="D18" s="52" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="49" t="n"/>
+      <c r="A19" s="50" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
       <c r="B19" s="49" t="n"/>
       <c r="C19" s="49" t="n"/>
-      <c r="D19" s="52" t="n"/>
+      <c r="D19" s="53" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="50" t="inlineStr">
-        <is>
-          <t>OTHER</t>
+      <c r="A20" s="34" t="inlineStr">
+        <is>
+          <t>Carbon Region</t>
         </is>
       </c>
       <c r="B20" s="49" t="n"/>
-      <c r="C20" s="49" t="n"/>
-      <c r="D20" s="53" t="n"/>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>None / CARB / RGGI (thermal only)</t>
+        </is>
+      </c>
+      <c r="D20" s="47" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="34" t="inlineStr">
-        <is>
-          <t>Carbon Region</t>
-        </is>
-      </c>
+      <c r="A21" s="54" t="inlineStr">
+        <is>
+          <t>Exit Method</t>
+        </is>
+      </c>
+      <c r="B21" s="49" t="n"/>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>None / CARB / RGGI (thermal only)</t>
+          <t>Multiple / DCF</t>
         </is>
       </c>
       <c r="D21" s="47" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
+          <t>Multiple</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="n"/>
+      <c r="F21" s="4" t="n"/>
+      <c r="G21" s="4" t="n"/>
+      <c r="H21" s="4" t="n"/>
+      <c r="I21" s="4" t="n"/>
+      <c r="J21" s="4" t="n"/>
+      <c r="K21" s="4" t="n"/>
+      <c r="L21" s="4" t="n"/>
+      <c r="M21" s="4" t="n"/>
+      <c r="N21" s="4" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="54" t="inlineStr">
-        <is>
-          <t>Exit Method</t>
-        </is>
-      </c>
-      <c r="B22" s="49" t="n"/>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>Multiple / DCF</t>
-        </is>
-      </c>
-      <c r="D22" s="47" t="inlineStr">
-        <is>
-          <t>Multiple</t>
-        </is>
+      <c r="A22" s="38" t="inlineStr">
+        <is>
+          <t>════════════════════════════════════</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="10">
+        <f>D132</f>
+        <v/>
       </c>
       <c r="E22" s="4" t="n"/>
       <c r="F22" s="4" t="n"/>
@@ -3534,52 +3597,81 @@
       <c r="N22" s="4" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="38" t="inlineStr">
-        <is>
-          <t>════════════════════════════════════</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr"/>
-      <c r="C23" s="6" t="inlineStr"/>
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Debt Payoff Y7</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="n"/>
       <c r="D23" s="10">
-        <f>D119</f>
+        <f>IF(K103&lt;1,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Debt Payoff Y7</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="inlineStr"/>
-      <c r="C24" s="6" t="inlineStr"/>
+          <t>Min DSCR ≥ 1.25x</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n"/>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>CFADS / Debt Service</t>
+        </is>
+      </c>
       <c r="D24" s="10">
-        <f>IF(K91&lt;1,"PASS","FAIL")</f>
+        <f>IF(MIN(E104:K104)&gt;=1.25,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>Min DSCR ≥ 1.25x</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="inlineStr"/>
-      <c r="C25" s="6" t="inlineStr"/>
-      <c r="D25" s="10" t="inlineStr"/>
+      <c r="A25" s="5" t="n"/>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="10" t="n"/>
     </row>
     <row r="26"/>
-    <row r="27"/>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>TRANSACTION INPUTS</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="n"/>
+      <c r="C27" s="4" t="n"/>
+      <c r="D27" s="4" t="n"/>
+      <c r="E27" s="4" t="n"/>
+      <c r="F27" s="4" t="n"/>
+      <c r="G27" s="4" t="n"/>
+      <c r="H27" s="4" t="n"/>
+      <c r="I27" s="4" t="n"/>
+      <c r="J27" s="4" t="n"/>
+      <c r="K27" s="4" t="n"/>
+      <c r="L27" s="4" t="n"/>
+      <c r="M27" s="4" t="n"/>
+      <c r="N27" s="4" t="n"/>
+    </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>TRANSACTION INPUTS</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="n"/>
-      <c r="C28" s="4" t="n"/>
-      <c r="D28" s="4" t="n"/>
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Entry EV</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>Purchase price</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="n">
+        <v>520</v>
+      </c>
       <c r="E28" s="4" t="n"/>
       <c r="F28" s="4" t="n"/>
       <c r="G28" s="4" t="n"/>
@@ -3594,93 +3686,108 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Entry EV</t>
+          <t>Transaction Fees</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>$mm</t>
+          <t>%</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Purchase price</t>
-        </is>
-      </c>
-      <c r="D29" s="11" t="n">
-        <v>520</v>
+          <t>Legal, advisory, financing</t>
+        </is>
+      </c>
+      <c r="D29" s="32" t="n">
+        <v>0.015</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Transaction Fees</t>
+          <t>Exit Multiple</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>x</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>Legal, advisory, financing</t>
-        </is>
-      </c>
-      <c r="D30" s="32" t="n">
-        <v>0.015</v>
+          <t>On exit year EBITDA</t>
+        </is>
+      </c>
+      <c r="D30" s="33" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>Exit Multiple</t>
+          <t>Exit Year</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>On exit year EBITDA</t>
-        </is>
-      </c>
-      <c r="D31" s="33" t="n">
+          <t>Hold period</t>
+        </is>
+      </c>
+      <c r="D31" s="14" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>Exit Year</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="C32" s="6" t="inlineStr">
-        <is>
-          <t>Hold period</t>
-        </is>
-      </c>
-      <c r="D32" s="14" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="33"/>
+      <c r="A32" s="5" t="n"/>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="14" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>ASSET INPUTS</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="n"/>
+      <c r="C33" s="4" t="n"/>
+      <c r="D33" s="4" t="n"/>
+      <c r="E33" s="4" t="n"/>
+      <c r="F33" s="4" t="n"/>
+      <c r="G33" s="4" t="n"/>
+      <c r="H33" s="4" t="n"/>
+      <c r="I33" s="4" t="n"/>
+      <c r="J33" s="4" t="n"/>
+      <c r="K33" s="4" t="n"/>
+      <c r="L33" s="4" t="n"/>
+      <c r="M33" s="4" t="n"/>
+      <c r="N33" s="4" t="n"/>
+    </row>
     <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>ASSET INPUTS</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="n"/>
-      <c r="C34" s="4" t="n"/>
-      <c r="D34" s="4" t="n"/>
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>Capacity</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>MW</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>Nameplate rating</t>
+        </is>
+      </c>
+      <c r="D34" s="14" t="n">
+        <v>365</v>
+      </c>
       <c r="E34" s="4" t="n"/>
       <c r="F34" s="4" t="n"/>
       <c r="G34" s="4" t="n"/>
@@ -3695,47 +3802,47 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>Capacity</t>
+          <t>Heat Rate</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>MW</t>
+          <t>Btu/kWh</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>Nameplate rating</t>
+          <t>Efficiency (lower = better)</t>
         </is>
       </c>
       <c r="D35" s="14" t="n">
-        <v>365</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>Heat Rate</t>
+          <t>Capacity Factor</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>Btu/kWh</t>
+          <t>%</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>Efficiency (lower = better)</t>
-        </is>
-      </c>
-      <c r="D36" s="14" t="n">
-        <v>7000</v>
+          <t>Annual utilization</t>
+        </is>
+      </c>
+      <c r="D36" s="32" t="n">
+        <v>0.55</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>Capacity Factor</t>
+          <t>Forced Outage Rate</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
@@ -3745,43 +3852,58 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>Annual utilization</t>
+          <t>Unplanned downtime</t>
         </is>
       </c>
       <c r="D37" s="32" t="n">
-        <v>0.55</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>Forced Outage Rate</t>
-        </is>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C38" s="6" t="inlineStr">
-        <is>
-          <t>Unplanned downtime</t>
-        </is>
-      </c>
-      <c r="D38" s="32" t="n">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="39"/>
+      <c r="A38" s="5" t="n"/>
+      <c r="B38" s="6" t="n"/>
+      <c r="C38" s="6" t="n"/>
+      <c r="D38" s="32" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>PRICING INPUTS</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="n"/>
+      <c r="C39" s="4" t="n"/>
+      <c r="D39" s="4" t="n"/>
+      <c r="E39" s="4" t="n"/>
+      <c r="F39" s="4" t="n"/>
+      <c r="G39" s="4" t="n"/>
+      <c r="H39" s="4" t="n"/>
+      <c r="I39" s="4" t="n"/>
+      <c r="J39" s="4" t="n"/>
+      <c r="K39" s="4" t="n"/>
+      <c r="L39" s="4" t="n"/>
+      <c r="M39" s="4" t="n"/>
+      <c r="N39" s="4" t="n"/>
+    </row>
     <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>PRICING INPUTS</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="n"/>
-      <c r="C40" s="4" t="n"/>
-      <c r="D40" s="4" t="n"/>
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>Power Price Y1</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>$/MWh</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>Energy clearing price</t>
+        </is>
+      </c>
+      <c r="D40" s="11" t="n">
+        <v>48</v>
+      </c>
       <c r="E40" s="4" t="n"/>
       <c r="F40" s="4" t="n"/>
       <c r="G40" s="4" t="n"/>
@@ -3796,93 +3918,108 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>Power Price Y1</t>
+          <t>Capacity Price Y1</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>$/MWh</t>
+          <t>$/kW-yr</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>Energy clearing price</t>
+          <t>ICAP/RPM auction result</t>
         </is>
       </c>
       <c r="D41" s="11" t="n">
-        <v>48</v>
+        <v>110</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>Capacity Price Y1</t>
+          <t>Gas Price Y1</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>$/kW-yr</t>
+          <t>$/mmBtu</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>ICAP/RPM auction result</t>
-        </is>
-      </c>
-      <c r="D42" s="11" t="n">
-        <v>110</v>
+          <t>Henry Hub + basis</t>
+        </is>
+      </c>
+      <c r="D42" s="15" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>Gas Price Y1</t>
+          <t>Escalation</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>$/mmBtu</t>
+          <t>%/yr</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>Henry Hub + basis</t>
-        </is>
-      </c>
-      <c r="D43" s="15" t="n">
-        <v>3</v>
+          <t>Applied to all prices/costs</t>
+        </is>
+      </c>
+      <c r="D43" s="32" t="n">
+        <v>0.025</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>Escalation</t>
-        </is>
-      </c>
-      <c r="B44" s="6" t="inlineStr">
-        <is>
-          <t>%/yr</t>
-        </is>
-      </c>
-      <c r="C44" s="6" t="inlineStr">
-        <is>
-          <t>Applied to all prices/costs</t>
-        </is>
-      </c>
-      <c r="D44" s="32" t="n">
-        <v>0.025</v>
-      </c>
-    </row>
-    <row r="45"/>
+      <c r="A44" s="5" t="n"/>
+      <c r="B44" s="6" t="n"/>
+      <c r="C44" s="6" t="n"/>
+      <c r="D44" s="32" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>COST INPUTS</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="n"/>
+      <c r="C45" s="4" t="n"/>
+      <c r="D45" s="4" t="n"/>
+      <c r="E45" s="4" t="n"/>
+      <c r="F45" s="4" t="n"/>
+      <c r="G45" s="4" t="n"/>
+      <c r="H45" s="4" t="n"/>
+      <c r="I45" s="4" t="n"/>
+      <c r="J45" s="4" t="n"/>
+      <c r="K45" s="4" t="n"/>
+      <c r="L45" s="4" t="n"/>
+      <c r="M45" s="4" t="n"/>
+      <c r="N45" s="4" t="n"/>
+    </row>
     <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>COST INPUTS</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="n"/>
-      <c r="C46" s="4" t="n"/>
-      <c r="D46" s="4" t="n"/>
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>VOM</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>$/MWh</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>Variable O&amp;M</t>
+        </is>
+      </c>
+      <c r="D46" s="15" t="n">
+        <v>3.5</v>
+      </c>
       <c r="E46" s="4" t="n"/>
       <c r="F46" s="4" t="n"/>
       <c r="G46" s="4" t="n"/>
@@ -3897,53 +4034,68 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>VOM</t>
+          <t>FOM</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>$/MWh</t>
+          <t>$/kW-yr</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>Variable O&amp;M</t>
+          <t>Fixed O&amp;M</t>
         </is>
       </c>
       <c r="D47" s="15" t="n">
-        <v>3.5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>FOM</t>
-        </is>
-      </c>
-      <c r="B48" s="6" t="inlineStr">
-        <is>
-          <t>$/kW-yr</t>
-        </is>
-      </c>
-      <c r="C48" s="6" t="inlineStr">
-        <is>
-          <t>Fixed O&amp;M</t>
-        </is>
-      </c>
-      <c r="D48" s="15" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="49"/>
+      <c r="A48" s="5" t="n"/>
+      <c r="B48" s="6" t="n"/>
+      <c r="C48" s="6" t="n"/>
+      <c r="D48" s="15" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>FINANCING INPUTS</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="n"/>
+      <c r="C49" s="4" t="n"/>
+      <c r="D49" s="4" t="n"/>
+      <c r="E49" s="4" t="n"/>
+      <c r="F49" s="4" t="n"/>
+      <c r="G49" s="4" t="n"/>
+      <c r="H49" s="4" t="n"/>
+      <c r="I49" s="4" t="n"/>
+      <c r="J49" s="4" t="n"/>
+      <c r="K49" s="4" t="n"/>
+      <c r="L49" s="4" t="n"/>
+      <c r="M49" s="4" t="n"/>
+      <c r="N49" s="4" t="n"/>
+    </row>
     <row r="50">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t>FINANCING INPUTS</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="n"/>
-      <c r="C50" s="4" t="n"/>
-      <c r="D50" s="4" t="n"/>
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>Leverage</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>Debt / Entry EV</t>
+        </is>
+      </c>
+      <c r="D50" s="32" t="n">
+        <v>0.45</v>
+      </c>
       <c r="E50" s="4" t="n"/>
       <c r="F50" s="4" t="n"/>
       <c r="G50" s="4" t="n"/>
@@ -3958,7 +4110,7 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>Leverage</t>
+          <t>Interest Rate</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
@@ -3968,123 +4120,138 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>Debt / Entry EV</t>
+          <t>All-in borrowing cost</t>
         </is>
       </c>
       <c r="D51" s="32" t="n">
-        <v>0.45</v>
+        <v>0.065</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>Interest Rate</t>
+          <t>Debt Tenor</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>years</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>All-in borrowing cost</t>
-        </is>
-      </c>
-      <c r="D52" s="32" t="n">
-        <v>0.065</v>
+          <t>Amortization period</t>
+        </is>
+      </c>
+      <c r="D52" s="14" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>Debt Tenor</t>
+          <t>DSRA Months</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>years</t>
+          <t>months</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>Amortization period</t>
+          <t>Debt service reserve</t>
         </is>
       </c>
       <c r="D53" s="14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>DSRA Months</t>
+          <t>Cash Sweep %</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>months</t>
+          <t>%</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>Debt service reserve</t>
-        </is>
-      </c>
-      <c r="D54" s="14" t="n">
-        <v>6</v>
+          <t>Mandatory excess CF prepay</t>
+        </is>
+      </c>
+      <c r="D54" s="32" t="n">
+        <v>0.75</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>Cash Sweep %</t>
+          <t>Lock-up DSCR</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>Distribution threshold</t>
+        </is>
+      </c>
+      <c r="D55" s="33" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="n"/>
+      <c r="B56" s="6" t="n"/>
+      <c r="C56" s="6" t="n"/>
+      <c r="D56" s="33" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>TAX INPUTS</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="n"/>
+      <c r="C57" s="4" t="n"/>
+      <c r="D57" s="4" t="n"/>
+      <c r="E57" s="4" t="n"/>
+      <c r="F57" s="4" t="n"/>
+      <c r="G57" s="4" t="n"/>
+      <c r="H57" s="4" t="n"/>
+      <c r="I57" s="4" t="n"/>
+      <c r="J57" s="4" t="n"/>
+      <c r="K57" s="4" t="n"/>
+      <c r="L57" s="4" t="n"/>
+      <c r="M57" s="4" t="n"/>
+      <c r="N57" s="4" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>Tax Rate</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
           <t>%</t>
         </is>
       </c>
-      <c r="C55" s="6" t="inlineStr">
-        <is>
-          <t>Mandatory excess CF prepay</t>
-        </is>
-      </c>
-      <c r="D55" s="32" t="n">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="5" t="inlineStr">
-        <is>
-          <t>Lock-up DSCR</t>
-        </is>
-      </c>
-      <c r="B56" s="6" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="C56" s="6" t="inlineStr">
-        <is>
-          <t>Distribution threshold</t>
-        </is>
-      </c>
-      <c r="D56" s="33" t="n">
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="57"/>
-    <row r="58">
-      <c r="A58" s="3" t="inlineStr">
-        <is>
-          <t>TAX INPUTS</t>
-        </is>
-      </c>
-      <c r="B58" s="4" t="n"/>
-      <c r="C58" s="4" t="n"/>
-      <c r="D58" s="4" t="n"/>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>Blended federal + state</t>
+        </is>
+      </c>
+      <c r="D58" s="32" t="n">
+        <v>0.25</v>
+      </c>
       <c r="E58" s="4" t="n"/>
       <c r="F58" s="4" t="n"/>
       <c r="G58" s="4" t="n"/>
@@ -4099,7 +4266,7 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>Tax Rate</t>
+          <t>Depreciable Basis</t>
         </is>
       </c>
       <c r="B59" s="6" t="inlineStr">
@@ -4109,64 +4276,80 @@
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>Blended federal + state</t>
+          <t>% of EV for depreciation</t>
         </is>
       </c>
       <c r="D59" s="32" t="n">
-        <v>0.25</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>Depreciable Basis</t>
+          <t>Depreciation Life</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>years</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>% of EV for depreciation</t>
-        </is>
-      </c>
-      <c r="D60" s="32" t="n">
-        <v>0.85</v>
+          <t>Straight-line</t>
+        </is>
+      </c>
+      <c r="D60" s="14" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>Depreciation Life</t>
-        </is>
-      </c>
-      <c r="B61" s="6" t="inlineStr">
-        <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="C61" s="6" t="inlineStr">
-        <is>
-          <t>Straight-line</t>
-        </is>
-      </c>
-      <c r="D61" s="14" t="n">
-        <v>15</v>
-      </c>
+      <c r="A61" s="5" t="n"/>
+      <c r="B61" s="6" t="n"/>
+      <c r="C61" s="6" t="n"/>
+      <c r="D61" s="14" t="n"/>
     </row>
     <row r="62"/>
-    <row r="63"/>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>CALCULATED ITEMS</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="n"/>
+      <c r="C63" s="4" t="n"/>
+      <c r="D63" s="4" t="n"/>
+      <c r="E63" s="4" t="n"/>
+      <c r="F63" s="4" t="n"/>
+      <c r="G63" s="4" t="n"/>
+      <c r="H63" s="4" t="n"/>
+      <c r="I63" s="4" t="n"/>
+      <c r="J63" s="4" t="n"/>
+      <c r="K63" s="4" t="n"/>
+      <c r="L63" s="4" t="n"/>
+      <c r="M63" s="4" t="n"/>
+      <c r="N63" s="4" t="n"/>
+    </row>
     <row r="64">
-      <c r="A64" s="3" t="inlineStr">
-        <is>
-          <t>CALCULATED ITEMS</t>
-        </is>
-      </c>
-      <c r="B64" s="4" t="n"/>
-      <c r="C64" s="4" t="n"/>
-      <c r="D64" s="4" t="n"/>
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>UCAP (Unforced Capacity)</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>MW</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>Capacity × (1 - FOR)</t>
+        </is>
+      </c>
+      <c r="D64" s="16">
+        <f>$D$34*(1-$D$37)</f>
+        <v/>
+      </c>
       <c r="E64" s="4" t="n"/>
       <c r="F64" s="4" t="n"/>
       <c r="G64" s="4" t="n"/>
@@ -4181,49 +4364,49 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>UCAP (Unforced Capacity)</t>
+          <t>Annual Generation</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>MW</t>
+          <t>MWh</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>Capacity × (1 - FOR)</t>
-        </is>
-      </c>
-      <c r="D65" s="16">
-        <f>$D$23*(1-$D$26)</f>
+          <t>Capacity × CF × 8,760</t>
+        </is>
+      </c>
+      <c r="D65" s="17">
+        <f>$D$34*$D$36*8760*(1-$D$37)</f>
         <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>Annual Generation</t>
+          <t>Debt Amount</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>MWh</t>
+          <t>$mm</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>Capacity × CF × 8,760</t>
-        </is>
-      </c>
-      <c r="D66" s="17">
-        <f>$D$23*$D$25*8760</f>
+          <t>Entry EV × Leverage</t>
+        </is>
+      </c>
+      <c r="D66" s="18">
+        <f>$D$28*$D$50</f>
         <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>Debt Amount</t>
+          <t>Annual Depreciation</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
@@ -4233,84 +4416,129 @@
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>Entry EV × Leverage</t>
+          <t>EV × Basis / Life</t>
         </is>
       </c>
       <c r="D67" s="18">
-        <f>$D$17*$D$39</f>
+        <f>$D$28*$D$59/$D$60</f>
         <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>Annual Depreciation</t>
+          <t>Scheduled Principal</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>$mm</t>
+          <t>$mm/yr</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>EV × Basis / Life</t>
+          <t>Debt / Tenor</t>
         </is>
       </c>
       <c r="D68" s="18">
-        <f>$D$17*$D$48/$D$49</f>
+        <f>$D$66/$D$52</f>
         <v/>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="5" t="inlineStr">
-        <is>
-          <t>Scheduled Principal</t>
-        </is>
-      </c>
-      <c r="B69" s="6" t="inlineStr">
-        <is>
-          <t>$mm/yr</t>
-        </is>
-      </c>
-      <c r="C69" s="6" t="inlineStr">
-        <is>
-          <t>Debt / Tenor</t>
-        </is>
-      </c>
-      <c r="D69" s="18" t="inlineStr"/>
+      <c r="A69" s="5" t="n"/>
+      <c r="B69" s="6" t="n"/>
+      <c r="C69" s="6" t="n"/>
+      <c r="D69" s="18" t="n"/>
     </row>
     <row r="70"/>
-    <row r="71"/>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>OPERATING MODEL</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="n"/>
+      <c r="C71" s="4" t="n"/>
+      <c r="D71" s="4" t="n"/>
+      <c r="E71" s="4" t="n"/>
+      <c r="F71" s="4" t="n"/>
+      <c r="G71" s="4" t="n"/>
+      <c r="H71" s="4" t="n"/>
+      <c r="I71" s="4" t="n"/>
+      <c r="J71" s="4" t="n"/>
+      <c r="K71" s="4" t="n"/>
+      <c r="L71" s="4" t="n"/>
+      <c r="M71" s="4" t="n"/>
+      <c r="N71" s="4" t="n"/>
+    </row>
     <row r="72">
-      <c r="A72" s="3" t="inlineStr">
-        <is>
-          <t>OPERATING MODEL</t>
-        </is>
-      </c>
-      <c r="B72" s="4" t="n"/>
-      <c r="C72" s="4" t="n"/>
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>Power Price</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>$/MWh</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>Escalated</t>
+        </is>
+      </c>
       <c r="D72" s="4" t="n"/>
-      <c r="E72" s="4" t="n"/>
-      <c r="F72" s="4" t="n"/>
-      <c r="G72" s="4" t="n"/>
-      <c r="H72" s="4" t="n"/>
-      <c r="I72" s="4" t="n"/>
-      <c r="J72" s="4" t="n"/>
-      <c r="K72" s="4" t="n"/>
-      <c r="L72" s="4" t="n"/>
-      <c r="M72" s="4" t="n"/>
-      <c r="N72" s="4" t="n"/>
+      <c r="E72" s="18">
+        <f>$D$40*(1+$D$43)^(1-1)</f>
+        <v/>
+      </c>
+      <c r="F72" s="18">
+        <f>$D$40*(1+$D$43)^(2-1)</f>
+        <v/>
+      </c>
+      <c r="G72" s="18">
+        <f>$D$40*(1+$D$43)^(3-1)</f>
+        <v/>
+      </c>
+      <c r="H72" s="18">
+        <f>$D$40*(1+$D$43)^(4-1)</f>
+        <v/>
+      </c>
+      <c r="I72" s="18">
+        <f>$D$40*(1+$D$43)^(5-1)</f>
+        <v/>
+      </c>
+      <c r="J72" s="18">
+        <f>$D$40*(1+$D$43)^(6-1)</f>
+        <v/>
+      </c>
+      <c r="K72" s="18">
+        <f>$D$40*(1+$D$43)^(7-1)</f>
+        <v/>
+      </c>
+      <c r="L72" s="18">
+        <f>$D$40*(1+$D$43)^(8-1)</f>
+        <v/>
+      </c>
+      <c r="M72" s="18">
+        <f>$D$40*(1+$D$43)^(9-1)</f>
+        <v/>
+      </c>
+      <c r="N72" s="18">
+        <f>$D$40*(1+$D$43)^(10-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>Power Price</t>
+          <t>Capacity Price</t>
         </is>
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>$/MWh</t>
+          <t>$/kW-yr</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
@@ -4319,55 +4547,55 @@
         </is>
       </c>
       <c r="E73" s="18">
-        <f>$D$29*(1+$D$32)^(1-1)</f>
+        <f>$D$41*(1+$D$43)^(1-1)</f>
         <v/>
       </c>
       <c r="F73" s="18">
-        <f>$D$29*(1+$D$32)^(2-1)</f>
+        <f>$D$41*(1+$D$43)^(2-1)</f>
         <v/>
       </c>
       <c r="G73" s="18">
-        <f>$D$29*(1+$D$32)^(3-1)</f>
+        <f>$D$41*(1+$D$43)^(3-1)</f>
         <v/>
       </c>
       <c r="H73" s="18">
-        <f>$D$29*(1+$D$32)^(4-1)</f>
+        <f>$D$41*(1+$D$43)^(4-1)</f>
         <v/>
       </c>
       <c r="I73" s="18">
-        <f>$D$29*(1+$D$32)^(5-1)</f>
+        <f>$D$41*(1+$D$43)^(5-1)</f>
         <v/>
       </c>
       <c r="J73" s="18">
-        <f>$D$29*(1+$D$32)^(6-1)</f>
+        <f>$D$41*(1+$D$43)^(6-1)</f>
         <v/>
       </c>
       <c r="K73" s="18">
-        <f>$D$29*(1+$D$32)^(7-1)</f>
+        <f>$D$41*(1+$D$43)^(7-1)</f>
         <v/>
       </c>
       <c r="L73" s="18">
-        <f>$D$29*(1+$D$32)^(8-1)</f>
+        <f>$D$41*(1+$D$43)^(8-1)</f>
         <v/>
       </c>
       <c r="M73" s="18">
-        <f>$D$29*(1+$D$32)^(9-1)</f>
+        <f>$D$41*(1+$D$43)^(9-1)</f>
         <v/>
       </c>
       <c r="N73" s="18">
-        <f>$D$29*(1+$D$32)^(10-1)</f>
+        <f>$D$41*(1+$D$43)^(10-1)</f>
         <v/>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>Capacity Price</t>
+          <t>Gas Price</t>
         </is>
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>$/kW-yr</t>
+          <t>$/mmBtu</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
@@ -4375,109 +4603,93 @@
           <t>Escalated</t>
         </is>
       </c>
-      <c r="E74" s="18">
-        <f>$D$30*(1+$D$32)^(1-1)</f>
-        <v/>
-      </c>
-      <c r="F74" s="18">
-        <f>$D$30*(1+$D$32)^(2-1)</f>
-        <v/>
-      </c>
-      <c r="G74" s="18">
-        <f>$D$30*(1+$D$32)^(3-1)</f>
-        <v/>
-      </c>
-      <c r="H74" s="18">
-        <f>$D$30*(1+$D$32)^(4-1)</f>
-        <v/>
-      </c>
-      <c r="I74" s="18">
-        <f>$D$30*(1+$D$32)^(5-1)</f>
-        <v/>
-      </c>
-      <c r="J74" s="18">
-        <f>$D$30*(1+$D$32)^(6-1)</f>
-        <v/>
-      </c>
-      <c r="K74" s="18">
-        <f>$D$30*(1+$D$32)^(7-1)</f>
-        <v/>
-      </c>
-      <c r="L74" s="18">
-        <f>$D$30*(1+$D$32)^(8-1)</f>
-        <v/>
-      </c>
-      <c r="M74" s="18">
-        <f>$D$30*(1+$D$32)^(9-1)</f>
-        <v/>
-      </c>
-      <c r="N74" s="18">
-        <f>$D$30*(1+$D$32)^(10-1)</f>
+      <c r="E74" s="19">
+        <f>$D$42*(1+$D$43)^(1-1)</f>
+        <v/>
+      </c>
+      <c r="F74" s="19">
+        <f>$D$42*(1+$D$43)^(2-1)</f>
+        <v/>
+      </c>
+      <c r="G74" s="19">
+        <f>$D$42*(1+$D$43)^(3-1)</f>
+        <v/>
+      </c>
+      <c r="H74" s="19">
+        <f>$D$42*(1+$D$43)^(4-1)</f>
+        <v/>
+      </c>
+      <c r="I74" s="19">
+        <f>$D$42*(1+$D$43)^(5-1)</f>
+        <v/>
+      </c>
+      <c r="J74" s="19">
+        <f>$D$42*(1+$D$43)^(6-1)</f>
+        <v/>
+      </c>
+      <c r="K74" s="19">
+        <f>$D$42*(1+$D$43)^(7-1)</f>
+        <v/>
+      </c>
+      <c r="L74" s="19">
+        <f>$D$42*(1+$D$43)^(8-1)</f>
+        <v/>
+      </c>
+      <c r="M74" s="19">
+        <f>$D$42*(1+$D$43)^(9-1)</f>
+        <v/>
+      </c>
+      <c r="N74" s="19">
+        <f>$D$42*(1+$D$43)^(10-1)</f>
         <v/>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="5" t="inlineStr">
-        <is>
-          <t>Gas Price</t>
-        </is>
-      </c>
-      <c r="B75" s="6" t="inlineStr">
-        <is>
-          <t>$/mmBtu</t>
-        </is>
-      </c>
-      <c r="C75" s="6" t="inlineStr">
-        <is>
-          <t>Escalated</t>
-        </is>
-      </c>
-      <c r="E75" s="19">
-        <f>$D$31*(1+$D$32)^(1-1)</f>
-        <v/>
-      </c>
-      <c r="F75" s="19">
-        <f>$D$31*(1+$D$32)^(2-1)</f>
-        <v/>
-      </c>
-      <c r="G75" s="19">
-        <f>$D$31*(1+$D$32)^(3-1)</f>
-        <v/>
-      </c>
-      <c r="H75" s="19">
-        <f>$D$31*(1+$D$32)^(4-1)</f>
-        <v/>
-      </c>
-      <c r="I75" s="19">
-        <f>$D$31*(1+$D$32)^(5-1)</f>
-        <v/>
-      </c>
-      <c r="J75" s="19">
-        <f>$D$31*(1+$D$32)^(6-1)</f>
-        <v/>
-      </c>
-      <c r="K75" s="19">
-        <f>$D$31*(1+$D$32)^(7-1)</f>
-        <v/>
-      </c>
-      <c r="L75" s="19">
-        <f>$D$31*(1+$D$32)^(8-1)</f>
-        <v/>
-      </c>
-      <c r="M75" s="19">
-        <f>$D$31*(1+$D$32)^(9-1)</f>
-        <v/>
-      </c>
-      <c r="N75" s="19">
-        <f>$D$31*(1+$D$32)^(10-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="76"/>
+      <c r="A75" s="5" t="n"/>
+      <c r="B75" s="6" t="n"/>
+      <c r="C75" s="6" t="n"/>
+      <c r="E75" s="19" t="n"/>
+      <c r="F75" s="19" t="n"/>
+      <c r="G75" s="19" t="n"/>
+      <c r="H75" s="19" t="n"/>
+      <c r="I75" s="19" t="n"/>
+      <c r="J75" s="19" t="n"/>
+      <c r="K75" s="19" t="n"/>
+      <c r="L75" s="19" t="n"/>
+      <c r="M75" s="19" t="n"/>
+      <c r="N75" s="19" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>Energy Revenue</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>Generation × Power Price / 1M</t>
+        </is>
+      </c>
+      <c r="E76" s="18" t="n"/>
+      <c r="F76" s="18" t="n"/>
+      <c r="G76" s="18" t="n"/>
+      <c r="H76" s="18" t="n"/>
+      <c r="I76" s="18" t="n"/>
+      <c r="J76" s="18" t="n"/>
+      <c r="K76" s="18" t="n"/>
+      <c r="L76" s="18" t="n"/>
+      <c r="M76" s="18" t="n"/>
+      <c r="N76" s="18" t="n"/>
+    </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>Energy Revenue</t>
+          <t>Capacity Revenue</t>
         </is>
       </c>
       <c r="B77" s="6" t="inlineStr">
@@ -4487,24 +4699,24 @@
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>Generation × Power Price / 1M</t>
-        </is>
-      </c>
-      <c r="E77" s="18" t="inlineStr"/>
-      <c r="F77" s="18" t="inlineStr"/>
-      <c r="G77" s="18" t="inlineStr"/>
-      <c r="H77" s="18" t="inlineStr"/>
-      <c r="I77" s="18" t="inlineStr"/>
-      <c r="J77" s="18" t="inlineStr"/>
-      <c r="K77" s="18" t="inlineStr"/>
-      <c r="L77" s="18" t="inlineStr"/>
-      <c r="M77" s="18" t="inlineStr"/>
-      <c r="N77" s="18" t="inlineStr"/>
+          <t>UCAP × Cap Price × 1000 / 1M</t>
+        </is>
+      </c>
+      <c r="E77" s="18" t="n"/>
+      <c r="F77" s="18" t="n"/>
+      <c r="G77" s="18" t="n"/>
+      <c r="H77" s="18" t="n"/>
+      <c r="I77" s="18" t="n"/>
+      <c r="J77" s="18" t="n"/>
+      <c r="K77" s="18" t="n"/>
+      <c r="L77" s="18" t="n"/>
+      <c r="M77" s="18" t="n"/>
+      <c r="N77" s="18" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>Capacity Revenue</t>
+          <t>Total Revenue</t>
         </is>
       </c>
       <c r="B78" s="6" t="inlineStr">
@@ -4512,147 +4724,151 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C78" s="6" t="inlineStr">
-        <is>
-          <t>UCAP × Cap Price × 1000 / 1M</t>
-        </is>
-      </c>
-      <c r="E78" s="18" t="inlineStr"/>
-      <c r="F78" s="18" t="inlineStr"/>
-      <c r="G78" s="18" t="inlineStr"/>
-      <c r="H78" s="18" t="inlineStr"/>
-      <c r="I78" s="18" t="inlineStr"/>
-      <c r="J78" s="18" t="inlineStr"/>
-      <c r="K78" s="18" t="inlineStr"/>
-      <c r="L78" s="18" t="inlineStr"/>
-      <c r="M78" s="18" t="inlineStr"/>
-      <c r="N78" s="18" t="inlineStr"/>
+      <c r="C78" s="6" t="n"/>
+      <c r="E78" s="20" t="n"/>
+      <c r="F78" s="20" t="n"/>
+      <c r="G78" s="20" t="n"/>
+      <c r="H78" s="20" t="n"/>
+      <c r="I78" s="20" t="n"/>
+      <c r="J78" s="20" t="n"/>
+      <c r="K78" s="20" t="n"/>
+      <c r="L78" s="20" t="n"/>
+      <c r="M78" s="20" t="n"/>
+      <c r="N78" s="20" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" s="5" t="inlineStr">
-        <is>
-          <t>Total Revenue</t>
-        </is>
-      </c>
-      <c r="B79" s="6" t="inlineStr">
+      <c r="A79" s="5" t="n"/>
+      <c r="B79" s="6" t="n"/>
+      <c r="C79" s="6" t="n"/>
+      <c r="E79" s="20" t="n"/>
+      <c r="F79" s="20" t="n"/>
+      <c r="G79" s="20" t="n"/>
+      <c r="H79" s="20" t="n"/>
+      <c r="I79" s="20" t="n"/>
+      <c r="J79" s="20" t="n"/>
+      <c r="K79" s="20" t="n"/>
+      <c r="L79" s="20" t="n"/>
+      <c r="M79" s="20" t="n"/>
+      <c r="N79" s="20" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>Fuel Cost</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
         <is>
           <t>$mm</t>
         </is>
       </c>
-      <c r="C79" s="6" t="inlineStr"/>
-      <c r="E79" s="20" t="inlineStr"/>
-      <c r="F79" s="20" t="inlineStr"/>
-      <c r="G79" s="20" t="inlineStr"/>
-      <c r="H79" s="20" t="inlineStr"/>
-      <c r="I79" s="20" t="inlineStr"/>
-      <c r="J79" s="20" t="inlineStr"/>
-      <c r="K79" s="20" t="inlineStr"/>
-      <c r="L79" s="20" t="inlineStr"/>
-      <c r="M79" s="20" t="inlineStr"/>
-      <c r="N79" s="20" t="inlineStr"/>
-    </row>
-    <row r="80"/>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>Gen × HR × Gas / 1B</t>
+        </is>
+      </c>
+      <c r="E80" s="18" t="n"/>
+      <c r="F80" s="18" t="n"/>
+      <c r="G80" s="18" t="n"/>
+      <c r="H80" s="18" t="n"/>
+      <c r="I80" s="18" t="n"/>
+      <c r="J80" s="18" t="n"/>
+      <c r="K80" s="18" t="n"/>
+      <c r="L80" s="18" t="n"/>
+      <c r="M80" s="18" t="n"/>
+      <c r="N80" s="18" t="n"/>
+    </row>
     <row r="81">
-      <c r="A81" s="5" t="inlineStr">
-        <is>
-          <t>Fuel Cost</t>
+      <c r="A81" s="34" t="inlineStr">
+        <is>
+          <t>Spark Spread</t>
         </is>
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C81" s="6" t="inlineStr">
-        <is>
-          <t>Gen × HR × Gas / 1B</t>
-        </is>
-      </c>
-      <c r="E81" s="18" t="inlineStr"/>
-      <c r="F81" s="18" t="inlineStr"/>
-      <c r="G81" s="18" t="inlineStr"/>
-      <c r="H81" s="18" t="inlineStr"/>
-      <c r="I81" s="18" t="inlineStr"/>
-      <c r="J81" s="18" t="inlineStr"/>
-      <c r="K81" s="18" t="inlineStr"/>
-      <c r="L81" s="18" t="inlineStr"/>
-      <c r="M81" s="18" t="inlineStr"/>
-      <c r="N81" s="18" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="34" t="inlineStr">
-        <is>
-          <t>Spark Spread</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
           <t>$/MWh</t>
         </is>
       </c>
-      <c r="C82" s="55" t="inlineStr">
+      <c r="C81" s="55" t="inlineStr">
         <is>
           <t>[WHAT] Spark Spread = Power Price - (Plant HR × Gas / 1000)
 [WHY] Gross margin per MWh after fuel. Core driver of thermal profitability.
 [RMHR EQUIVALENCE - For Interview Discussion]
-Traders express this as "Market Heat Rate":
-  RMHR = Power / Gas × 1000
-  If RMHR &gt; Plant HR → "In the money" → Dispatch
-Spark Spread = (RMHR - Plant HR) × Gas / 1000
-Same math, different framing. Use Spark Spread in model (simpler).
-[EXAMPLE] Power=$50, Gas=$5, HR=7000
-  RMHR = 50/5 × 1000 = 10,000 Btu/kWh
-  Spread = 10,000 - 7,000 = 3,000 Btu/kWh
-  Spark = 3,000 × $5 / 1000 = $15/MWh ✓
-  (Or directly: $50 - 7×$5 = $15/MWh)
-[UNITS] $/MWh - (Btu/kWh × $/MMBtu / 1000) = $/MWh ✓</t>
-        </is>
-      </c>
-      <c r="E82" s="56">
-        <f>E71-($D$34/1000)*E73</f>
-        <v/>
-      </c>
-      <c r="F82" s="56">
-        <f>F71-($D$34/1000)*F73</f>
-        <v/>
-      </c>
-      <c r="G82" s="56">
-        <f>G71-($D$34/1000)*G73</f>
-        <v/>
-      </c>
-      <c r="H82" s="56">
-        <f>H71-($D$34/1000)*H73</f>
-        <v/>
-      </c>
-      <c r="I82" s="56">
-        <f>I71-($D$34/1000)*I73</f>
-        <v/>
-      </c>
-      <c r="J82" s="56">
-        <f>J71-($D$34/1000)*J73</f>
-        <v/>
-      </c>
-      <c r="K82" s="56">
-        <f>K71-($D$34/1000)*K73</f>
-        <v/>
-      </c>
-      <c r="L82" s="56">
-        <f>L71-($D$34/1000)*L73</f>
-        <v/>
-      </c>
-      <c r="M82" s="56">
-        <f>M71-($D$34/1000)*M73</f>
-        <v/>
-      </c>
-      <c r="N82" s="56">
-        <f>N71-($D$34/1000)*N73</f>
-        <v/>
-      </c>
+Traders express this as "Market Heat Rate":</t>
+        </is>
+      </c>
+      <c r="E81" s="56">
+        <f>E72-($D$35/1000)*E74</f>
+        <v/>
+      </c>
+      <c r="F81" s="56">
+        <f>F72-($D$35/1000)*F74</f>
+        <v/>
+      </c>
+      <c r="G81" s="56">
+        <f>G72-($D$35/1000)*G74</f>
+        <v/>
+      </c>
+      <c r="H81" s="56">
+        <f>H72-($D$35/1000)*H74</f>
+        <v/>
+      </c>
+      <c r="I81" s="56">
+        <f>I72-($D$35/1000)*I74</f>
+        <v/>
+      </c>
+      <c r="J81" s="56">
+        <f>J72-($D$35/1000)*J74</f>
+        <v/>
+      </c>
+      <c r="K81" s="56">
+        <f>K72-($D$35/1000)*K74</f>
+        <v/>
+      </c>
+      <c r="L81" s="56">
+        <f>L72-($D$35/1000)*L74</f>
+        <v/>
+      </c>
+      <c r="M81" s="56">
+        <f>M72-($D$35/1000)*M74</f>
+        <v/>
+      </c>
+      <c r="N81" s="56">
+        <f>N72-($D$35/1000)*N74</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>VOM</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>Generation × VOM rate / 1M</t>
+        </is>
+      </c>
+      <c r="E82" s="18" t="n"/>
+      <c r="F82" s="18" t="n"/>
+      <c r="G82" s="18" t="n"/>
+      <c r="H82" s="18" t="n"/>
+      <c r="I82" s="18" t="n"/>
+      <c r="J82" s="18" t="n"/>
+      <c r="K82" s="18" t="n"/>
+      <c r="L82" s="18" t="n"/>
+      <c r="M82" s="18" t="n"/>
+      <c r="N82" s="18" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>VOM</t>
+          <t>FOM</t>
         </is>
       </c>
       <c r="B83" s="6" t="inlineStr">
@@ -4662,54 +4878,24 @@
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>Generation × VOM rate / 1M</t>
-        </is>
-      </c>
-      <c r="E83" s="18">
-        <f>$D$54*$D$35/1000000</f>
-        <v/>
-      </c>
-      <c r="F83" s="18">
-        <f>$D$54*$D$35/1000000</f>
-        <v/>
-      </c>
-      <c r="G83" s="18">
-        <f>$D$54*$D$35/1000000</f>
-        <v/>
-      </c>
-      <c r="H83" s="18">
-        <f>$D$54*$D$35/1000000</f>
-        <v/>
-      </c>
-      <c r="I83" s="18">
-        <f>$D$54*$D$35/1000000</f>
-        <v/>
-      </c>
-      <c r="J83" s="18">
-        <f>$D$54*$D$35/1000000</f>
-        <v/>
-      </c>
-      <c r="K83" s="18">
-        <f>$D$54*$D$35/1000000</f>
-        <v/>
-      </c>
-      <c r="L83" s="18">
-        <f>$D$54*$D$35/1000000</f>
-        <v/>
-      </c>
-      <c r="M83" s="18">
-        <f>$D$54*$D$35/1000000</f>
-        <v/>
-      </c>
-      <c r="N83" s="18">
-        <f>$D$54*$D$35/1000000</f>
-        <v/>
-      </c>
+          <t>Capacity × FOM × esc × 1000 / 1M</t>
+        </is>
+      </c>
+      <c r="E83" s="18" t="n"/>
+      <c r="F83" s="18" t="n"/>
+      <c r="G83" s="18" t="n"/>
+      <c r="H83" s="18" t="n"/>
+      <c r="I83" s="18" t="n"/>
+      <c r="J83" s="18" t="n"/>
+      <c r="K83" s="18" t="n"/>
+      <c r="L83" s="18" t="n"/>
+      <c r="M83" s="18" t="n"/>
+      <c r="N83" s="18" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>FOM</t>
+          <t>Total Operating Costs</t>
         </is>
       </c>
       <c r="B84" s="6" t="inlineStr">
@@ -4717,155 +4903,158 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C84" s="6" t="inlineStr">
-        <is>
-          <t>Capacity × FOM × esc × 1000 / 1M</t>
-        </is>
-      </c>
-      <c r="E84" s="18">
-        <f>$D$23*$D$36*(1+$D$32)^(1-1)*1000/1000000</f>
-        <v/>
-      </c>
-      <c r="F84" s="18">
-        <f>$D$23*$D$36*(1+$D$32)^(2-1)*1000/1000000</f>
-        <v/>
-      </c>
-      <c r="G84" s="18">
-        <f>$D$23*$D$36*(1+$D$32)^(3-1)*1000/1000000</f>
-        <v/>
-      </c>
-      <c r="H84" s="18">
-        <f>$D$23*$D$36*(1+$D$32)^(4-1)*1000/1000000</f>
-        <v/>
-      </c>
-      <c r="I84" s="18">
-        <f>$D$23*$D$36*(1+$D$32)^(5-1)*1000/1000000</f>
-        <v/>
-      </c>
-      <c r="J84" s="18">
-        <f>$D$23*$D$36*(1+$D$32)^(6-1)*1000/1000000</f>
-        <v/>
-      </c>
-      <c r="K84" s="18">
-        <f>$D$23*$D$36*(1+$D$32)^(7-1)*1000/1000000</f>
-        <v/>
-      </c>
-      <c r="L84" s="18">
-        <f>$D$23*$D$36*(1+$D$32)^(8-1)*1000/1000000</f>
-        <v/>
-      </c>
-      <c r="M84" s="18">
-        <f>$D$23*$D$36*(1+$D$32)^(9-1)*1000/1000000</f>
-        <v/>
-      </c>
-      <c r="N84" s="18">
-        <f>$D$23*$D$36*(1+$D$32)^(10-1)*1000/1000000</f>
-        <v/>
-      </c>
+      <c r="C84" s="6" t="n"/>
+      <c r="E84" s="18" t="n"/>
+      <c r="F84" s="18" t="n"/>
+      <c r="G84" s="18" t="n"/>
+      <c r="H84" s="18" t="n"/>
+      <c r="I84" s="18" t="n"/>
+      <c r="J84" s="18" t="n"/>
+      <c r="K84" s="18" t="n"/>
+      <c r="L84" s="18" t="n"/>
+      <c r="M84" s="18" t="n"/>
+      <c r="N84" s="18" t="n"/>
     </row>
     <row r="85">
-      <c r="A85" s="5" t="inlineStr">
-        <is>
-          <t>Total Operating Costs</t>
-        </is>
-      </c>
-      <c r="B85" s="6" t="inlineStr">
+      <c r="A85" s="5" t="n"/>
+      <c r="B85" s="6" t="n"/>
+      <c r="C85" s="6" t="n"/>
+      <c r="E85" s="18" t="n"/>
+      <c r="F85" s="18" t="n"/>
+      <c r="G85" s="18" t="n"/>
+      <c r="H85" s="18" t="n"/>
+      <c r="I85" s="18" t="n"/>
+      <c r="J85" s="18" t="n"/>
+      <c r="K85" s="18" t="n"/>
+      <c r="L85" s="18" t="n"/>
+      <c r="M85" s="18" t="n"/>
+      <c r="N85" s="18" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
         <is>
           <t>$mm</t>
         </is>
       </c>
-      <c r="C85" s="6" t="inlineStr"/>
-      <c r="E85" s="18">
-        <f>E69+E70+E71</f>
-        <v/>
-      </c>
-      <c r="F85" s="18">
-        <f>F69+F70+F71</f>
-        <v/>
-      </c>
-      <c r="G85" s="18">
-        <f>G69+G70+G71</f>
-        <v/>
-      </c>
-      <c r="H85" s="18">
-        <f>H69+H70+H71</f>
-        <v/>
-      </c>
-      <c r="I85" s="18">
-        <f>I69+I70+I71</f>
-        <v/>
-      </c>
-      <c r="J85" s="18">
-        <f>J69+J70+J71</f>
-        <v/>
-      </c>
-      <c r="K85" s="18">
-        <f>K69+K70+K71</f>
-        <v/>
-      </c>
-      <c r="L85" s="18">
-        <f>L69+L70+L71</f>
-        <v/>
-      </c>
-      <c r="M85" s="18">
-        <f>M69+M70+M71</f>
-        <v/>
-      </c>
-      <c r="N85" s="18">
-        <f>N69+N70+N71</f>
-        <v/>
-      </c>
-    </row>
-    <row r="86"/>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>Revenue minus OpEx</t>
+        </is>
+      </c>
+      <c r="E86" s="7" t="n"/>
+      <c r="F86" s="7" t="n"/>
+      <c r="G86" s="7" t="n"/>
+      <c r="H86" s="7" t="n"/>
+      <c r="I86" s="7" t="n"/>
+      <c r="J86" s="7" t="n"/>
+      <c r="K86" s="7" t="n"/>
+      <c r="L86" s="7" t="n"/>
+      <c r="M86" s="7" t="n"/>
+      <c r="N86" s="7" t="n"/>
+    </row>
     <row r="87">
-      <c r="A87" s="5" t="inlineStr">
-        <is>
-          <t>EBITDA</t>
-        </is>
-      </c>
-      <c r="B87" s="6" t="inlineStr">
+      <c r="A87" s="5" t="n"/>
+      <c r="B87" s="6" t="n"/>
+      <c r="C87" s="6" t="n"/>
+      <c r="E87" s="7" t="n"/>
+      <c r="F87" s="7" t="n"/>
+      <c r="G87" s="7" t="n"/>
+      <c r="H87" s="7" t="n"/>
+      <c r="I87" s="7" t="n"/>
+      <c r="J87" s="7" t="n"/>
+      <c r="K87" s="7" t="n"/>
+      <c r="L87" s="7" t="n"/>
+      <c r="M87" s="7" t="n"/>
+      <c r="N87" s="7" t="n"/>
+    </row>
+    <row r="88"/>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>CASH FLOW</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="n"/>
+      <c r="C89" s="4" t="n"/>
+      <c r="D89" s="4" t="n"/>
+      <c r="E89" s="4" t="n"/>
+      <c r="F89" s="4" t="n"/>
+      <c r="G89" s="4" t="n"/>
+      <c r="H89" s="4" t="n"/>
+      <c r="I89" s="4" t="n"/>
+      <c r="J89" s="4" t="n"/>
+      <c r="K89" s="4" t="n"/>
+      <c r="L89" s="4" t="n"/>
+      <c r="M89" s="4" t="n"/>
+      <c r="N89" s="4" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t>EBIT</t>
+        </is>
+      </c>
+      <c r="B90" s="6" t="inlineStr">
         <is>
           <t>$mm</t>
         </is>
       </c>
-      <c r="C87" s="6" t="inlineStr"/>
-      <c r="E87" s="7" t="inlineStr"/>
-      <c r="F87" s="7" t="inlineStr"/>
-      <c r="G87" s="7" t="inlineStr"/>
-      <c r="H87" s="7" t="inlineStr"/>
-      <c r="I87" s="7" t="inlineStr"/>
-      <c r="J87" s="7" t="inlineStr"/>
-      <c r="K87" s="7" t="inlineStr"/>
-      <c r="L87" s="7" t="inlineStr"/>
-      <c r="M87" s="7" t="inlineStr"/>
-      <c r="N87" s="7" t="inlineStr"/>
-    </row>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90">
-      <c r="A90" s="3" t="inlineStr">
-        <is>
-          <t>CASH FLOW</t>
-        </is>
-      </c>
-      <c r="B90" s="4" t="n"/>
-      <c r="C90" s="4" t="n"/>
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>EBITDA - Depreciation</t>
+        </is>
+      </c>
       <c r="D90" s="4" t="n"/>
-      <c r="E90" s="4" t="n"/>
-      <c r="F90" s="4" t="n"/>
-      <c r="G90" s="4" t="n"/>
-      <c r="H90" s="4" t="n"/>
-      <c r="I90" s="4" t="n"/>
-      <c r="J90" s="4" t="n"/>
-      <c r="K90" s="4" t="n"/>
-      <c r="L90" s="4" t="n"/>
-      <c r="M90" s="4" t="n"/>
-      <c r="N90" s="4" t="n"/>
+      <c r="E90" s="18">
+        <f>E86-$D$67</f>
+        <v/>
+      </c>
+      <c r="F90" s="18">
+        <f>F86-$D$67</f>
+        <v/>
+      </c>
+      <c r="G90" s="18">
+        <f>G86-$D$67</f>
+        <v/>
+      </c>
+      <c r="H90" s="18">
+        <f>H86-$D$67</f>
+        <v/>
+      </c>
+      <c r="I90" s="18">
+        <f>I86-$D$67</f>
+        <v/>
+      </c>
+      <c r="J90" s="18">
+        <f>J86-$D$67</f>
+        <v/>
+      </c>
+      <c r="K90" s="18">
+        <f>K86-$D$67</f>
+        <v/>
+      </c>
+      <c r="L90" s="18">
+        <f>L86-$D$67</f>
+        <v/>
+      </c>
+      <c r="M90" s="18">
+        <f>M86-$D$67</f>
+        <v/>
+      </c>
+      <c r="N90" s="18">
+        <f>N86-$D$67</f>
+        <v/>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>EBIT</t>
+          <t>Taxes</t>
         </is>
       </c>
       <c r="B91" s="6" t="inlineStr">
@@ -4875,24 +5064,24 @@
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>EBITDA - Depreciation</t>
-        </is>
-      </c>
-      <c r="E91" s="18" t="inlineStr"/>
-      <c r="F91" s="18" t="inlineStr"/>
-      <c r="G91" s="18" t="inlineStr"/>
-      <c r="H91" s="18" t="inlineStr"/>
-      <c r="I91" s="18" t="inlineStr"/>
-      <c r="J91" s="18" t="inlineStr"/>
-      <c r="K91" s="18" t="inlineStr"/>
-      <c r="L91" s="18" t="inlineStr"/>
-      <c r="M91" s="18" t="inlineStr"/>
-      <c r="N91" s="18" t="inlineStr"/>
+          <t>MAX(0, EBIT) × Tax Rate</t>
+        </is>
+      </c>
+      <c r="E91" s="18" t="n"/>
+      <c r="F91" s="18" t="n"/>
+      <c r="G91" s="18" t="n"/>
+      <c r="H91" s="18" t="n"/>
+      <c r="I91" s="18" t="n"/>
+      <c r="J91" s="18" t="n"/>
+      <c r="K91" s="18" t="n"/>
+      <c r="L91" s="18" t="n"/>
+      <c r="M91" s="18" t="n"/>
+      <c r="N91" s="18" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t>Taxes</t>
+          <t>CFADS</t>
         </is>
       </c>
       <c r="B92" s="6" t="inlineStr">
@@ -4902,73 +5091,120 @@
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>MAX(0, EBIT) × Tax Rate</t>
-        </is>
-      </c>
-      <c r="E92" s="18" t="inlineStr"/>
-      <c r="F92" s="18" t="inlineStr"/>
-      <c r="G92" s="18" t="inlineStr"/>
-      <c r="H92" s="18" t="inlineStr"/>
-      <c r="I92" s="18" t="inlineStr"/>
-      <c r="J92" s="18" t="inlineStr"/>
-      <c r="K92" s="18" t="inlineStr"/>
-      <c r="L92" s="18" t="inlineStr"/>
-      <c r="M92" s="18" t="inlineStr"/>
-      <c r="N92" s="18" t="inlineStr"/>
+          <t>EBITDA - Taxes</t>
+        </is>
+      </c>
+      <c r="E92" s="7" t="n"/>
+      <c r="F92" s="7" t="n"/>
+      <c r="G92" s="7" t="n"/>
+      <c r="H92" s="7" t="n"/>
+      <c r="I92" s="7" t="n"/>
+      <c r="J92" s="7" t="n"/>
+      <c r="K92" s="7" t="n"/>
+      <c r="L92" s="7" t="n"/>
+      <c r="M92" s="7" t="n"/>
+      <c r="N92" s="7" t="n"/>
     </row>
     <row r="93">
-      <c r="A93" s="5" t="inlineStr">
-        <is>
-          <t>CFADS</t>
-        </is>
-      </c>
-      <c r="B93" s="6" t="inlineStr">
+      <c r="A93" s="5" t="n"/>
+      <c r="B93" s="6" t="n"/>
+      <c r="C93" s="6" t="n"/>
+      <c r="E93" s="7" t="n"/>
+      <c r="F93" s="7" t="n"/>
+      <c r="G93" s="7" t="n"/>
+      <c r="H93" s="7" t="n"/>
+      <c r="I93" s="7" t="n"/>
+      <c r="J93" s="7" t="n"/>
+      <c r="K93" s="7" t="n"/>
+      <c r="L93" s="7" t="n"/>
+      <c r="M93" s="7" t="n"/>
+      <c r="N93" s="7" t="n"/>
+    </row>
+    <row r="94"/>
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t>DEBT SCHEDULE (75% Cash Sweep)</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="n"/>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>MIN(Excess×%, Bal−Sched)</t>
+        </is>
+      </c>
+      <c r="D95" s="4" t="n"/>
+      <c r="E95" s="4" t="n"/>
+      <c r="F95" s="4" t="n"/>
+      <c r="G95" s="4" t="n"/>
+      <c r="H95" s="4" t="n"/>
+      <c r="I95" s="4" t="n"/>
+      <c r="J95" s="4" t="n"/>
+      <c r="K95" s="4" t="n"/>
+      <c r="L95" s="4" t="n"/>
+      <c r="M95" s="4" t="n"/>
+      <c r="N95" s="4" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="5" t="inlineStr">
+        <is>
+          <t>Beginning Balance</t>
+        </is>
+      </c>
+      <c r="B96" s="6" t="inlineStr">
         <is>
           <t>$mm</t>
         </is>
       </c>
-      <c r="C93" s="6" t="inlineStr">
-        <is>
-          <t>EBITDA - Taxes</t>
-        </is>
-      </c>
-      <c r="E93" s="7" t="inlineStr"/>
-      <c r="F93" s="7" t="inlineStr"/>
-      <c r="G93" s="7" t="inlineStr"/>
-      <c r="H93" s="7" t="inlineStr"/>
-      <c r="I93" s="7" t="inlineStr"/>
-      <c r="J93" s="7" t="inlineStr"/>
-      <c r="K93" s="7" t="inlineStr"/>
-      <c r="L93" s="7" t="inlineStr"/>
-      <c r="M93" s="7" t="inlineStr"/>
-      <c r="N93" s="7" t="inlineStr"/>
-    </row>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96">
-      <c r="A96" s="3" t="inlineStr">
-        <is>
-          <t>DEBT SCHEDULE (75% Cash Sweep)</t>
-        </is>
-      </c>
-      <c r="B96" s="4" t="n"/>
-      <c r="C96" s="4" t="n"/>
-      <c r="D96" s="4" t="n"/>
-      <c r="E96" s="4" t="n"/>
-      <c r="F96" s="4" t="n"/>
-      <c r="G96" s="4" t="n"/>
-      <c r="H96" s="4" t="n"/>
-      <c r="I96" s="4" t="n"/>
-      <c r="J96" s="4" t="n"/>
-      <c r="K96" s="4" t="n"/>
-      <c r="L96" s="4" t="n"/>
-      <c r="M96" s="4" t="n"/>
-      <c r="N96" s="4" t="n"/>
+      <c r="C96" s="6" t="n"/>
+      <c r="D96" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" s="18">
+        <f>$D$66</f>
+        <v/>
+      </c>
+      <c r="F96" s="18">
+        <f>E103</f>
+        <v/>
+      </c>
+      <c r="G96" s="18">
+        <f>F103</f>
+        <v/>
+      </c>
+      <c r="H96" s="18">
+        <f>G103</f>
+        <v/>
+      </c>
+      <c r="I96" s="18">
+        <f>H103</f>
+        <v/>
+      </c>
+      <c r="J96" s="18">
+        <f>I103</f>
+        <v/>
+      </c>
+      <c r="K96" s="18">
+        <f>J103</f>
+        <v/>
+      </c>
+      <c r="L96" s="18">
+        <f>K103</f>
+        <v/>
+      </c>
+      <c r="M96" s="18">
+        <f>L103</f>
+        <v/>
+      </c>
+      <c r="N96" s="18">
+        <f>M103</f>
+        <v/>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>Beginning Balance</t>
+          <t>Interest</t>
         </is>
       </c>
       <c r="B97" s="6" t="inlineStr">
@@ -4976,52 +5212,26 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C97" s="6" t="inlineStr"/>
-      <c r="E97" s="18">
-        <f>$D$55</f>
-        <v/>
-      </c>
-      <c r="F97" s="18">
-        <f>E91</f>
-        <v/>
-      </c>
-      <c r="G97" s="18">
-        <f>F91</f>
-        <v/>
-      </c>
-      <c r="H97" s="18">
-        <f>G91</f>
-        <v/>
-      </c>
-      <c r="I97" s="18">
-        <f>H91</f>
-        <v/>
-      </c>
-      <c r="J97" s="18">
-        <f>I91</f>
-        <v/>
-      </c>
-      <c r="K97" s="18">
-        <f>J91</f>
-        <v/>
-      </c>
-      <c r="L97" s="18">
-        <f>K91</f>
-        <v/>
-      </c>
-      <c r="M97" s="18">
-        <f>L91</f>
-        <v/>
-      </c>
-      <c r="N97" s="18">
-        <f>M91</f>
-        <v/>
-      </c>
+      <c r="C97" s="6" t="inlineStr">
+        <is>
+          <t>Beg Bal × Int Rate</t>
+        </is>
+      </c>
+      <c r="E97" s="18" t="n"/>
+      <c r="F97" s="18" t="n"/>
+      <c r="G97" s="18" t="n"/>
+      <c r="H97" s="18" t="n"/>
+      <c r="I97" s="18" t="n"/>
+      <c r="J97" s="18" t="n"/>
+      <c r="K97" s="18" t="n"/>
+      <c r="L97" s="18" t="n"/>
+      <c r="M97" s="18" t="n"/>
+      <c r="N97" s="18" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>Interest</t>
+          <t>Scheduled Principal</t>
         </is>
       </c>
       <c r="B98" s="6" t="inlineStr">
@@ -5031,24 +5241,24 @@
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>Beg Bal × Int Rate</t>
-        </is>
-      </c>
-      <c r="E98" s="18" t="inlineStr"/>
-      <c r="F98" s="18" t="inlineStr"/>
-      <c r="G98" s="18" t="inlineStr"/>
-      <c r="H98" s="18" t="inlineStr"/>
-      <c r="I98" s="18" t="inlineStr"/>
-      <c r="J98" s="18" t="inlineStr"/>
-      <c r="K98" s="18" t="inlineStr"/>
-      <c r="L98" s="18" t="inlineStr"/>
-      <c r="M98" s="18" t="inlineStr"/>
-      <c r="N98" s="18" t="inlineStr"/>
+          <t>MIN(Sched, Beg Bal)</t>
+        </is>
+      </c>
+      <c r="E98" s="18" t="n"/>
+      <c r="F98" s="18" t="n"/>
+      <c r="G98" s="18" t="n"/>
+      <c r="H98" s="18" t="n"/>
+      <c r="I98" s="18" t="n"/>
+      <c r="J98" s="18" t="n"/>
+      <c r="K98" s="18" t="n"/>
+      <c r="L98" s="18" t="n"/>
+      <c r="M98" s="18" t="n"/>
+      <c r="N98" s="18" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>Scheduled Principal</t>
+          <t>Debt Service (Pre-Sweep)</t>
         </is>
       </c>
       <c r="B99" s="6" t="inlineStr">
@@ -5058,24 +5268,24 @@
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>MIN(Sched, Beg Bal)</t>
-        </is>
-      </c>
-      <c r="E99" s="18" t="inlineStr"/>
-      <c r="F99" s="18" t="inlineStr"/>
-      <c r="G99" s="18" t="inlineStr"/>
-      <c r="H99" s="18" t="inlineStr"/>
-      <c r="I99" s="18" t="inlineStr"/>
-      <c r="J99" s="18" t="inlineStr"/>
-      <c r="K99" s="18" t="inlineStr"/>
-      <c r="L99" s="18" t="inlineStr"/>
-      <c r="M99" s="18" t="inlineStr"/>
-      <c r="N99" s="18" t="inlineStr"/>
+          <t>Interest + Sched Prin</t>
+        </is>
+      </c>
+      <c r="E99" s="18" t="n"/>
+      <c r="F99" s="18" t="n"/>
+      <c r="G99" s="18" t="n"/>
+      <c r="H99" s="18" t="n"/>
+      <c r="I99" s="18" t="n"/>
+      <c r="J99" s="18" t="n"/>
+      <c r="K99" s="18" t="n"/>
+      <c r="L99" s="18" t="n"/>
+      <c r="M99" s="18" t="n"/>
+      <c r="N99" s="18" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>Debt Service (Pre-Sweep)</t>
+          <t>Excess Cash</t>
         </is>
       </c>
       <c r="B100" s="6" t="inlineStr">
@@ -5085,54 +5295,54 @@
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>Interest + Sched Prin</t>
+          <t>CFADS - DS - DSRA Funding</t>
         </is>
       </c>
       <c r="E100" s="18">
-        <f>E85+E86</f>
+        <f>MAX(0,E92-E99-E110)</f>
         <v/>
       </c>
       <c r="F100" s="18">
-        <f>F85+F86</f>
+        <f>MAX(0,F92-F99-F110)</f>
         <v/>
       </c>
       <c r="G100" s="18">
-        <f>G85+G86</f>
+        <f>MAX(0,G92-G99-G110)</f>
         <v/>
       </c>
       <c r="H100" s="18">
-        <f>H85+H86</f>
+        <f>MAX(0,H92-H99-H110)</f>
         <v/>
       </c>
       <c r="I100" s="18">
-        <f>I85+I86</f>
+        <f>MAX(0,I92-I99-I110)</f>
         <v/>
       </c>
       <c r="J100" s="18">
-        <f>J85+J86</f>
+        <f>MAX(0,J92-J99-J110)</f>
         <v/>
       </c>
       <c r="K100" s="18">
-        <f>K85+K86</f>
+        <f>MAX(0,K92-K99-K110)</f>
         <v/>
       </c>
       <c r="L100" s="18">
-        <f>L85+L86</f>
+        <f>MAX(0,L92-L99-L110)</f>
         <v/>
       </c>
       <c r="M100" s="18">
-        <f>M85+M86</f>
+        <f>MAX(0,M92-M99-M110)</f>
         <v/>
       </c>
       <c r="N100" s="18">
-        <f>N85+N86</f>
+        <f>MAX(0,N92-N99-N110)</f>
         <v/>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>Excess Cash</t>
+          <t>Cash Sweep</t>
         </is>
       </c>
       <c r="B101" s="6" t="inlineStr">
@@ -5142,54 +5352,24 @@
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>CFADS - DS - DSRA Funding</t>
-        </is>
-      </c>
-      <c r="E101" s="18">
-        <f>MAX(0,E80-E87-E98)</f>
-        <v/>
-      </c>
-      <c r="F101" s="18">
-        <f>MAX(0,F80-F87-F98)</f>
-        <v/>
-      </c>
-      <c r="G101" s="18">
-        <f>MAX(0,G80-G87-G98)</f>
-        <v/>
-      </c>
-      <c r="H101" s="18">
-        <f>MAX(0,H80-H87-H98)</f>
-        <v/>
-      </c>
-      <c r="I101" s="18">
-        <f>MAX(0,I80-I87-I98)</f>
-        <v/>
-      </c>
-      <c r="J101" s="18">
-        <f>MAX(0,J80-J87-J98)</f>
-        <v/>
-      </c>
-      <c r="K101" s="18">
-        <f>MAX(0,K80-K87-K98)</f>
-        <v/>
-      </c>
-      <c r="L101" s="18">
-        <f>MAX(0,L80-L87-L98)</f>
-        <v/>
-      </c>
-      <c r="M101" s="18">
-        <f>MAX(0,M80-M87-M98)</f>
-        <v/>
-      </c>
-      <c r="N101" s="18">
-        <f>MAX(0,N80-N87-N98)</f>
-        <v/>
-      </c>
+          <t>MIN(Excess×Sweep%, Beg-Sched)</t>
+        </is>
+      </c>
+      <c r="E101" s="21" t="n"/>
+      <c r="F101" s="21" t="n"/>
+      <c r="G101" s="21" t="n"/>
+      <c r="H101" s="21" t="n"/>
+      <c r="I101" s="21" t="n"/>
+      <c r="J101" s="21" t="n"/>
+      <c r="K101" s="21" t="n"/>
+      <c r="L101" s="21" t="n"/>
+      <c r="M101" s="21" t="n"/>
+      <c r="N101" s="21" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>Cash Sweep</t>
+          <t>Total Principal</t>
         </is>
       </c>
       <c r="B102" s="6" t="inlineStr">
@@ -5199,24 +5379,24 @@
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>MIN(Excess×Sweep%, Beg-Sched)</t>
-        </is>
-      </c>
-      <c r="E102" s="21" t="inlineStr"/>
-      <c r="F102" s="21" t="inlineStr"/>
-      <c r="G102" s="21" t="inlineStr"/>
-      <c r="H102" s="21" t="inlineStr"/>
-      <c r="I102" s="21" t="inlineStr"/>
-      <c r="J102" s="21" t="inlineStr"/>
-      <c r="K102" s="21" t="inlineStr"/>
-      <c r="L102" s="21" t="inlineStr"/>
-      <c r="M102" s="21" t="inlineStr"/>
-      <c r="N102" s="21" t="inlineStr"/>
+          <t>Scheduled + Sweep</t>
+        </is>
+      </c>
+      <c r="E102" s="18" t="n"/>
+      <c r="F102" s="18" t="n"/>
+      <c r="G102" s="18" t="n"/>
+      <c r="H102" s="18" t="n"/>
+      <c r="I102" s="18" t="n"/>
+      <c r="J102" s="18" t="n"/>
+      <c r="K102" s="18" t="n"/>
+      <c r="L102" s="18" t="n"/>
+      <c r="M102" s="18" t="n"/>
+      <c r="N102" s="18" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>Total Principal</t>
+          <t>Ending Balance</t>
         </is>
       </c>
       <c r="B103" s="6" t="inlineStr">
@@ -5226,156 +5406,237 @@
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>Scheduled + Sweep</t>
-        </is>
-      </c>
-      <c r="E103" s="18" t="inlineStr"/>
-      <c r="F103" s="18" t="inlineStr"/>
-      <c r="G103" s="18" t="inlineStr"/>
-      <c r="H103" s="18" t="inlineStr"/>
-      <c r="I103" s="18" t="inlineStr"/>
-      <c r="J103" s="18" t="inlineStr"/>
-      <c r="K103" s="18" t="inlineStr"/>
-      <c r="L103" s="18" t="inlineStr"/>
-      <c r="M103" s="18" t="inlineStr"/>
-      <c r="N103" s="18" t="inlineStr"/>
+          <t>MAX(0, Beg - Total Prin)</t>
+        </is>
+      </c>
+      <c r="D103">
+        <f>$D$66</f>
+        <v/>
+      </c>
+      <c r="E103" s="18" t="n"/>
+      <c r="F103" s="18" t="n"/>
+      <c r="G103" s="18" t="n"/>
+      <c r="H103" s="18" t="n"/>
+      <c r="I103" s="18" t="n"/>
+      <c r="J103" s="18" t="n"/>
+      <c r="K103" s="18" t="n"/>
+      <c r="L103" s="18" t="n"/>
+      <c r="M103" s="18" t="n"/>
+      <c r="N103" s="18" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>Ending Balance</t>
+          <t>DSCR</t>
         </is>
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>$mm</t>
+          <t>x</t>
         </is>
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>MAX(0, Beg - Total Prin)</t>
-        </is>
-      </c>
-      <c r="E104" s="18" t="inlineStr"/>
-      <c r="F104" s="18" t="inlineStr"/>
-      <c r="G104" s="18" t="inlineStr"/>
-      <c r="H104" s="18" t="inlineStr"/>
-      <c r="I104" s="18" t="inlineStr"/>
-      <c r="J104" s="18" t="inlineStr"/>
-      <c r="K104" s="18" t="inlineStr"/>
-      <c r="L104" s="18" t="inlineStr"/>
-      <c r="M104" s="18" t="inlineStr"/>
-      <c r="N104" s="18" t="inlineStr"/>
+          <t>CFADS / Debt Service</t>
+        </is>
+      </c>
+      <c r="E104" s="30" t="n"/>
+      <c r="F104" s="30" t="n"/>
+      <c r="G104" s="30" t="n"/>
+      <c r="H104" s="30" t="n"/>
+      <c r="I104" s="30" t="n"/>
+      <c r="J104" s="30" t="n"/>
+      <c r="K104" s="30" t="n"/>
+      <c r="L104" s="30" t="n"/>
+      <c r="M104" s="30" t="n"/>
+      <c r="N104" s="30" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>DSCR</t>
+          <t>Scheduled DS (for DSRA)</t>
         </is>
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>$mm</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>CFADS / Debt Service</t>
-        </is>
-      </c>
-      <c r="E105" s="30" t="inlineStr"/>
-      <c r="F105" s="30" t="inlineStr"/>
-      <c r="G105" s="30" t="inlineStr"/>
-      <c r="H105" s="30" t="inlineStr"/>
-      <c r="I105" s="30" t="inlineStr"/>
-      <c r="J105" s="30" t="inlineStr"/>
-      <c r="K105" s="30" t="inlineStr"/>
-      <c r="L105" s="30" t="inlineStr"/>
-      <c r="M105" s="30" t="inlineStr"/>
-      <c r="N105" s="30" t="inlineStr"/>
+          <t>Based on straight-line amort, no sweep</t>
+        </is>
+      </c>
+      <c r="E105" s="18">
+        <f>MAX(0,$D$55-(1-1)*$D$57)*$D$40+$D$57</f>
+        <v/>
+      </c>
+      <c r="F105" s="18">
+        <f>MAX(0,$D$55-(2-1)*$D$57)*$D$40+$D$57</f>
+        <v/>
+      </c>
+      <c r="G105" s="18">
+        <f>MAX(0,$D$55-(3-1)*$D$57)*$D$40+$D$57</f>
+        <v/>
+      </c>
+      <c r="H105" s="18">
+        <f>MAX(0,$D$55-(4-1)*$D$57)*$D$40+$D$57</f>
+        <v/>
+      </c>
+      <c r="I105" s="18">
+        <f>MAX(0,$D$55-(5-1)*$D$57)*$D$40+$D$57</f>
+        <v/>
+      </c>
+      <c r="J105" s="18">
+        <f>MAX(0,$D$55-(6-1)*$D$57)*$D$40+$D$57</f>
+        <v/>
+      </c>
+      <c r="K105" s="18">
+        <f>MAX(0,$D$55-(7-1)*$D$57)*$D$40+$D$57</f>
+        <v/>
+      </c>
+      <c r="L105" s="18">
+        <f>MAX(0,$D$55-(8-1)*$D$57)*$D$40+$D$57</f>
+        <v/>
+      </c>
+      <c r="M105" s="18">
+        <f>MAX(0,$D$55-(9-1)*$D$57)*$D$40+$D$57</f>
+        <v/>
+      </c>
+      <c r="N105" s="18">
+        <f>MAX(0,$D$55-(10-1)*$D$57)*$D$40+$D$57</f>
+        <v/>
+      </c>
     </row>
     <row r="106">
-      <c r="A106" s="5" t="inlineStr">
-        <is>
-          <t>Scheduled DS (for DSRA)</t>
-        </is>
-      </c>
-      <c r="B106" s="6" t="inlineStr">
+      <c r="A106" s="5" t="n"/>
+      <c r="B106" s="6" t="n"/>
+      <c r="C106" s="6" t="n"/>
+      <c r="E106" s="18">
+        <f>MAX(0,$D$66-(1-1)*$D$68)*$D$51+$D$68</f>
+        <v/>
+      </c>
+      <c r="F106" s="18">
+        <f>MAX(0,$D$66-(2-1)*$D$68)*$D$51+$D$68</f>
+        <v/>
+      </c>
+      <c r="G106" s="18">
+        <f>MAX(0,$D$66-(3-1)*$D$68)*$D$51+$D$68</f>
+        <v/>
+      </c>
+      <c r="H106" s="18">
+        <f>MAX(0,$D$66-(4-1)*$D$68)*$D$51+$D$68</f>
+        <v/>
+      </c>
+      <c r="I106" s="18">
+        <f>MAX(0,$D$66-(5-1)*$D$68)*$D$51+$D$68</f>
+        <v/>
+      </c>
+      <c r="J106" s="18">
+        <f>MAX(0,$D$66-(6-1)*$D$68)*$D$51+$D$68</f>
+        <v/>
+      </c>
+      <c r="K106" s="18">
+        <f>MAX(0,$D$66-(7-1)*$D$68)*$D$51+$D$68</f>
+        <v/>
+      </c>
+      <c r="L106" s="18">
+        <f>MAX(0,$D$66-(8-1)*$D$68)*$D$51+$D$68</f>
+        <v/>
+      </c>
+      <c r="M106" s="18">
+        <f>MAX(0,$D$66-(9-1)*$D$68)*$D$51+$D$68</f>
+        <v/>
+      </c>
+      <c r="N106" s="18">
+        <f>MAX(0,$D$66-(10-1)*$D$68)*$D$51+$D$68</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="inlineStr">
+        <is>
+          <t>DSRA (Debt Service Reserve Account)</t>
+        </is>
+      </c>
+      <c r="B107" s="4" t="n"/>
+      <c r="C107" s="4" t="n"/>
+      <c r="D107" s="4" t="n"/>
+      <c r="E107" s="4" t="n"/>
+      <c r="F107" s="4" t="n"/>
+      <c r="G107" s="4" t="n"/>
+      <c r="H107" s="4" t="n"/>
+      <c r="I107" s="4" t="n"/>
+      <c r="J107" s="4" t="n"/>
+      <c r="K107" s="4" t="n"/>
+      <c r="L107" s="4" t="n"/>
+      <c r="M107" s="4" t="n"/>
+      <c r="N107" s="4" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="5" t="inlineStr">
+        <is>
+          <t>DSRA Target</t>
+        </is>
+      </c>
+      <c r="B108" s="6" t="inlineStr">
         <is>
           <t>$mm</t>
         </is>
       </c>
-      <c r="C106" s="6" t="inlineStr">
-        <is>
-          <t>Based on straight-line amort, no sweep</t>
-        </is>
-      </c>
-      <c r="E106" s="18">
-        <f>MAX(0,$D$55-(1-1)*$D$57)*$D$40+$D$57</f>
-        <v/>
-      </c>
-      <c r="F106" s="18">
-        <f>MAX(0,$D$55-(2-1)*$D$57)*$D$40+$D$57</f>
-        <v/>
-      </c>
-      <c r="G106" s="18">
-        <f>MAX(0,$D$55-(3-1)*$D$57)*$D$40+$D$57</f>
-        <v/>
-      </c>
-      <c r="H106" s="18">
-        <f>MAX(0,$D$55-(4-1)*$D$57)*$D$40+$D$57</f>
-        <v/>
-      </c>
-      <c r="I106" s="18">
-        <f>MAX(0,$D$55-(5-1)*$D$57)*$D$40+$D$57</f>
-        <v/>
-      </c>
-      <c r="J106" s="18">
-        <f>MAX(0,$D$55-(6-1)*$D$57)*$D$40+$D$57</f>
-        <v/>
-      </c>
-      <c r="K106" s="18">
-        <f>MAX(0,$D$55-(7-1)*$D$57)*$D$40+$D$57</f>
-        <v/>
-      </c>
-      <c r="L106" s="18">
-        <f>MAX(0,$D$55-(8-1)*$D$57)*$D$40+$D$57</f>
-        <v/>
-      </c>
-      <c r="M106" s="18">
-        <f>MAX(0,$D$55-(9-1)*$D$57)*$D$40+$D$57</f>
-        <v/>
-      </c>
-      <c r="N106" s="18">
-        <f>MAX(0,$D$55-(10-1)*$D$57)*$D$40+$D$57</f>
-        <v/>
-      </c>
-    </row>
-    <row r="107"/>
-    <row r="108">
-      <c r="A108" s="3" t="inlineStr">
-        <is>
-          <t>DSRA (Debt Service Reserve Account)</t>
-        </is>
-      </c>
-      <c r="B108" s="4" t="n"/>
-      <c r="C108" s="4" t="n"/>
-      <c r="D108" s="4" t="n"/>
-      <c r="E108" s="4" t="n"/>
-      <c r="F108" s="4" t="n"/>
-      <c r="G108" s="4" t="n"/>
-      <c r="H108" s="4" t="n"/>
-      <c r="I108" s="4" t="n"/>
-      <c r="J108" s="4" t="n"/>
-      <c r="K108" s="4" t="n"/>
-      <c r="L108" s="4" t="n"/>
-      <c r="M108" s="4" t="n"/>
-      <c r="N108" s="4" t="n"/>
+      <c r="C108" s="6" t="inlineStr">
+        <is>
+          <t>Next Yr Scheduled DS × DSRA Months / 12</t>
+        </is>
+      </c>
+      <c r="D108" s="18">
+        <f>E93*$D$42/12</f>
+        <v/>
+      </c>
+      <c r="E108" s="18">
+        <f>F106*$D$53/12</f>
+        <v/>
+      </c>
+      <c r="F108" s="18">
+        <f>G106*$D$53/12</f>
+        <v/>
+      </c>
+      <c r="G108" s="18">
+        <f>H106*$D$53/12</f>
+        <v/>
+      </c>
+      <c r="H108" s="18">
+        <f>I106*$D$53/12</f>
+        <v/>
+      </c>
+      <c r="I108" s="18">
+        <f>J106*$D$53/12</f>
+        <v/>
+      </c>
+      <c r="J108" s="18">
+        <f>K106*$D$53/12</f>
+        <v/>
+      </c>
+      <c r="K108" s="18">
+        <f>L106*$D$53/12</f>
+        <v/>
+      </c>
+      <c r="L108" s="18">
+        <f>M106*$D$53/12</f>
+        <v/>
+      </c>
+      <c r="M108" s="18">
+        <f>N106*$D$53/12</f>
+        <v/>
+      </c>
+      <c r="N108" s="18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>DSRA Target</t>
+          <t>DSRA Beginning</t>
         </is>
       </c>
       <c r="B109" s="6" t="inlineStr">
@@ -5383,60 +5644,55 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C109" s="6" t="inlineStr">
-        <is>
-          <t>Next Yr Scheduled DS × DSRA Months / 12</t>
-        </is>
-      </c>
-      <c r="D109" s="18">
-        <f>E93*$D$42/12</f>
-        <v/>
+      <c r="C109" s="6" t="n"/>
+      <c r="D109" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="E109" s="18">
-        <f>F93*$D$42/12</f>
+        <f>D124</f>
         <v/>
       </c>
       <c r="F109" s="18">
-        <f>G93*$D$42/12</f>
+        <f>E111</f>
         <v/>
       </c>
       <c r="G109" s="18">
-        <f>H93*$D$42/12</f>
+        <f>F111</f>
         <v/>
       </c>
       <c r="H109" s="18">
-        <f>I93*$D$42/12</f>
+        <f>G111</f>
         <v/>
       </c>
       <c r="I109" s="18">
-        <f>J93*$D$42/12</f>
+        <f>H111</f>
         <v/>
       </c>
       <c r="J109" s="18">
-        <f>K93*$D$42/12</f>
+        <f>I111</f>
         <v/>
       </c>
       <c r="K109" s="18">
-        <f>L93*$D$42/12</f>
+        <f>J111</f>
         <v/>
       </c>
       <c r="L109" s="18">
-        <f>M93*$D$42/12</f>
+        <f>K111</f>
         <v/>
       </c>
       <c r="M109" s="18">
-        <f>N93*$D$42/12</f>
+        <f>L111</f>
         <v/>
       </c>
       <c r="N109" s="18">
-        <f>0</f>
+        <f>M111</f>
         <v/>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>DSRA Beginning</t>
+          <t>DSRA Funding/(Release)</t>
         </is>
       </c>
       <c r="B110" s="6" t="inlineStr">
@@ -5444,56 +5700,60 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C110" s="6" t="inlineStr"/>
+      <c r="C110" s="6" t="inlineStr">
+        <is>
+          <t>Target - Beginning</t>
+        </is>
+      </c>
       <c r="D110" s="18">
-        <f>0</f>
+        <f>D96-D97</f>
         <v/>
       </c>
       <c r="E110" s="18">
-        <f>D99</f>
+        <f>E108-E109</f>
         <v/>
       </c>
       <c r="F110" s="18">
-        <f>E99</f>
+        <f>F108-F109</f>
         <v/>
       </c>
       <c r="G110" s="18">
-        <f>F99</f>
+        <f>G108-G109</f>
         <v/>
       </c>
       <c r="H110" s="18">
-        <f>G99</f>
+        <f>H108-H109</f>
         <v/>
       </c>
       <c r="I110" s="18">
-        <f>H99</f>
+        <f>I108-I109</f>
         <v/>
       </c>
       <c r="J110" s="18">
-        <f>I99</f>
+        <f>J108-J109</f>
         <v/>
       </c>
       <c r="K110" s="18">
-        <f>J99</f>
+        <f>K108-K109</f>
         <v/>
       </c>
       <c r="L110" s="18">
-        <f>K99</f>
+        <f>L108-L109</f>
         <v/>
       </c>
       <c r="M110" s="18">
-        <f>L99</f>
+        <f>M108-M109</f>
         <v/>
       </c>
       <c r="N110" s="18">
-        <f>M99</f>
+        <f>N108-N109</f>
         <v/>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>DSRA Funding/(Release)</t>
+          <t>DSRA Ending</t>
         </is>
       </c>
       <c r="B111" s="6" t="inlineStr">
@@ -5503,284 +5763,303 @@
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>Target - Beginning</t>
+          <t>Beginning + Funding</t>
         </is>
       </c>
       <c r="D111" s="18">
-        <f>D96-D97</f>
+        <f>D97+D98</f>
         <v/>
       </c>
       <c r="E111" s="18">
-        <f>E96-E97</f>
+        <f>E109+E110</f>
         <v/>
       </c>
       <c r="F111" s="18">
-        <f>F96-F97</f>
+        <f>F109+F110</f>
         <v/>
       </c>
       <c r="G111" s="18">
-        <f>G96-G97</f>
+        <f>G109+G110</f>
         <v/>
       </c>
       <c r="H111" s="18">
-        <f>H96-H97</f>
+        <f>H109+H110</f>
         <v/>
       </c>
       <c r="I111" s="18">
-        <f>I96-I97</f>
+        <f>I109+I110</f>
         <v/>
       </c>
       <c r="J111" s="18">
-        <f>J96-J97</f>
+        <f>J109+J110</f>
         <v/>
       </c>
       <c r="K111" s="18">
-        <f>K96-K97</f>
+        <f>K109+K110</f>
         <v/>
       </c>
       <c r="L111" s="18">
-        <f>L96-L97</f>
+        <f>L109+L110</f>
         <v/>
       </c>
       <c r="M111" s="18">
-        <f>M96-M97</f>
+        <f>M109+M110</f>
         <v/>
       </c>
       <c r="N111" s="18">
-        <f>N96-N97</f>
+        <f>N109+N110</f>
         <v/>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="5" t="inlineStr">
-        <is>
-          <t>DSRA Ending</t>
-        </is>
-      </c>
-      <c r="B112" s="6" t="inlineStr">
+      <c r="A112" s="5" t="n"/>
+      <c r="B112" s="6" t="n"/>
+      <c r="C112" s="6" t="n"/>
+      <c r="D112" s="18" t="n"/>
+      <c r="E112" s="18" t="n"/>
+      <c r="F112" s="18" t="n"/>
+      <c r="G112" s="18" t="n"/>
+      <c r="H112" s="18" t="n"/>
+      <c r="I112" s="18" t="n"/>
+      <c r="J112" s="18" t="n"/>
+      <c r="K112" s="18" t="n"/>
+      <c r="L112" s="18" t="n"/>
+      <c r="M112" s="18" t="n"/>
+      <c r="N112" s="18" t="n"/>
+    </row>
+    <row r="113"/>
+    <row r="114">
+      <c r="A114" s="3" t="inlineStr">
+        <is>
+          <t>DISTRIBUTION WATERFALL</t>
+        </is>
+      </c>
+      <c r="B114" s="4" t="n"/>
+      <c r="C114" s="4" t="n"/>
+      <c r="D114" s="4" t="n"/>
+      <c r="E114" s="4" t="n"/>
+      <c r="F114" s="4" t="n"/>
+      <c r="G114" s="4" t="n"/>
+      <c r="H114" s="4" t="n"/>
+      <c r="I114" s="4" t="n"/>
+      <c r="J114" s="4" t="n"/>
+      <c r="K114" s="4" t="n"/>
+      <c r="L114" s="4" t="n"/>
+      <c r="M114" s="4" t="n"/>
+      <c r="N114" s="4" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="5" t="inlineStr">
+        <is>
+          <t>Cash Available for Distribution</t>
+        </is>
+      </c>
+      <c r="B115" s="6" t="inlineStr">
         <is>
           <t>$mm</t>
         </is>
       </c>
-      <c r="C112" s="6" t="inlineStr">
-        <is>
-          <t>Beginning + Funding</t>
-        </is>
-      </c>
-      <c r="D112" s="18">
-        <f>D97+D98</f>
-        <v/>
-      </c>
-      <c r="E112" s="18">
-        <f>E97+E98</f>
-        <v/>
-      </c>
-      <c r="F112" s="18">
-        <f>F97+F98</f>
-        <v/>
-      </c>
-      <c r="G112" s="18">
-        <f>G97+G98</f>
-        <v/>
-      </c>
-      <c r="H112" s="18">
-        <f>H97+H98</f>
-        <v/>
-      </c>
-      <c r="I112" s="18">
-        <f>I97+I98</f>
-        <v/>
-      </c>
-      <c r="J112" s="18">
-        <f>J97+J98</f>
-        <v/>
-      </c>
-      <c r="K112" s="18">
-        <f>K97+K98</f>
-        <v/>
-      </c>
-      <c r="L112" s="18">
-        <f>L97+L98</f>
-        <v/>
-      </c>
-      <c r="M112" s="18">
-        <f>M97+M98</f>
-        <v/>
-      </c>
-      <c r="N112" s="18">
-        <f>N97+N98</f>
-        <v/>
-      </c>
-    </row>
-    <row r="113"/>
-    <row r="114"/>
-    <row r="115">
-      <c r="A115" s="3" t="inlineStr">
-        <is>
-          <t>DISTRIBUTION WATERFALL</t>
-        </is>
-      </c>
-      <c r="B115" s="4" t="n"/>
-      <c r="C115" s="4" t="n"/>
+      <c r="C115" s="6" t="inlineStr">
+        <is>
+          <t>CFADS - Total DS - DSRA Fund</t>
+        </is>
+      </c>
       <c r="D115" s="4" t="n"/>
-      <c r="E115" s="4" t="n"/>
-      <c r="F115" s="4" t="n"/>
-      <c r="G115" s="4" t="n"/>
-      <c r="H115" s="4" t="n"/>
-      <c r="I115" s="4" t="n"/>
-      <c r="J115" s="4" t="n"/>
-      <c r="K115" s="4" t="n"/>
-      <c r="L115" s="4" t="n"/>
-      <c r="M115" s="4" t="n"/>
-      <c r="N115" s="4" t="n"/>
+      <c r="E115" s="18">
+        <f>E92-E97-E102-E110</f>
+        <v/>
+      </c>
+      <c r="F115" s="18">
+        <f>F92-F97-F102-F110</f>
+        <v/>
+      </c>
+      <c r="G115" s="18">
+        <f>G92-G97-G102-G110</f>
+        <v/>
+      </c>
+      <c r="H115" s="18">
+        <f>H92-H97-H102-H110</f>
+        <v/>
+      </c>
+      <c r="I115" s="18">
+        <f>I92-I97-I102-I110</f>
+        <v/>
+      </c>
+      <c r="J115" s="18">
+        <f>J92-J97-J102-J110</f>
+        <v/>
+      </c>
+      <c r="K115" s="18">
+        <f>K92-K97-K102-K110</f>
+        <v/>
+      </c>
+      <c r="L115" s="18">
+        <f>L92-L97-L102-L110</f>
+        <v/>
+      </c>
+      <c r="M115" s="18">
+        <f>M92-M97-M102-M110</f>
+        <v/>
+      </c>
+      <c r="N115" s="18">
+        <f>N92-N97-N102-N110</f>
+        <v/>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>Cash Available for Distribution</t>
-        </is>
-      </c>
-      <c r="B116" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
+          <t>Lock-up Test</t>
+        </is>
+      </c>
+      <c r="B116" s="6" t="n"/>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t>CFADS - Total DS - DSRA Fund</t>
-        </is>
-      </c>
-      <c r="E116" s="18">
-        <f>E80-(E85+E90)-E98</f>
-        <v/>
-      </c>
-      <c r="F116" s="18">
-        <f>F80-(F85+F90)-F98</f>
-        <v/>
-      </c>
-      <c r="G116" s="18">
-        <f>G80-(G85+G90)-G98</f>
-        <v/>
-      </c>
-      <c r="H116" s="18">
-        <f>H80-(H85+H90)-H98</f>
-        <v/>
-      </c>
-      <c r="I116" s="18">
-        <f>I80-(I85+I90)-I98</f>
-        <v/>
-      </c>
-      <c r="J116" s="18">
-        <f>J80-(J85+J90)-J98</f>
-        <v/>
-      </c>
-      <c r="K116" s="18">
-        <f>K80-(K85+K90)-K98</f>
-        <v/>
-      </c>
-      <c r="L116" s="18">
-        <f>L80-(L85+L90)-L98</f>
-        <v/>
-      </c>
-      <c r="M116" s="18">
-        <f>M80-(M85+M90)-M98</f>
-        <v/>
-      </c>
-      <c r="N116" s="18">
-        <f>N80-(N85+N90)-N98</f>
+          <t>PASS if DSCR ≥ Lock-up</t>
+        </is>
+      </c>
+      <c r="E116" s="22">
+        <f>IF(E104&gt;=$D$55,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="F116" s="22">
+        <f>IF(F104&gt;=$D$55,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="G116" s="22">
+        <f>IF(G104&gt;=$D$55,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="H116" s="22">
+        <f>IF(H104&gt;=$D$55,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="I116" s="22">
+        <f>IF(I104&gt;=$D$55,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="J116" s="22">
+        <f>IF(J104&gt;=$D$55,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="K116" s="22">
+        <f>IF(K104&gt;=$D$55,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="L116" s="22">
+        <f>IF(L104&gt;=$D$55,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="M116" s="22">
+        <f>IF(M104&gt;=$D$55,"PASS","LOCKED")</f>
+        <v/>
+      </c>
+      <c r="N116" s="22">
+        <f>IF(N104&gt;=$D$55,"PASS","LOCKED")</f>
         <v/>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>Lock-up Test</t>
-        </is>
-      </c>
-      <c r="B117" s="6" t="inlineStr"/>
+          <t>Distributable Cash</t>
+        </is>
+      </c>
+      <c r="B117" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>PASS if DSCR ≥ Lock-up</t>
-        </is>
-      </c>
-      <c r="E117" s="22">
-        <f>IF(E92&gt;=$D$44,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="F117" s="22">
-        <f>IF(F92&gt;=$D$44,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="G117" s="22">
-        <f>IF(G92&gt;=$D$44,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="H117" s="22">
-        <f>IF(H92&gt;=$D$44,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="I117" s="22">
-        <f>IF(I92&gt;=$D$44,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="J117" s="22">
-        <f>IF(J92&gt;=$D$44,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="K117" s="22">
-        <f>IF(K92&gt;=$D$44,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="L117" s="22">
-        <f>IF(L92&gt;=$D$44,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="M117" s="22">
-        <f>IF(M92&gt;=$D$44,"PASS","LOCKED")</f>
-        <v/>
-      </c>
-      <c r="N117" s="22">
-        <f>IF(N92&gt;=$D$44,"PASS","LOCKED")</f>
+          <t>If PASS, MAX(0, Cash Avail)</t>
+        </is>
+      </c>
+      <c r="E117" s="7">
+        <f>IF(E116="PASS",MAX(0,E115),0)</f>
+        <v/>
+      </c>
+      <c r="F117" s="7">
+        <f>IF(F116="PASS",MAX(0,F115),0)</f>
+        <v/>
+      </c>
+      <c r="G117" s="7">
+        <f>IF(G116="PASS",MAX(0,G115),0)</f>
+        <v/>
+      </c>
+      <c r="H117" s="7">
+        <f>IF(H116="PASS",MAX(0,H115),0)</f>
+        <v/>
+      </c>
+      <c r="I117" s="7">
+        <f>IF(I116="PASS",MAX(0,I115),0)</f>
+        <v/>
+      </c>
+      <c r="J117" s="7">
+        <f>IF(J116="PASS",MAX(0,J115),0)</f>
+        <v/>
+      </c>
+      <c r="K117" s="7">
+        <f>IF(K116="PASS",MAX(0,K115),0)</f>
+        <v/>
+      </c>
+      <c r="L117" s="7">
+        <f>IF(L116="PASS",MAX(0,L115),0)</f>
+        <v/>
+      </c>
+      <c r="M117" s="7">
+        <f>IF(M116="PASS",MAX(0,M115),0)</f>
+        <v/>
+      </c>
+      <c r="N117" s="7">
+        <f>IF(N116="PASS",MAX(0,N115),0)</f>
         <v/>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="5" t="inlineStr">
-        <is>
-          <t>Distributable Cash</t>
-        </is>
-      </c>
-      <c r="B118" s="6" t="inlineStr">
-        <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C118" s="6" t="inlineStr">
-        <is>
-          <t>If PASS, MAX(0, Cash Avail)</t>
-        </is>
-      </c>
-      <c r="E118" s="7" t="inlineStr"/>
-      <c r="F118" s="7" t="inlineStr"/>
-      <c r="G118" s="7" t="inlineStr"/>
-      <c r="H118" s="7" t="inlineStr"/>
-      <c r="I118" s="7" t="inlineStr"/>
-      <c r="J118" s="7" t="inlineStr"/>
-      <c r="K118" s="7" t="inlineStr"/>
-      <c r="L118" s="7" t="inlineStr"/>
-      <c r="M118" s="7" t="inlineStr"/>
-      <c r="N118" s="7" t="inlineStr"/>
+      <c r="A118" s="5" t="n"/>
+      <c r="B118" s="6" t="n"/>
+      <c r="C118" s="6" t="n"/>
+      <c r="E118" s="7" t="n"/>
+      <c r="F118" s="7" t="n"/>
+      <c r="G118" s="7" t="n"/>
+      <c r="H118" s="7" t="n"/>
+      <c r="I118" s="7" t="n"/>
+      <c r="J118" s="7" t="n"/>
+      <c r="K118" s="7" t="n"/>
+      <c r="L118" s="7" t="n"/>
+      <c r="M118" s="7" t="n"/>
+      <c r="N118" s="7" t="n"/>
     </row>
     <row r="119"/>
-    <row r="120"/>
+    <row r="120">
+      <c r="A120" s="3" t="inlineStr">
+        <is>
+          <t>SOURCES &amp; USES (Year 0)</t>
+        </is>
+      </c>
+      <c r="B120" s="4" t="n"/>
+      <c r="C120" s="4" t="n"/>
+      <c r="D120" s="4" t="n"/>
+      <c r="E120" s="4" t="n"/>
+      <c r="F120" s="4" t="n"/>
+      <c r="G120" s="4" t="n"/>
+      <c r="H120" s="4" t="n"/>
+      <c r="I120" s="4" t="n"/>
+      <c r="J120" s="4" t="n"/>
+      <c r="K120" s="4" t="n"/>
+      <c r="L120" s="4" t="n"/>
+      <c r="M120" s="4" t="n"/>
+      <c r="N120" s="4" t="n"/>
+    </row>
     <row r="121">
-      <c r="A121" s="3" t="inlineStr">
-        <is>
-          <t>SOURCES &amp; USES (Year 0)</t>
-        </is>
-      </c>
-      <c r="B121" s="4" t="n"/>
-      <c r="C121" s="4" t="n"/>
+      <c r="A121" s="23" t="inlineStr">
+        <is>
+          <t>USES</t>
+        </is>
+      </c>
+      <c r="B121" s="6" t="n"/>
+      <c r="C121" s="6" t="n"/>
       <c r="D121" s="4" t="n"/>
       <c r="E121" s="4" t="n"/>
       <c r="F121" s="4" t="n"/>
@@ -5794,18 +6073,26 @@
       <c r="N121" s="4" t="n"/>
     </row>
     <row r="122">
-      <c r="A122" s="23" t="inlineStr">
-        <is>
-          <t>USES</t>
-        </is>
-      </c>
-      <c r="B122" s="6" t="inlineStr"/>
-      <c r="C122" s="6" t="inlineStr"/>
+      <c r="A122" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Purchase Price</t>
+        </is>
+      </c>
+      <c r="B122" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C122" s="6" t="n"/>
+      <c r="D122" s="18">
+        <f>$D$28</f>
+        <v/>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Purchase Price</t>
+          <t xml:space="preserve">  Transaction Fees</t>
         </is>
       </c>
       <c r="B123" s="6" t="inlineStr">
@@ -5813,16 +6100,16 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C123" s="6" t="inlineStr"/>
+      <c r="C123" s="6" t="n"/>
       <c r="D123" s="18">
-        <f>$D$17</f>
+        <f>$D$28*$D$29</f>
         <v/>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Transaction Fees</t>
+          <t xml:space="preserve">  DSRA Funding</t>
         </is>
       </c>
       <c r="B124" s="6" t="inlineStr">
@@ -5830,16 +6117,16 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C124" s="6" t="inlineStr"/>
+      <c r="C124" s="6" t="n"/>
       <c r="D124" s="18">
-        <f>$D$17*$D$18</f>
+        <f>E108</f>
         <v/>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  DSRA Funding</t>
+          <t>Total Uses</t>
         </is>
       </c>
       <c r="B125" s="6" t="inlineStr">
@@ -5847,43 +6134,55 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C125" s="6" t="inlineStr"/>
-      <c r="D125" s="18">
-        <f>D96</f>
+      <c r="C125" s="6" t="n"/>
+      <c r="D125" s="7">
+        <f>D122+D123+D124</f>
         <v/>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="5" t="inlineStr">
-        <is>
-          <t>Total Uses</t>
-        </is>
-      </c>
-      <c r="B126" s="6" t="inlineStr">
+      <c r="A126" s="5" t="n"/>
+      <c r="B126" s="6" t="n"/>
+      <c r="C126" s="6" t="n"/>
+      <c r="D126" s="7">
+        <f>$D$28*$D$29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="23" t="inlineStr">
+        <is>
+          <t>SOURCES</t>
+        </is>
+      </c>
+      <c r="B127" s="6" t="n"/>
+      <c r="C127" s="6" t="n"/>
+      <c r="D127">
+        <f>E108</f>
+        <v/>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Debt</t>
+        </is>
+      </c>
+      <c r="B128" s="6" t="inlineStr">
         <is>
           <t>$mm</t>
         </is>
       </c>
-      <c r="C126" s="6" t="inlineStr"/>
-      <c r="D126" s="7">
-        <f>D110+D111+D112</f>
-        <v/>
-      </c>
-    </row>
-    <row r="127"/>
-    <row r="128">
-      <c r="A128" s="23" t="inlineStr">
-        <is>
-          <t>SOURCES</t>
-        </is>
-      </c>
-      <c r="B128" s="6" t="inlineStr"/>
-      <c r="C128" s="6" t="inlineStr"/>
+      <c r="C128" s="6" t="n"/>
+      <c r="D128" s="18">
+        <f>$D$28*$D$50</f>
+        <v/>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Debt</t>
+          <t xml:space="preserve">  Equity</t>
         </is>
       </c>
       <c r="B129" s="6" t="inlineStr">
@@ -5891,16 +6190,20 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C129" s="6" t="inlineStr"/>
+      <c r="C129" s="6" t="inlineStr">
+        <is>
+          <t>Plug to balance</t>
+        </is>
+      </c>
       <c r="D129" s="18">
-        <f>$D$55</f>
+        <f>D125-D128</f>
         <v/>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Equity</t>
+          <t>Total Sources</t>
         </is>
       </c>
       <c r="B130" s="6" t="inlineStr">
@@ -5908,64 +6211,90 @@
           <t>$mm</t>
         </is>
       </c>
-      <c r="C130" s="6" t="inlineStr">
-        <is>
-          <t>Plug to balance</t>
-        </is>
-      </c>
-      <c r="D130" s="18">
-        <f>D113-D116</f>
+      <c r="C130" s="6" t="n"/>
+      <c r="D130" s="7">
+        <f>D128+D129</f>
         <v/>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="5" t="inlineStr">
         <is>
-          <t>Total Sources</t>
-        </is>
-      </c>
-      <c r="B131" s="6" t="inlineStr">
+          <t>Balance Check</t>
+        </is>
+      </c>
+      <c r="B131" s="6" t="n"/>
+      <c r="C131" s="6" t="n"/>
+      <c r="D131" s="10">
+        <f>$D$28*$D$50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="5" t="n"/>
+      <c r="B132" s="6" t="n"/>
+      <c r="C132" s="6" t="n"/>
+      <c r="D132" s="10">
+        <f>D125-D130</f>
+        <v/>
+      </c>
+    </row>
+    <row r="133">
+      <c r="D133">
+        <f>D131+D132</f>
+        <v/>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="3" t="inlineStr">
+        <is>
+          <t>EXIT CALCULATIONS</t>
+        </is>
+      </c>
+      <c r="B134" s="4" t="n"/>
+      <c r="C134" s="4" t="n"/>
+      <c r="D134" s="4" t="n"/>
+      <c r="E134" s="4" t="n"/>
+      <c r="F134" s="4" t="n"/>
+      <c r="G134" s="4" t="n"/>
+      <c r="H134" s="4" t="n"/>
+      <c r="I134" s="4" t="n"/>
+      <c r="J134" s="4" t="n"/>
+      <c r="K134" s="4" t="n"/>
+      <c r="L134" s="4" t="n"/>
+      <c r="M134" s="4" t="n"/>
+      <c r="N134" s="4" t="n"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="5" t="inlineStr">
+        <is>
+          <t>Exit EV</t>
+        </is>
+      </c>
+      <c r="B135" s="6" t="inlineStr">
         <is>
           <t>$mm</t>
         </is>
       </c>
-      <c r="C131" s="6" t="inlineStr"/>
-      <c r="D131" s="7">
-        <f>D116+D117</f>
-        <v/>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="5" t="inlineStr">
-        <is>
-          <t>Balance Check</t>
-        </is>
-      </c>
-      <c r="B132" s="6" t="inlineStr"/>
-      <c r="C132" s="6" t="inlineStr"/>
-      <c r="D132" s="10">
-        <f>IF(ABS(D113-D118)&lt;0.01,"PASS","FAIL")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="133"/>
-    <row r="134"/>
-    <row r="135">
-      <c r="A135" s="3" t="inlineStr">
-        <is>
-          <t>EXIT CALCULATIONS</t>
-        </is>
-      </c>
-      <c r="B135" s="4" t="n"/>
-      <c r="C135" s="4" t="n"/>
-      <c r="D135" s="4" t="n"/>
+      <c r="C135" s="6" t="inlineStr">
+        <is>
+          <t>Exit Multiple × Exit Yr EBITDA</t>
+        </is>
+      </c>
+      <c r="D135" s="4">
+        <f>D128-D133</f>
+        <v/>
+      </c>
       <c r="E135" s="4" t="n"/>
       <c r="F135" s="4" t="n"/>
       <c r="G135" s="4" t="n"/>
       <c r="H135" s="4" t="n"/>
       <c r="I135" s="4" t="n"/>
       <c r="J135" s="4" t="n"/>
-      <c r="K135" s="4" t="n"/>
+      <c r="K135" s="18">
+        <f>$D$19*K74</f>
+        <v/>
+      </c>
       <c r="L135" s="4" t="n"/>
       <c r="M135" s="4" t="n"/>
       <c r="N135" s="4" t="n"/>
@@ -5973,7 +6302,7 @@
     <row r="136">
       <c r="A136" s="5" t="inlineStr">
         <is>
-          <t>Exit EV</t>
+          <t>Exit Debt Payoff</t>
         </is>
       </c>
       <c r="B136" s="6" t="inlineStr">
@@ -5983,15 +6312,18 @@
       </c>
       <c r="C136" s="6" t="inlineStr">
         <is>
-          <t>Exit Multiple × Exit Yr EBITDA</t>
-        </is>
-      </c>
-      <c r="K136" s="18" t="inlineStr"/>
+          <t>Ending Bal at Exit</t>
+        </is>
+      </c>
+      <c r="K136" s="18">
+        <f>K91</f>
+        <v/>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="5" t="inlineStr">
         <is>
-          <t>Exit Debt Payoff</t>
+          <t>DSRA Release</t>
         </is>
       </c>
       <c r="B137" s="6" t="inlineStr">
@@ -6001,18 +6333,18 @@
       </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
-          <t>Ending Bal at Exit</t>
+          <t>DSRA Ending at Exit</t>
         </is>
       </c>
       <c r="K137" s="18">
-        <f>K91</f>
+        <f>K99</f>
         <v/>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
         <is>
-          <t>DSRA Release</t>
+          <t>Exit Equity Proceeds</t>
         </is>
       </c>
       <c r="B138" s="6" t="inlineStr">
@@ -6022,190 +6354,271 @@
       </c>
       <c r="C138" s="6" t="inlineStr">
         <is>
-          <t>DSRA Ending at Exit</t>
-        </is>
-      </c>
-      <c r="K138" s="18">
-        <f>K99</f>
+          <t>Exit EV - Debt + DSRA</t>
+        </is>
+      </c>
+      <c r="K138" s="7">
+        <f>K123-K124+K125</f>
         <v/>
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="5" t="inlineStr">
-        <is>
-          <t>Exit Equity Proceeds</t>
-        </is>
-      </c>
-      <c r="B139" s="6" t="inlineStr">
+      <c r="A139" s="5" t="n"/>
+      <c r="B139" s="6" t="n"/>
+      <c r="C139" s="6" t="n"/>
+      <c r="D139">
+        <f>K86</f>
+        <v/>
+      </c>
+      <c r="K139" s="7" t="n"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="3" t="inlineStr">
+        <is>
+          <t>EQUITY RETURNS</t>
+        </is>
+      </c>
+      <c r="B140" s="4" t="n"/>
+      <c r="C140" s="4" t="n"/>
+      <c r="D140" s="4">
+        <f>D139*$D$30</f>
+        <v/>
+      </c>
+      <c r="E140" s="4" t="n"/>
+      <c r="F140" s="4" t="n"/>
+      <c r="G140" s="4" t="n"/>
+      <c r="H140" s="4" t="n"/>
+      <c r="I140" s="4" t="n"/>
+      <c r="J140" s="4" t="n"/>
+      <c r="K140" s="4" t="n"/>
+      <c r="L140" s="4" t="n"/>
+      <c r="M140" s="4" t="n"/>
+      <c r="N140" s="4" t="n"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="5" t="inlineStr">
+        <is>
+          <t>Equity Cash Flow</t>
+        </is>
+      </c>
+      <c r="B141" s="6" t="inlineStr">
         <is>
           <t>$mm</t>
         </is>
       </c>
-      <c r="C139" s="6" t="inlineStr">
-        <is>
-          <t>Exit EV - Debt + DSRA</t>
-        </is>
-      </c>
-      <c r="K139" s="7" t="inlineStr"/>
-    </row>
-    <row r="140"/>
-    <row r="141">
-      <c r="A141" s="3" t="inlineStr">
-        <is>
-          <t>EQUITY RETURNS</t>
-        </is>
-      </c>
-      <c r="B141" s="4" t="n"/>
-      <c r="C141" s="4" t="n"/>
-      <c r="D141" s="4" t="n"/>
-      <c r="E141" s="4" t="n"/>
-      <c r="F141" s="4" t="n"/>
-      <c r="G141" s="4" t="n"/>
-      <c r="H141" s="4" t="n"/>
-      <c r="I141" s="4" t="n"/>
-      <c r="J141" s="4" t="n"/>
-      <c r="K141" s="4" t="n"/>
-      <c r="L141" s="4" t="n"/>
-      <c r="M141" s="4" t="n"/>
-      <c r="N141" s="4" t="n"/>
+      <c r="C141" s="6" t="n"/>
+      <c r="D141" s="18">
+        <f>K103</f>
+        <v/>
+      </c>
+      <c r="E141" s="18">
+        <f>E105</f>
+        <v/>
+      </c>
+      <c r="F141" s="18">
+        <f>F105</f>
+        <v/>
+      </c>
+      <c r="G141" s="18">
+        <f>G105</f>
+        <v/>
+      </c>
+      <c r="H141" s="18">
+        <f>H105</f>
+        <v/>
+      </c>
+      <c r="I141" s="18">
+        <f>I105</f>
+        <v/>
+      </c>
+      <c r="J141" s="18">
+        <f>J105</f>
+        <v/>
+      </c>
+      <c r="K141" s="18">
+        <f>K105+K126</f>
+        <v/>
+      </c>
+      <c r="L141" s="18">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="M141" s="18">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="N141" s="18">
+        <f>0</f>
+        <v/>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="5" t="inlineStr">
         <is>
-          <t>Equity Cash Flow</t>
+          <t>Levered IRR</t>
         </is>
       </c>
       <c r="B142" s="6" t="inlineStr">
         <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C142" s="6" t="inlineStr"/>
-      <c r="D142" s="18" t="inlineStr"/>
-      <c r="E142" s="18" t="inlineStr"/>
-      <c r="F142" s="18" t="inlineStr"/>
-      <c r="G142" s="18" t="inlineStr"/>
-      <c r="H142" s="18" t="inlineStr"/>
-      <c r="I142" s="18" t="inlineStr"/>
-      <c r="J142" s="18" t="inlineStr"/>
-      <c r="K142" s="18" t="inlineStr"/>
-      <c r="L142" s="18" t="inlineStr"/>
-      <c r="M142" s="18" t="inlineStr"/>
-      <c r="N142" s="18" t="inlineStr"/>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C142" s="6" t="inlineStr">
+        <is>
+          <t>IRR of Equity CFs</t>
+        </is>
+      </c>
+      <c r="D142" s="31">
+        <f>K111</f>
+        <v/>
+      </c>
+      <c r="E142" s="18" t="n"/>
+      <c r="F142" s="18" t="n"/>
+      <c r="G142" s="18" t="n"/>
+      <c r="H142" s="18" t="n"/>
+      <c r="I142" s="18" t="n"/>
+      <c r="J142" s="18" t="n"/>
+      <c r="K142" s="18" t="n"/>
+      <c r="L142" s="18" t="n"/>
+      <c r="M142" s="18" t="n"/>
+      <c r="N142" s="18" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="5" t="inlineStr">
         <is>
-          <t>Levered IRR</t>
+          <t>MOIC</t>
         </is>
       </c>
       <c r="B143" s="6" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C143" s="6" t="inlineStr"/>
-      <c r="D143" s="31" t="inlineStr"/>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C143" s="6" t="inlineStr">
+        <is>
+          <t>Sum inflows / outflow</t>
+        </is>
+      </c>
+      <c r="D143" s="30">
+        <f>D140-D141+D142</f>
+        <v/>
+      </c>
     </row>
     <row r="144">
-      <c r="A144" s="5" t="inlineStr">
-        <is>
-          <t>MOIC</t>
-        </is>
-      </c>
-      <c r="B144" s="6" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="C144" s="6" t="inlineStr">
-        <is>
-          <t>Sum inflows / outflow</t>
-        </is>
-      </c>
-      <c r="D144" s="30" t="inlineStr"/>
-    </row>
-    <row r="145"/>
+      <c r="A144" s="5" t="n"/>
+      <c r="B144" s="6" t="n"/>
+      <c r="C144" s="6" t="n"/>
+      <c r="D144" s="30" t="n"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="23" t="inlineStr">
+        <is>
+          <t>Unlevered Returns (for reference)</t>
+        </is>
+      </c>
+      <c r="B145" s="6" t="n"/>
+      <c r="C145" s="6" t="n"/>
+    </row>
     <row r="146">
-      <c r="A146" s="23" t="inlineStr">
-        <is>
-          <t>Unlevered Returns (for reference)</t>
-        </is>
-      </c>
-      <c r="B146" s="6" t="inlineStr"/>
-      <c r="C146" s="6" t="inlineStr"/>
+      <c r="A146" s="5" t="inlineStr">
+        <is>
+          <t>Unlevered Cash Flow</t>
+        </is>
+      </c>
+      <c r="B146" s="6" t="inlineStr">
+        <is>
+          <t>$mm</t>
+        </is>
+      </c>
+      <c r="C146" s="6" t="n"/>
+      <c r="D146" s="18">
+        <f>-D129</f>
+        <v/>
+      </c>
+      <c r="E146" s="18">
+        <f>E117</f>
+        <v/>
+      </c>
+      <c r="F146" s="18">
+        <f>F117</f>
+        <v/>
+      </c>
+      <c r="G146" s="18">
+        <f>G117</f>
+        <v/>
+      </c>
+      <c r="H146" s="18">
+        <f>H117</f>
+        <v/>
+      </c>
+      <c r="I146" s="18">
+        <f>I117</f>
+        <v/>
+      </c>
+      <c r="J146" s="18">
+        <f>J117</f>
+        <v/>
+      </c>
+      <c r="K146" s="18">
+        <f>K117+D143</f>
+        <v/>
+      </c>
+      <c r="L146" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M146" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N146" s="18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="5" t="inlineStr">
         <is>
-          <t>Unlevered Cash Flow</t>
+          <t>Unlevered IRR</t>
         </is>
       </c>
       <c r="B147" s="6" t="inlineStr">
         <is>
-          <t>$mm</t>
-        </is>
-      </c>
-      <c r="C147" s="6" t="inlineStr"/>
-      <c r="D147" s="18">
-        <f>-$D$17-D111</f>
-        <v/>
-      </c>
-      <c r="E147" s="18">
-        <f>E80</f>
-        <v/>
-      </c>
-      <c r="F147" s="18">
-        <f>F80</f>
-        <v/>
-      </c>
-      <c r="G147" s="18">
-        <f>G80</f>
-        <v/>
-      </c>
-      <c r="H147" s="18">
-        <f>H80</f>
-        <v/>
-      </c>
-      <c r="I147" s="18">
-        <f>I80</f>
-        <v/>
-      </c>
-      <c r="J147" s="18">
-        <f>J80</f>
-        <v/>
-      </c>
-      <c r="K147" s="18">
-        <f>K80+K123</f>
-        <v/>
-      </c>
-      <c r="L147" s="18">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="M147" s="18">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="N147" s="18">
-        <f>0</f>
-        <v/>
-      </c>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C147" s="6" t="inlineStr">
+        <is>
+          <t>IRR of Equity CFs</t>
+        </is>
+      </c>
+      <c r="D147" s="31" t="n"/>
+      <c r="E147" s="18" t="n"/>
+      <c r="F147" s="18" t="n"/>
+      <c r="G147" s="18" t="n"/>
+      <c r="H147" s="18" t="n"/>
+      <c r="I147" s="18" t="n"/>
+      <c r="J147" s="18" t="n"/>
+      <c r="K147" s="18" t="n"/>
+      <c r="L147" s="18" t="n"/>
+      <c r="M147" s="18" t="n"/>
+      <c r="N147" s="18" t="n"/>
     </row>
     <row r="148">
-      <c r="A148" s="5" t="inlineStr">
-        <is>
-          <t>Unlevered IRR</t>
-        </is>
-      </c>
-      <c r="B148" s="6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C148" s="6" t="inlineStr"/>
-      <c r="D148" s="31" t="inlineStr"/>
-    </row>
+      <c r="A148" s="5" t="n"/>
+      <c r="B148" s="6" t="n"/>
+      <c r="C148" s="6" t="n"/>
+      <c r="D148" s="60" t="n"/>
+    </row>
+    <row r="149"/>
+    <row r="150"/>
+    <row r="151"/>
+    <row r="152"/>
+    <row r="153"/>
+    <row r="154"/>
+    <row r="155"/>
+    <row r="156"/>
+    <row r="157"/>
+    <row r="158"/>
+    <row r="159"/>
+    <row r="160"/>
   </sheetData>
   <dataValidations count="3">
     <dataValidation sqref="D7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">

--- a/deliverables/deliverables-20260120-0030/Drill_1_CCGT.xlsx
+++ b/deliverables/deliverables-20260120-0030/Drill_1_CCGT.xlsx
@@ -3184,7 +3184,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N160"/>
+  <dimension ref="A1:N159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -3268,7 +3268,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>═══ DRILL MODE - Fill in yellow cells ═══</t>
+          <t>═══ AUDIT STRIP ═══</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -4675,16 +4675,46 @@
           <t>Generation × Power Price / 1M</t>
         </is>
       </c>
-      <c r="E76" s="18" t="n"/>
-      <c r="F76" s="18" t="n"/>
-      <c r="G76" s="18" t="n"/>
-      <c r="H76" s="18" t="n"/>
-      <c r="I76" s="18" t="n"/>
-      <c r="J76" s="18" t="n"/>
-      <c r="K76" s="18" t="n"/>
-      <c r="L76" s="18" t="n"/>
-      <c r="M76" s="18" t="n"/>
-      <c r="N76" s="18" t="n"/>
+      <c r="E76" s="18">
+        <f>$D$65*E72/1000000</f>
+        <v/>
+      </c>
+      <c r="F76" s="18">
+        <f>$D$65*F72/1000000</f>
+        <v/>
+      </c>
+      <c r="G76" s="18">
+        <f>$D$65*G72/1000000</f>
+        <v/>
+      </c>
+      <c r="H76" s="18">
+        <f>$D$65*H72/1000000</f>
+        <v/>
+      </c>
+      <c r="I76" s="18">
+        <f>$D$65*I72/1000000</f>
+        <v/>
+      </c>
+      <c r="J76" s="18">
+        <f>$D$65*J72/1000000</f>
+        <v/>
+      </c>
+      <c r="K76" s="18">
+        <f>$D$65*K72/1000000</f>
+        <v/>
+      </c>
+      <c r="L76" s="18">
+        <f>$D$65*L72/1000000</f>
+        <v/>
+      </c>
+      <c r="M76" s="18">
+        <f>$D$65*M72/1000000</f>
+        <v/>
+      </c>
+      <c r="N76" s="18">
+        <f>$D$65*N72/1000000</f>
+        <v/>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
@@ -4702,16 +4732,46 @@
           <t>UCAP × Cap Price × 1000 / 1M</t>
         </is>
       </c>
-      <c r="E77" s="18" t="n"/>
-      <c r="F77" s="18" t="n"/>
-      <c r="G77" s="18" t="n"/>
-      <c r="H77" s="18" t="n"/>
-      <c r="I77" s="18" t="n"/>
-      <c r="J77" s="18" t="n"/>
-      <c r="K77" s="18" t="n"/>
-      <c r="L77" s="18" t="n"/>
-      <c r="M77" s="18" t="n"/>
-      <c r="N77" s="18" t="n"/>
+      <c r="E77" s="18">
+        <f>$D$34*E73*1000/1000000</f>
+        <v/>
+      </c>
+      <c r="F77" s="18">
+        <f>$D$34*F73*1000/1000000</f>
+        <v/>
+      </c>
+      <c r="G77" s="18">
+        <f>$D$34*G73*1000/1000000</f>
+        <v/>
+      </c>
+      <c r="H77" s="18">
+        <f>$D$34*H73*1000/1000000</f>
+        <v/>
+      </c>
+      <c r="I77" s="18">
+        <f>$D$34*I73*1000/1000000</f>
+        <v/>
+      </c>
+      <c r="J77" s="18">
+        <f>$D$34*J73*1000/1000000</f>
+        <v/>
+      </c>
+      <c r="K77" s="18">
+        <f>$D$34*K73*1000/1000000</f>
+        <v/>
+      </c>
+      <c r="L77" s="18">
+        <f>$D$34*L73*1000/1000000</f>
+        <v/>
+      </c>
+      <c r="M77" s="18">
+        <f>$D$34*M73*1000/1000000</f>
+        <v/>
+      </c>
+      <c r="N77" s="18">
+        <f>$D$34*N73*1000/1000000</f>
+        <v/>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
@@ -4725,16 +4785,46 @@
         </is>
       </c>
       <c r="C78" s="6" t="n"/>
-      <c r="E78" s="20" t="n"/>
-      <c r="F78" s="20" t="n"/>
-      <c r="G78" s="20" t="n"/>
-      <c r="H78" s="20" t="n"/>
-      <c r="I78" s="20" t="n"/>
-      <c r="J78" s="20" t="n"/>
-      <c r="K78" s="20" t="n"/>
-      <c r="L78" s="20" t="n"/>
-      <c r="M78" s="20" t="n"/>
-      <c r="N78" s="20" t="n"/>
+      <c r="E78" s="20">
+        <f>E76+E77</f>
+        <v/>
+      </c>
+      <c r="F78" s="20">
+        <f>F76+F77</f>
+        <v/>
+      </c>
+      <c r="G78" s="20">
+        <f>G76+G77</f>
+        <v/>
+      </c>
+      <c r="H78" s="20">
+        <f>H76+H77</f>
+        <v/>
+      </c>
+      <c r="I78" s="20">
+        <f>I76+I77</f>
+        <v/>
+      </c>
+      <c r="J78" s="20">
+        <f>J76+J77</f>
+        <v/>
+      </c>
+      <c r="K78" s="20">
+        <f>K76+K77</f>
+        <v/>
+      </c>
+      <c r="L78" s="20">
+        <f>L76+L77</f>
+        <v/>
+      </c>
+      <c r="M78" s="20">
+        <f>M76+M77</f>
+        <v/>
+      </c>
+      <c r="N78" s="20">
+        <f>N76+N77</f>
+        <v/>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="n"/>
@@ -4767,16 +4857,46 @@
           <t>Gen × HR × Gas / 1B</t>
         </is>
       </c>
-      <c r="E80" s="18" t="n"/>
-      <c r="F80" s="18" t="n"/>
-      <c r="G80" s="18" t="n"/>
-      <c r="H80" s="18" t="n"/>
-      <c r="I80" s="18" t="n"/>
-      <c r="J80" s="18" t="n"/>
-      <c r="K80" s="18" t="n"/>
-      <c r="L80" s="18" t="n"/>
-      <c r="M80" s="18" t="n"/>
-      <c r="N80" s="18" t="n"/>
+      <c r="E80" s="18">
+        <f>$D$65*$D$35*E74/1000000000</f>
+        <v/>
+      </c>
+      <c r="F80" s="18">
+        <f>$D$65*$D$35*F74/1000000000</f>
+        <v/>
+      </c>
+      <c r="G80" s="18">
+        <f>$D$65*$D$35*G74/1000000000</f>
+        <v/>
+      </c>
+      <c r="H80" s="18">
+        <f>$D$65*$D$35*H74/1000000000</f>
+        <v/>
+      </c>
+      <c r="I80" s="18">
+        <f>$D$65*$D$35*I74/1000000000</f>
+        <v/>
+      </c>
+      <c r="J80" s="18">
+        <f>$D$65*$D$35*J74/1000000000</f>
+        <v/>
+      </c>
+      <c r="K80" s="18">
+        <f>$D$65*$D$35*K74/1000000000</f>
+        <v/>
+      </c>
+      <c r="L80" s="18">
+        <f>$D$65*$D$35*L74/1000000000</f>
+        <v/>
+      </c>
+      <c r="M80" s="18">
+        <f>$D$65*$D$35*M74/1000000000</f>
+        <v/>
+      </c>
+      <c r="N80" s="18">
+        <f>$D$65*$D$35*N74/1000000000</f>
+        <v/>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="34" t="inlineStr">
@@ -4854,16 +4974,46 @@
           <t>Generation × VOM rate / 1M</t>
         </is>
       </c>
-      <c r="E82" s="18" t="n"/>
-      <c r="F82" s="18" t="n"/>
-      <c r="G82" s="18" t="n"/>
-      <c r="H82" s="18" t="n"/>
-      <c r="I82" s="18" t="n"/>
-      <c r="J82" s="18" t="n"/>
-      <c r="K82" s="18" t="n"/>
-      <c r="L82" s="18" t="n"/>
-      <c r="M82" s="18" t="n"/>
-      <c r="N82" s="18" t="n"/>
+      <c r="E82" s="18">
+        <f>$D$65*$D$46/1000000</f>
+        <v/>
+      </c>
+      <c r="F82" s="18">
+        <f>$D$65*$D$46/1000000</f>
+        <v/>
+      </c>
+      <c r="G82" s="18">
+        <f>$D$65*$D$46/1000000</f>
+        <v/>
+      </c>
+      <c r="H82" s="18">
+        <f>$D$65*$D$46/1000000</f>
+        <v/>
+      </c>
+      <c r="I82" s="18">
+        <f>$D$65*$D$46/1000000</f>
+        <v/>
+      </c>
+      <c r="J82" s="18">
+        <f>$D$65*$D$46/1000000</f>
+        <v/>
+      </c>
+      <c r="K82" s="18">
+        <f>$D$65*$D$46/1000000</f>
+        <v/>
+      </c>
+      <c r="L82" s="18">
+        <f>$D$65*$D$46/1000000</f>
+        <v/>
+      </c>
+      <c r="M82" s="18">
+        <f>$D$65*$D$46/1000000</f>
+        <v/>
+      </c>
+      <c r="N82" s="18">
+        <f>$D$65*$D$46/1000000</f>
+        <v/>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
@@ -4881,16 +5031,46 @@
           <t>Capacity × FOM × esc × 1000 / 1M</t>
         </is>
       </c>
-      <c r="E83" s="18" t="n"/>
-      <c r="F83" s="18" t="n"/>
-      <c r="G83" s="18" t="n"/>
-      <c r="H83" s="18" t="n"/>
-      <c r="I83" s="18" t="n"/>
-      <c r="J83" s="18" t="n"/>
-      <c r="K83" s="18" t="n"/>
-      <c r="L83" s="18" t="n"/>
-      <c r="M83" s="18" t="n"/>
-      <c r="N83" s="18" t="n"/>
+      <c r="E83" s="18">
+        <f>$D$34*$D$47*1000/1000000</f>
+        <v/>
+      </c>
+      <c r="F83" s="18">
+        <f>$D$34*$D$47*1000/1000000</f>
+        <v/>
+      </c>
+      <c r="G83" s="18">
+        <f>$D$34*$D$47*1000/1000000</f>
+        <v/>
+      </c>
+      <c r="H83" s="18">
+        <f>$D$34*$D$47*1000/1000000</f>
+        <v/>
+      </c>
+      <c r="I83" s="18">
+        <f>$D$34*$D$47*1000/1000000</f>
+        <v/>
+      </c>
+      <c r="J83" s="18">
+        <f>$D$34*$D$47*1000/1000000</f>
+        <v/>
+      </c>
+      <c r="K83" s="18">
+        <f>$D$34*$D$47*1000/1000000</f>
+        <v/>
+      </c>
+      <c r="L83" s="18">
+        <f>$D$34*$D$47*1000/1000000</f>
+        <v/>
+      </c>
+      <c r="M83" s="18">
+        <f>$D$34*$D$47*1000/1000000</f>
+        <v/>
+      </c>
+      <c r="N83" s="18">
+        <f>$D$34*$D$47*1000/1000000</f>
+        <v/>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
@@ -4904,16 +5084,46 @@
         </is>
       </c>
       <c r="C84" s="6" t="n"/>
-      <c r="E84" s="18" t="n"/>
-      <c r="F84" s="18" t="n"/>
-      <c r="G84" s="18" t="n"/>
-      <c r="H84" s="18" t="n"/>
-      <c r="I84" s="18" t="n"/>
-      <c r="J84" s="18" t="n"/>
-      <c r="K84" s="18" t="n"/>
-      <c r="L84" s="18" t="n"/>
-      <c r="M84" s="18" t="n"/>
-      <c r="N84" s="18" t="n"/>
+      <c r="E84" s="18">
+        <f>E80+E82+E83</f>
+        <v/>
+      </c>
+      <c r="F84" s="18">
+        <f>F80+F82+F83</f>
+        <v/>
+      </c>
+      <c r="G84" s="18">
+        <f>G80+G82+G83</f>
+        <v/>
+      </c>
+      <c r="H84" s="18">
+        <f>H80+H82+H83</f>
+        <v/>
+      </c>
+      <c r="I84" s="18">
+        <f>I80+I82+I83</f>
+        <v/>
+      </c>
+      <c r="J84" s="18">
+        <f>J80+J82+J83</f>
+        <v/>
+      </c>
+      <c r="K84" s="18">
+        <f>K80+K82+K83</f>
+        <v/>
+      </c>
+      <c r="L84" s="18">
+        <f>L80+L82+L83</f>
+        <v/>
+      </c>
+      <c r="M84" s="18">
+        <f>M80+M82+M83</f>
+        <v/>
+      </c>
+      <c r="N84" s="18">
+        <f>N80+N82+N83</f>
+        <v/>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="n"/>
@@ -4946,16 +5156,46 @@
           <t>Revenue minus OpEx</t>
         </is>
       </c>
-      <c r="E86" s="7" t="n"/>
-      <c r="F86" s="7" t="n"/>
-      <c r="G86" s="7" t="n"/>
-      <c r="H86" s="7" t="n"/>
-      <c r="I86" s="7" t="n"/>
-      <c r="J86" s="7" t="n"/>
-      <c r="K86" s="7" t="n"/>
-      <c r="L86" s="7" t="n"/>
-      <c r="M86" s="7" t="n"/>
-      <c r="N86" s="7" t="n"/>
+      <c r="E86" s="7">
+        <f>E78-E84</f>
+        <v/>
+      </c>
+      <c r="F86" s="7">
+        <f>F78-F84</f>
+        <v/>
+      </c>
+      <c r="G86" s="7">
+        <f>G78-G84</f>
+        <v/>
+      </c>
+      <c r="H86" s="7">
+        <f>H78-H84</f>
+        <v/>
+      </c>
+      <c r="I86" s="7">
+        <f>I78-I84</f>
+        <v/>
+      </c>
+      <c r="J86" s="7">
+        <f>J78-J84</f>
+        <v/>
+      </c>
+      <c r="K86" s="7">
+        <f>K78-K84</f>
+        <v/>
+      </c>
+      <c r="L86" s="7">
+        <f>L78-L84</f>
+        <v/>
+      </c>
+      <c r="M86" s="7">
+        <f>M78-M84</f>
+        <v/>
+      </c>
+      <c r="N86" s="7">
+        <f>N78-N84</f>
+        <v/>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="n"/>
@@ -5067,16 +5307,46 @@
           <t>MAX(0, EBIT) × Tax Rate</t>
         </is>
       </c>
-      <c r="E91" s="18" t="n"/>
-      <c r="F91" s="18" t="n"/>
-      <c r="G91" s="18" t="n"/>
-      <c r="H91" s="18" t="n"/>
-      <c r="I91" s="18" t="n"/>
-      <c r="J91" s="18" t="n"/>
-      <c r="K91" s="18" t="n"/>
-      <c r="L91" s="18" t="n"/>
-      <c r="M91" s="18" t="n"/>
-      <c r="N91" s="18" t="n"/>
+      <c r="E91" s="18">
+        <f>MAX(0,E90)*$D$58</f>
+        <v/>
+      </c>
+      <c r="F91" s="18">
+        <f>MAX(0,F90)*$D$58</f>
+        <v/>
+      </c>
+      <c r="G91" s="18">
+        <f>MAX(0,G90)*$D$58</f>
+        <v/>
+      </c>
+      <c r="H91" s="18">
+        <f>MAX(0,H90)*$D$58</f>
+        <v/>
+      </c>
+      <c r="I91" s="18">
+        <f>MAX(0,I90)*$D$58</f>
+        <v/>
+      </c>
+      <c r="J91" s="18">
+        <f>MAX(0,J90)*$D$58</f>
+        <v/>
+      </c>
+      <c r="K91" s="18">
+        <f>MAX(0,K90)*$D$58</f>
+        <v/>
+      </c>
+      <c r="L91" s="18">
+        <f>MAX(0,L90)*$D$58</f>
+        <v/>
+      </c>
+      <c r="M91" s="18">
+        <f>MAX(0,M90)*$D$58</f>
+        <v/>
+      </c>
+      <c r="N91" s="18">
+        <f>MAX(0,N90)*$D$58</f>
+        <v/>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
@@ -5094,16 +5364,46 @@
           <t>EBITDA - Taxes</t>
         </is>
       </c>
-      <c r="E92" s="7" t="n"/>
-      <c r="F92" s="7" t="n"/>
-      <c r="G92" s="7" t="n"/>
-      <c r="H92" s="7" t="n"/>
-      <c r="I92" s="7" t="n"/>
-      <c r="J92" s="7" t="n"/>
-      <c r="K92" s="7" t="n"/>
-      <c r="L92" s="7" t="n"/>
-      <c r="M92" s="7" t="n"/>
-      <c r="N92" s="7" t="n"/>
+      <c r="E92" s="7">
+        <f>E86-E91</f>
+        <v/>
+      </c>
+      <c r="F92" s="7">
+        <f>F86-F91</f>
+        <v/>
+      </c>
+      <c r="G92" s="7">
+        <f>G86-G91</f>
+        <v/>
+      </c>
+      <c r="H92" s="7">
+        <f>H86-H91</f>
+        <v/>
+      </c>
+      <c r="I92" s="7">
+        <f>I86-I91</f>
+        <v/>
+      </c>
+      <c r="J92" s="7">
+        <f>J86-J91</f>
+        <v/>
+      </c>
+      <c r="K92" s="7">
+        <f>K86-K91</f>
+        <v/>
+      </c>
+      <c r="L92" s="7">
+        <f>L86-L91</f>
+        <v/>
+      </c>
+      <c r="M92" s="7">
+        <f>M86-M91</f>
+        <v/>
+      </c>
+      <c r="N92" s="7">
+        <f>N86-N91</f>
+        <v/>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="n"/>
@@ -5217,16 +5517,46 @@
           <t>Beg Bal × Int Rate</t>
         </is>
       </c>
-      <c r="E97" s="18" t="n"/>
-      <c r="F97" s="18" t="n"/>
-      <c r="G97" s="18" t="n"/>
-      <c r="H97" s="18" t="n"/>
-      <c r="I97" s="18" t="n"/>
-      <c r="J97" s="18" t="n"/>
-      <c r="K97" s="18" t="n"/>
-      <c r="L97" s="18" t="n"/>
-      <c r="M97" s="18" t="n"/>
-      <c r="N97" s="18" t="n"/>
+      <c r="E97" s="18">
+        <f>E96*$D$51</f>
+        <v/>
+      </c>
+      <c r="F97" s="18">
+        <f>F96*$D$51</f>
+        <v/>
+      </c>
+      <c r="G97" s="18">
+        <f>G96*$D$51</f>
+        <v/>
+      </c>
+      <c r="H97" s="18">
+        <f>H96*$D$51</f>
+        <v/>
+      </c>
+      <c r="I97" s="18">
+        <f>I96*$D$51</f>
+        <v/>
+      </c>
+      <c r="J97" s="18">
+        <f>J96*$D$51</f>
+        <v/>
+      </c>
+      <c r="K97" s="18">
+        <f>K96*$D$51</f>
+        <v/>
+      </c>
+      <c r="L97" s="18">
+        <f>L96*$D$51</f>
+        <v/>
+      </c>
+      <c r="M97" s="18">
+        <f>M96*$D$51</f>
+        <v/>
+      </c>
+      <c r="N97" s="18">
+        <f>N96*$D$51</f>
+        <v/>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
@@ -5244,16 +5574,46 @@
           <t>MIN(Sched, Beg Bal)</t>
         </is>
       </c>
-      <c r="E98" s="18" t="n"/>
-      <c r="F98" s="18" t="n"/>
-      <c r="G98" s="18" t="n"/>
-      <c r="H98" s="18" t="n"/>
-      <c r="I98" s="18" t="n"/>
-      <c r="J98" s="18" t="n"/>
-      <c r="K98" s="18" t="n"/>
-      <c r="L98" s="18" t="n"/>
-      <c r="M98" s="18" t="n"/>
-      <c r="N98" s="18" t="n"/>
+      <c r="E98" s="18">
+        <f>MIN($D$68,E96)</f>
+        <v/>
+      </c>
+      <c r="F98" s="18">
+        <f>MIN($D$68,F96)</f>
+        <v/>
+      </c>
+      <c r="G98" s="18">
+        <f>MIN($D$68,G96)</f>
+        <v/>
+      </c>
+      <c r="H98" s="18">
+        <f>MIN($D$68,H96)</f>
+        <v/>
+      </c>
+      <c r="I98" s="18">
+        <f>MIN($D$68,I96)</f>
+        <v/>
+      </c>
+      <c r="J98" s="18">
+        <f>MIN($D$68,J96)</f>
+        <v/>
+      </c>
+      <c r="K98" s="18">
+        <f>MIN($D$68,K96)</f>
+        <v/>
+      </c>
+      <c r="L98" s="18">
+        <f>MIN($D$68,L96)</f>
+        <v/>
+      </c>
+      <c r="M98" s="18">
+        <f>MIN($D$68,M96)</f>
+        <v/>
+      </c>
+      <c r="N98" s="18">
+        <f>MIN($D$68,N96)</f>
+        <v/>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
@@ -5271,16 +5631,46 @@
           <t>Interest + Sched Prin</t>
         </is>
       </c>
-      <c r="E99" s="18" t="n"/>
-      <c r="F99" s="18" t="n"/>
-      <c r="G99" s="18" t="n"/>
-      <c r="H99" s="18" t="n"/>
-      <c r="I99" s="18" t="n"/>
-      <c r="J99" s="18" t="n"/>
-      <c r="K99" s="18" t="n"/>
-      <c r="L99" s="18" t="n"/>
-      <c r="M99" s="18" t="n"/>
-      <c r="N99" s="18" t="n"/>
+      <c r="E99" s="18">
+        <f>E97+E98</f>
+        <v/>
+      </c>
+      <c r="F99" s="18">
+        <f>F97+F98</f>
+        <v/>
+      </c>
+      <c r="G99" s="18">
+        <f>G97+G98</f>
+        <v/>
+      </c>
+      <c r="H99" s="18">
+        <f>H97+H98</f>
+        <v/>
+      </c>
+      <c r="I99" s="18">
+        <f>I97+I98</f>
+        <v/>
+      </c>
+      <c r="J99" s="18">
+        <f>J97+J98</f>
+        <v/>
+      </c>
+      <c r="K99" s="18">
+        <f>K97+K98</f>
+        <v/>
+      </c>
+      <c r="L99" s="18">
+        <f>L97+L98</f>
+        <v/>
+      </c>
+      <c r="M99" s="18">
+        <f>M97+M98</f>
+        <v/>
+      </c>
+      <c r="N99" s="18">
+        <f>N97+N98</f>
+        <v/>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
@@ -5355,16 +5745,46 @@
           <t>MIN(Excess×Sweep%, Beg-Sched)</t>
         </is>
       </c>
-      <c r="E101" s="21" t="n"/>
-      <c r="F101" s="21" t="n"/>
-      <c r="G101" s="21" t="n"/>
-      <c r="H101" s="21" t="n"/>
-      <c r="I101" s="21" t="n"/>
-      <c r="J101" s="21" t="n"/>
-      <c r="K101" s="21" t="n"/>
-      <c r="L101" s="21" t="n"/>
-      <c r="M101" s="21" t="n"/>
-      <c r="N101" s="21" t="n"/>
+      <c r="E101" s="21">
+        <f>MIN(E100*$D$54,MAX(0,E96-E98))</f>
+        <v/>
+      </c>
+      <c r="F101" s="21">
+        <f>MIN(F100*$D$54,MAX(0,F96-F98))</f>
+        <v/>
+      </c>
+      <c r="G101" s="21">
+        <f>MIN(G100*$D$54,MAX(0,G96-G98))</f>
+        <v/>
+      </c>
+      <c r="H101" s="21">
+        <f>MIN(H100*$D$54,MAX(0,H96-H98))</f>
+        <v/>
+      </c>
+      <c r="I101" s="21">
+        <f>MIN(I100*$D$54,MAX(0,I96-I98))</f>
+        <v/>
+      </c>
+      <c r="J101" s="21">
+        <f>MIN(J100*$D$54,MAX(0,J96-J98))</f>
+        <v/>
+      </c>
+      <c r="K101" s="21">
+        <f>MIN(K100*$D$54,MAX(0,K96-K98))</f>
+        <v/>
+      </c>
+      <c r="L101" s="21">
+        <f>MIN(L100*$D$54,MAX(0,L96-L98))</f>
+        <v/>
+      </c>
+      <c r="M101" s="21">
+        <f>MIN(M100*$D$54,MAX(0,M96-M98))</f>
+        <v/>
+      </c>
+      <c r="N101" s="21">
+        <f>MIN(N100*$D$54,MAX(0,N96-N98))</f>
+        <v/>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
@@ -5382,16 +5802,46 @@
           <t>Scheduled + Sweep</t>
         </is>
       </c>
-      <c r="E102" s="18" t="n"/>
-      <c r="F102" s="18" t="n"/>
-      <c r="G102" s="18" t="n"/>
-      <c r="H102" s="18" t="n"/>
-      <c r="I102" s="18" t="n"/>
-      <c r="J102" s="18" t="n"/>
-      <c r="K102" s="18" t="n"/>
-      <c r="L102" s="18" t="n"/>
-      <c r="M102" s="18" t="n"/>
-      <c r="N102" s="18" t="n"/>
+      <c r="E102" s="18">
+        <f>E98+E101</f>
+        <v/>
+      </c>
+      <c r="F102" s="18">
+        <f>F98+F101</f>
+        <v/>
+      </c>
+      <c r="G102" s="18">
+        <f>G98+G101</f>
+        <v/>
+      </c>
+      <c r="H102" s="18">
+        <f>H98+H101</f>
+        <v/>
+      </c>
+      <c r="I102" s="18">
+        <f>I98+I101</f>
+        <v/>
+      </c>
+      <c r="J102" s="18">
+        <f>J98+J101</f>
+        <v/>
+      </c>
+      <c r="K102" s="18">
+        <f>K98+K101</f>
+        <v/>
+      </c>
+      <c r="L102" s="18">
+        <f>L98+L101</f>
+        <v/>
+      </c>
+      <c r="M102" s="18">
+        <f>M98+M101</f>
+        <v/>
+      </c>
+      <c r="N102" s="18">
+        <f>N98+N101</f>
+        <v/>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
@@ -5413,16 +5863,46 @@
         <f>$D$66</f>
         <v/>
       </c>
-      <c r="E103" s="18" t="n"/>
-      <c r="F103" s="18" t="n"/>
-      <c r="G103" s="18" t="n"/>
-      <c r="H103" s="18" t="n"/>
-      <c r="I103" s="18" t="n"/>
-      <c r="J103" s="18" t="n"/>
-      <c r="K103" s="18" t="n"/>
-      <c r="L103" s="18" t="n"/>
-      <c r="M103" s="18" t="n"/>
-      <c r="N103" s="18" t="n"/>
+      <c r="E103" s="18">
+        <f>MAX(0,E96-E102)</f>
+        <v/>
+      </c>
+      <c r="F103" s="18">
+        <f>MAX(0,F96-F102)</f>
+        <v/>
+      </c>
+      <c r="G103" s="18">
+        <f>MAX(0,G96-G102)</f>
+        <v/>
+      </c>
+      <c r="H103" s="18">
+        <f>MAX(0,H96-H102)</f>
+        <v/>
+      </c>
+      <c r="I103" s="18">
+        <f>MAX(0,I96-I102)</f>
+        <v/>
+      </c>
+      <c r="J103" s="18">
+        <f>MAX(0,J96-J102)</f>
+        <v/>
+      </c>
+      <c r="K103" s="18">
+        <f>MAX(0,K96-K102)</f>
+        <v/>
+      </c>
+      <c r="L103" s="18">
+        <f>MAX(0,L96-L102)</f>
+        <v/>
+      </c>
+      <c r="M103" s="18">
+        <f>MAX(0,M96-M102)</f>
+        <v/>
+      </c>
+      <c r="N103" s="18">
+        <f>MAX(0,N96-N102)</f>
+        <v/>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
@@ -5440,16 +5920,46 @@
           <t>CFADS / Debt Service</t>
         </is>
       </c>
-      <c r="E104" s="30" t="n"/>
-      <c r="F104" s="30" t="n"/>
-      <c r="G104" s="30" t="n"/>
-      <c r="H104" s="30" t="n"/>
-      <c r="I104" s="30" t="n"/>
-      <c r="J104" s="30" t="n"/>
-      <c r="K104" s="30" t="n"/>
-      <c r="L104" s="30" t="n"/>
-      <c r="M104" s="30" t="n"/>
-      <c r="N104" s="30" t="n"/>
+      <c r="E104" s="30">
+        <f>IF(E99&gt;0,E92/E99,0)</f>
+        <v/>
+      </c>
+      <c r="F104" s="30">
+        <f>IF(F99&gt;0,F92/F99,0)</f>
+        <v/>
+      </c>
+      <c r="G104" s="30">
+        <f>IF(G99&gt;0,G92/G99,0)</f>
+        <v/>
+      </c>
+      <c r="H104" s="30">
+        <f>IF(H99&gt;0,H92/H99,0)</f>
+        <v/>
+      </c>
+      <c r="I104" s="30">
+        <f>IF(I99&gt;0,I92/I99,0)</f>
+        <v/>
+      </c>
+      <c r="J104" s="30">
+        <f>IF(J99&gt;0,J92/J99,0)</f>
+        <v/>
+      </c>
+      <c r="K104" s="30">
+        <f>IF(K99&gt;0,K92/K99,0)</f>
+        <v/>
+      </c>
+      <c r="L104" s="30">
+        <f>IF(L99&gt;0,L92/L99,0)</f>
+        <v/>
+      </c>
+      <c r="M104" s="30">
+        <f>IF(M99&gt;0,M92/M99,0)</f>
+        <v/>
+      </c>
+      <c r="N104" s="30">
+        <f>IF(N99&gt;0,N92/N99,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
@@ -6363,7 +6873,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="5" t="n"/>
+      <c r="A139" s="5" t="inlineStr">
+        <is>
+          <t>Exit EBITDA</t>
+        </is>
+      </c>
       <c r="B139" s="6" t="n"/>
       <c r="C139" s="6" t="n"/>
       <c r="D139">
@@ -6375,7 +6889,7 @@
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
         <is>
-          <t>EQUITY RETURNS</t>
+          <t>Exit EV</t>
         </is>
       </c>
       <c r="B140" s="4" t="n"/>
@@ -6408,48 +6922,45 @@
       </c>
       <c r="C141" s="6" t="n"/>
       <c r="D141" s="18">
-        <f>K103</f>
+        <f>-D129</f>
         <v/>
       </c>
       <c r="E141" s="18">
-        <f>E105</f>
+        <f>E117</f>
         <v/>
       </c>
       <c r="F141" s="18">
-        <f>F105</f>
+        <f>F117</f>
         <v/>
       </c>
       <c r="G141" s="18">
-        <f>G105</f>
+        <f>G117</f>
         <v/>
       </c>
       <c r="H141" s="18">
-        <f>H105</f>
+        <f>H117</f>
         <v/>
       </c>
       <c r="I141" s="18">
-        <f>I105</f>
+        <f>I117</f>
         <v/>
       </c>
       <c r="J141" s="18">
-        <f>J105</f>
+        <f>J117</f>
         <v/>
       </c>
       <c r="K141" s="18">
-        <f>K105+K126</f>
-        <v/>
-      </c>
-      <c r="L141" s="18">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="M141" s="18">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="N141" s="18">
-        <f>0</f>
-        <v/>
+        <f>K117+D143</f>
+        <v/>
+      </c>
+      <c r="L141" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M141" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N141" s="18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="142">
@@ -6469,7 +6980,7 @@
         </is>
       </c>
       <c r="D142" s="31">
-        <f>K111</f>
+        <f>IRR(D141:N141)</f>
         <v/>
       </c>
       <c r="E142" s="18" t="n"/>
@@ -6486,7 +6997,7 @@
     <row r="143">
       <c r="A143" s="5" t="inlineStr">
         <is>
-          <t>MOIC</t>
+          <t>Exit Equity Proceeds</t>
         </is>
       </c>
       <c r="B143" s="6" t="inlineStr">
@@ -6500,24 +7011,35 @@
         </is>
       </c>
       <c r="D143" s="30">
-        <f>D140-D141+D142</f>
+        <f>D140-D144+D145</f>
         <v/>
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="5" t="n"/>
+      <c r="A144" s="5" t="inlineStr">
+        <is>
+          <t>Exit Debt Balance</t>
+        </is>
+      </c>
       <c r="B144" s="6" t="n"/>
       <c r="C144" s="6" t="n"/>
-      <c r="D144" s="30" t="n"/>
+      <c r="D144" s="30">
+        <f>K103</f>
+        <v/>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="23" t="inlineStr">
         <is>
-          <t>Unlevered Returns (for reference)</t>
+          <t>Exit DSRA Release</t>
         </is>
       </c>
       <c r="B145" s="6" t="n"/>
       <c r="C145" s="6" t="n"/>
+      <c r="D145">
+        <f>K111</f>
+        <v/>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="5" t="inlineStr">
@@ -6576,7 +7098,7 @@
     <row r="147">
       <c r="A147" s="5" t="inlineStr">
         <is>
-          <t>Unlevered IRR</t>
+          <t>MOIC</t>
         </is>
       </c>
       <c r="B147" s="6" t="inlineStr">
@@ -6589,7 +7111,10 @@
           <t>IRR of Equity CFs</t>
         </is>
       </c>
-      <c r="D147" s="31" t="n"/>
+      <c r="D147" s="30">
+        <f>(SUM(E141:K141))/-D141</f>
+        <v/>
+      </c>
       <c r="E147" s="18" t="n"/>
       <c r="F147" s="18" t="n"/>
       <c r="G147" s="18" t="n"/>
@@ -6605,7 +7130,10 @@
       <c r="A148" s="5" t="n"/>
       <c r="B148" s="6" t="n"/>
       <c r="C148" s="6" t="n"/>
-      <c r="D148" s="60" t="n"/>
+      <c r="D148" s="60">
+        <f>(SUM(E146:K146))/-D146</f>
+        <v/>
+      </c>
     </row>
     <row r="149"/>
     <row r="150"/>
@@ -6618,7 +7146,6 @@
     <row r="157"/>
     <row r="158"/>
     <row r="159"/>
-    <row r="160"/>
   </sheetData>
   <dataValidations count="3">
     <dataValidation sqref="D7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">

--- a/deliverables/deliverables-20260120-0030/Drill_1_CCGT.xlsx
+++ b/deliverables/deliverables-20260120-0030/Drill_1_CCGT.xlsx
@@ -27,7 +27,7 @@
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -105,6 +105,10 @@
       <color rgb="00666666"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FF0000"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -162,7 +166,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -244,6 +248,13 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3184,7 +3195,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N159"/>
+  <dimension ref="A1:N148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -3266,9 +3277,9 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>═══ AUDIT STRIP ═══</t>
+      <c r="A2" s="61" t="inlineStr">
+        <is>
+          <t>═══ DRILL MODE: Rebuild formulas in highlighted cells ═══</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -3288,7 +3299,7 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Entry EV</t>
+          <t>═══ AUDIT STRIP ═══</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
@@ -3632,7 +3643,6 @@
       <c r="C25" s="6" t="n"/>
       <c r="D25" s="10" t="n"/>
     </row>
-    <row r="26"/>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
@@ -4309,7 +4319,6 @@
       <c r="C61" s="6" t="n"/>
       <c r="D61" s="14" t="n"/>
     </row>
-    <row r="62"/>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
@@ -4451,7 +4460,6 @@
       <c r="C69" s="6" t="n"/>
       <c r="D69" s="18" t="n"/>
     </row>
-    <row r="70"/>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
@@ -4675,46 +4683,16 @@
           <t>Generation × Power Price / 1M</t>
         </is>
       </c>
-      <c r="E76" s="18">
-        <f>$D$65*E72/1000000</f>
-        <v/>
-      </c>
-      <c r="F76" s="18">
-        <f>$D$65*F72/1000000</f>
-        <v/>
-      </c>
-      <c r="G76" s="18">
-        <f>$D$65*G72/1000000</f>
-        <v/>
-      </c>
-      <c r="H76" s="18">
-        <f>$D$65*H72/1000000</f>
-        <v/>
-      </c>
-      <c r="I76" s="18">
-        <f>$D$65*I72/1000000</f>
-        <v/>
-      </c>
-      <c r="J76" s="18">
-        <f>$D$65*J72/1000000</f>
-        <v/>
-      </c>
-      <c r="K76" s="18">
-        <f>$D$65*K72/1000000</f>
-        <v/>
-      </c>
-      <c r="L76" s="18">
-        <f>$D$65*L72/1000000</f>
-        <v/>
-      </c>
-      <c r="M76" s="18">
-        <f>$D$65*M72/1000000</f>
-        <v/>
-      </c>
-      <c r="N76" s="18">
-        <f>$D$65*N72/1000000</f>
-        <v/>
-      </c>
+      <c r="E76" s="62" t="n"/>
+      <c r="F76" s="62" t="n"/>
+      <c r="G76" s="62" t="n"/>
+      <c r="H76" s="62" t="n"/>
+      <c r="I76" s="62" t="n"/>
+      <c r="J76" s="62" t="n"/>
+      <c r="K76" s="62" t="n"/>
+      <c r="L76" s="62" t="n"/>
+      <c r="M76" s="62" t="n"/>
+      <c r="N76" s="62" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
@@ -4732,46 +4710,16 @@
           <t>UCAP × Cap Price × 1000 / 1M</t>
         </is>
       </c>
-      <c r="E77" s="18">
-        <f>$D$34*E73*1000/1000000</f>
-        <v/>
-      </c>
-      <c r="F77" s="18">
-        <f>$D$34*F73*1000/1000000</f>
-        <v/>
-      </c>
-      <c r="G77" s="18">
-        <f>$D$34*G73*1000/1000000</f>
-        <v/>
-      </c>
-      <c r="H77" s="18">
-        <f>$D$34*H73*1000/1000000</f>
-        <v/>
-      </c>
-      <c r="I77" s="18">
-        <f>$D$34*I73*1000/1000000</f>
-        <v/>
-      </c>
-      <c r="J77" s="18">
-        <f>$D$34*J73*1000/1000000</f>
-        <v/>
-      </c>
-      <c r="K77" s="18">
-        <f>$D$34*K73*1000/1000000</f>
-        <v/>
-      </c>
-      <c r="L77" s="18">
-        <f>$D$34*L73*1000/1000000</f>
-        <v/>
-      </c>
-      <c r="M77" s="18">
-        <f>$D$34*M73*1000/1000000</f>
-        <v/>
-      </c>
-      <c r="N77" s="18">
-        <f>$D$34*N73*1000/1000000</f>
-        <v/>
-      </c>
+      <c r="E77" s="62" t="n"/>
+      <c r="F77" s="62" t="n"/>
+      <c r="G77" s="62" t="n"/>
+      <c r="H77" s="62" t="n"/>
+      <c r="I77" s="62" t="n"/>
+      <c r="J77" s="62" t="n"/>
+      <c r="K77" s="62" t="n"/>
+      <c r="L77" s="62" t="n"/>
+      <c r="M77" s="62" t="n"/>
+      <c r="N77" s="62" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
@@ -4785,46 +4733,16 @@
         </is>
       </c>
       <c r="C78" s="6" t="n"/>
-      <c r="E78" s="20">
-        <f>E76+E77</f>
-        <v/>
-      </c>
-      <c r="F78" s="20">
-        <f>F76+F77</f>
-        <v/>
-      </c>
-      <c r="G78" s="20">
-        <f>G76+G77</f>
-        <v/>
-      </c>
-      <c r="H78" s="20">
-        <f>H76+H77</f>
-        <v/>
-      </c>
-      <c r="I78" s="20">
-        <f>I76+I77</f>
-        <v/>
-      </c>
-      <c r="J78" s="20">
-        <f>J76+J77</f>
-        <v/>
-      </c>
-      <c r="K78" s="20">
-        <f>K76+K77</f>
-        <v/>
-      </c>
-      <c r="L78" s="20">
-        <f>L76+L77</f>
-        <v/>
-      </c>
-      <c r="M78" s="20">
-        <f>M76+M77</f>
-        <v/>
-      </c>
-      <c r="N78" s="20">
-        <f>N76+N77</f>
-        <v/>
-      </c>
+      <c r="E78" s="63" t="n"/>
+      <c r="F78" s="63" t="n"/>
+      <c r="G78" s="63" t="n"/>
+      <c r="H78" s="63" t="n"/>
+      <c r="I78" s="63" t="n"/>
+      <c r="J78" s="63" t="n"/>
+      <c r="K78" s="63" t="n"/>
+      <c r="L78" s="63" t="n"/>
+      <c r="M78" s="63" t="n"/>
+      <c r="N78" s="63" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="5" t="n"/>
@@ -4857,46 +4775,16 @@
           <t>Gen × HR × Gas / 1B</t>
         </is>
       </c>
-      <c r="E80" s="18">
-        <f>$D$65*$D$35*E74/1000000000</f>
-        <v/>
-      </c>
-      <c r="F80" s="18">
-        <f>$D$65*$D$35*F74/1000000000</f>
-        <v/>
-      </c>
-      <c r="G80" s="18">
-        <f>$D$65*$D$35*G74/1000000000</f>
-        <v/>
-      </c>
-      <c r="H80" s="18">
-        <f>$D$65*$D$35*H74/1000000000</f>
-        <v/>
-      </c>
-      <c r="I80" s="18">
-        <f>$D$65*$D$35*I74/1000000000</f>
-        <v/>
-      </c>
-      <c r="J80" s="18">
-        <f>$D$65*$D$35*J74/1000000000</f>
-        <v/>
-      </c>
-      <c r="K80" s="18">
-        <f>$D$65*$D$35*K74/1000000000</f>
-        <v/>
-      </c>
-      <c r="L80" s="18">
-        <f>$D$65*$D$35*L74/1000000000</f>
-        <v/>
-      </c>
-      <c r="M80" s="18">
-        <f>$D$65*$D$35*M74/1000000000</f>
-        <v/>
-      </c>
-      <c r="N80" s="18">
-        <f>$D$65*$D$35*N74/1000000000</f>
-        <v/>
-      </c>
+      <c r="E80" s="62" t="n"/>
+      <c r="F80" s="62" t="n"/>
+      <c r="G80" s="62" t="n"/>
+      <c r="H80" s="62" t="n"/>
+      <c r="I80" s="62" t="n"/>
+      <c r="J80" s="62" t="n"/>
+      <c r="K80" s="62" t="n"/>
+      <c r="L80" s="62" t="n"/>
+      <c r="M80" s="62" t="n"/>
+      <c r="N80" s="62" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="34" t="inlineStr">
@@ -4974,46 +4862,16 @@
           <t>Generation × VOM rate / 1M</t>
         </is>
       </c>
-      <c r="E82" s="18">
-        <f>$D$65*$D$46/1000000</f>
-        <v/>
-      </c>
-      <c r="F82" s="18">
-        <f>$D$65*$D$46/1000000</f>
-        <v/>
-      </c>
-      <c r="G82" s="18">
-        <f>$D$65*$D$46/1000000</f>
-        <v/>
-      </c>
-      <c r="H82" s="18">
-        <f>$D$65*$D$46/1000000</f>
-        <v/>
-      </c>
-      <c r="I82" s="18">
-        <f>$D$65*$D$46/1000000</f>
-        <v/>
-      </c>
-      <c r="J82" s="18">
-        <f>$D$65*$D$46/1000000</f>
-        <v/>
-      </c>
-      <c r="K82" s="18">
-        <f>$D$65*$D$46/1000000</f>
-        <v/>
-      </c>
-      <c r="L82" s="18">
-        <f>$D$65*$D$46/1000000</f>
-        <v/>
-      </c>
-      <c r="M82" s="18">
-        <f>$D$65*$D$46/1000000</f>
-        <v/>
-      </c>
-      <c r="N82" s="18">
-        <f>$D$65*$D$46/1000000</f>
-        <v/>
-      </c>
+      <c r="E82" s="62" t="n"/>
+      <c r="F82" s="62" t="n"/>
+      <c r="G82" s="62" t="n"/>
+      <c r="H82" s="62" t="n"/>
+      <c r="I82" s="62" t="n"/>
+      <c r="J82" s="62" t="n"/>
+      <c r="K82" s="62" t="n"/>
+      <c r="L82" s="62" t="n"/>
+      <c r="M82" s="62" t="n"/>
+      <c r="N82" s="62" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
@@ -5031,46 +4889,16 @@
           <t>Capacity × FOM × esc × 1000 / 1M</t>
         </is>
       </c>
-      <c r="E83" s="18">
-        <f>$D$34*$D$47*1000/1000000</f>
-        <v/>
-      </c>
-      <c r="F83" s="18">
-        <f>$D$34*$D$47*1000/1000000</f>
-        <v/>
-      </c>
-      <c r="G83" s="18">
-        <f>$D$34*$D$47*1000/1000000</f>
-        <v/>
-      </c>
-      <c r="H83" s="18">
-        <f>$D$34*$D$47*1000/1000000</f>
-        <v/>
-      </c>
-      <c r="I83" s="18">
-        <f>$D$34*$D$47*1000/1000000</f>
-        <v/>
-      </c>
-      <c r="J83" s="18">
-        <f>$D$34*$D$47*1000/1000000</f>
-        <v/>
-      </c>
-      <c r="K83" s="18">
-        <f>$D$34*$D$47*1000/1000000</f>
-        <v/>
-      </c>
-      <c r="L83" s="18">
-        <f>$D$34*$D$47*1000/1000000</f>
-        <v/>
-      </c>
-      <c r="M83" s="18">
-        <f>$D$34*$D$47*1000/1000000</f>
-        <v/>
-      </c>
-      <c r="N83" s="18">
-        <f>$D$34*$D$47*1000/1000000</f>
-        <v/>
-      </c>
+      <c r="E83" s="62" t="n"/>
+      <c r="F83" s="62" t="n"/>
+      <c r="G83" s="62" t="n"/>
+      <c r="H83" s="62" t="n"/>
+      <c r="I83" s="62" t="n"/>
+      <c r="J83" s="62" t="n"/>
+      <c r="K83" s="62" t="n"/>
+      <c r="L83" s="62" t="n"/>
+      <c r="M83" s="62" t="n"/>
+      <c r="N83" s="62" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
@@ -5084,46 +4912,16 @@
         </is>
       </c>
       <c r="C84" s="6" t="n"/>
-      <c r="E84" s="18">
-        <f>E80+E82+E83</f>
-        <v/>
-      </c>
-      <c r="F84" s="18">
-        <f>F80+F82+F83</f>
-        <v/>
-      </c>
-      <c r="G84" s="18">
-        <f>G80+G82+G83</f>
-        <v/>
-      </c>
-      <c r="H84" s="18">
-        <f>H80+H82+H83</f>
-        <v/>
-      </c>
-      <c r="I84" s="18">
-        <f>I80+I82+I83</f>
-        <v/>
-      </c>
-      <c r="J84" s="18">
-        <f>J80+J82+J83</f>
-        <v/>
-      </c>
-      <c r="K84" s="18">
-        <f>K80+K82+K83</f>
-        <v/>
-      </c>
-      <c r="L84" s="18">
-        <f>L80+L82+L83</f>
-        <v/>
-      </c>
-      <c r="M84" s="18">
-        <f>M80+M82+M83</f>
-        <v/>
-      </c>
-      <c r="N84" s="18">
-        <f>N80+N82+N83</f>
-        <v/>
-      </c>
+      <c r="E84" s="62" t="n"/>
+      <c r="F84" s="62" t="n"/>
+      <c r="G84" s="62" t="n"/>
+      <c r="H84" s="62" t="n"/>
+      <c r="I84" s="62" t="n"/>
+      <c r="J84" s="62" t="n"/>
+      <c r="K84" s="62" t="n"/>
+      <c r="L84" s="62" t="n"/>
+      <c r="M84" s="62" t="n"/>
+      <c r="N84" s="62" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="5" t="n"/>
@@ -5156,46 +4954,16 @@
           <t>Revenue minus OpEx</t>
         </is>
       </c>
-      <c r="E86" s="7">
-        <f>E78-E84</f>
-        <v/>
-      </c>
-      <c r="F86" s="7">
-        <f>F78-F84</f>
-        <v/>
-      </c>
-      <c r="G86" s="7">
-        <f>G78-G84</f>
-        <v/>
-      </c>
-      <c r="H86" s="7">
-        <f>H78-H84</f>
-        <v/>
-      </c>
-      <c r="I86" s="7">
-        <f>I78-I84</f>
-        <v/>
-      </c>
-      <c r="J86" s="7">
-        <f>J78-J84</f>
-        <v/>
-      </c>
-      <c r="K86" s="7">
-        <f>K78-K84</f>
-        <v/>
-      </c>
-      <c r="L86" s="7">
-        <f>L78-L84</f>
-        <v/>
-      </c>
-      <c r="M86" s="7">
-        <f>M78-M84</f>
-        <v/>
-      </c>
-      <c r="N86" s="7">
-        <f>N78-N84</f>
-        <v/>
-      </c>
+      <c r="E86" s="63" t="n"/>
+      <c r="F86" s="63" t="n"/>
+      <c r="G86" s="63" t="n"/>
+      <c r="H86" s="63" t="n"/>
+      <c r="I86" s="63" t="n"/>
+      <c r="J86" s="63" t="n"/>
+      <c r="K86" s="63" t="n"/>
+      <c r="L86" s="63" t="n"/>
+      <c r="M86" s="63" t="n"/>
+      <c r="N86" s="63" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="5" t="n"/>
@@ -5212,7 +4980,6 @@
       <c r="M87" s="7" t="n"/>
       <c r="N87" s="7" t="n"/>
     </row>
-    <row r="88"/>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
@@ -5307,46 +5074,16 @@
           <t>MAX(0, EBIT) × Tax Rate</t>
         </is>
       </c>
-      <c r="E91" s="18">
-        <f>MAX(0,E90)*$D$58</f>
-        <v/>
-      </c>
-      <c r="F91" s="18">
-        <f>MAX(0,F90)*$D$58</f>
-        <v/>
-      </c>
-      <c r="G91" s="18">
-        <f>MAX(0,G90)*$D$58</f>
-        <v/>
-      </c>
-      <c r="H91" s="18">
-        <f>MAX(0,H90)*$D$58</f>
-        <v/>
-      </c>
-      <c r="I91" s="18">
-        <f>MAX(0,I90)*$D$58</f>
-        <v/>
-      </c>
-      <c r="J91" s="18">
-        <f>MAX(0,J90)*$D$58</f>
-        <v/>
-      </c>
-      <c r="K91" s="18">
-        <f>MAX(0,K90)*$D$58</f>
-        <v/>
-      </c>
-      <c r="L91" s="18">
-        <f>MAX(0,L90)*$D$58</f>
-        <v/>
-      </c>
-      <c r="M91" s="18">
-        <f>MAX(0,M90)*$D$58</f>
-        <v/>
-      </c>
-      <c r="N91" s="18">
-        <f>MAX(0,N90)*$D$58</f>
-        <v/>
-      </c>
+      <c r="E91" s="62" t="n"/>
+      <c r="F91" s="62" t="n"/>
+      <c r="G91" s="62" t="n"/>
+      <c r="H91" s="62" t="n"/>
+      <c r="I91" s="62" t="n"/>
+      <c r="J91" s="62" t="n"/>
+      <c r="K91" s="62" t="n"/>
+      <c r="L91" s="62" t="n"/>
+      <c r="M91" s="62" t="n"/>
+      <c r="N91" s="62" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
@@ -5364,46 +5101,16 @@
           <t>EBITDA - Taxes</t>
         </is>
       </c>
-      <c r="E92" s="7">
-        <f>E86-E91</f>
-        <v/>
-      </c>
-      <c r="F92" s="7">
-        <f>F86-F91</f>
-        <v/>
-      </c>
-      <c r="G92" s="7">
-        <f>G86-G91</f>
-        <v/>
-      </c>
-      <c r="H92" s="7">
-        <f>H86-H91</f>
-        <v/>
-      </c>
-      <c r="I92" s="7">
-        <f>I86-I91</f>
-        <v/>
-      </c>
-      <c r="J92" s="7">
-        <f>J86-J91</f>
-        <v/>
-      </c>
-      <c r="K92" s="7">
-        <f>K86-K91</f>
-        <v/>
-      </c>
-      <c r="L92" s="7">
-        <f>L86-L91</f>
-        <v/>
-      </c>
-      <c r="M92" s="7">
-        <f>M86-M91</f>
-        <v/>
-      </c>
-      <c r="N92" s="7">
-        <f>N86-N91</f>
-        <v/>
-      </c>
+      <c r="E92" s="63" t="n"/>
+      <c r="F92" s="63" t="n"/>
+      <c r="G92" s="63" t="n"/>
+      <c r="H92" s="63" t="n"/>
+      <c r="I92" s="63" t="n"/>
+      <c r="J92" s="63" t="n"/>
+      <c r="K92" s="63" t="n"/>
+      <c r="L92" s="63" t="n"/>
+      <c r="M92" s="63" t="n"/>
+      <c r="N92" s="63" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="5" t="n"/>
@@ -5420,7 +5127,6 @@
       <c r="M93" s="7" t="n"/>
       <c r="N93" s="7" t="n"/>
     </row>
-    <row r="94"/>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
@@ -5517,46 +5223,16 @@
           <t>Beg Bal × Int Rate</t>
         </is>
       </c>
-      <c r="E97" s="18">
-        <f>E96*$D$51</f>
-        <v/>
-      </c>
-      <c r="F97" s="18">
-        <f>F96*$D$51</f>
-        <v/>
-      </c>
-      <c r="G97" s="18">
-        <f>G96*$D$51</f>
-        <v/>
-      </c>
-      <c r="H97" s="18">
-        <f>H96*$D$51</f>
-        <v/>
-      </c>
-      <c r="I97" s="18">
-        <f>I96*$D$51</f>
-        <v/>
-      </c>
-      <c r="J97" s="18">
-        <f>J96*$D$51</f>
-        <v/>
-      </c>
-      <c r="K97" s="18">
-        <f>K96*$D$51</f>
-        <v/>
-      </c>
-      <c r="L97" s="18">
-        <f>L96*$D$51</f>
-        <v/>
-      </c>
-      <c r="M97" s="18">
-        <f>M96*$D$51</f>
-        <v/>
-      </c>
-      <c r="N97" s="18">
-        <f>N96*$D$51</f>
-        <v/>
-      </c>
+      <c r="E97" s="62" t="n"/>
+      <c r="F97" s="62" t="n"/>
+      <c r="G97" s="62" t="n"/>
+      <c r="H97" s="62" t="n"/>
+      <c r="I97" s="62" t="n"/>
+      <c r="J97" s="62" t="n"/>
+      <c r="K97" s="62" t="n"/>
+      <c r="L97" s="62" t="n"/>
+      <c r="M97" s="62" t="n"/>
+      <c r="N97" s="62" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
@@ -5574,46 +5250,16 @@
           <t>MIN(Sched, Beg Bal)</t>
         </is>
       </c>
-      <c r="E98" s="18">
-        <f>MIN($D$68,E96)</f>
-        <v/>
-      </c>
-      <c r="F98" s="18">
-        <f>MIN($D$68,F96)</f>
-        <v/>
-      </c>
-      <c r="G98" s="18">
-        <f>MIN($D$68,G96)</f>
-        <v/>
-      </c>
-      <c r="H98" s="18">
-        <f>MIN($D$68,H96)</f>
-        <v/>
-      </c>
-      <c r="I98" s="18">
-        <f>MIN($D$68,I96)</f>
-        <v/>
-      </c>
-      <c r="J98" s="18">
-        <f>MIN($D$68,J96)</f>
-        <v/>
-      </c>
-      <c r="K98" s="18">
-        <f>MIN($D$68,K96)</f>
-        <v/>
-      </c>
-      <c r="L98" s="18">
-        <f>MIN($D$68,L96)</f>
-        <v/>
-      </c>
-      <c r="M98" s="18">
-        <f>MIN($D$68,M96)</f>
-        <v/>
-      </c>
-      <c r="N98" s="18">
-        <f>MIN($D$68,N96)</f>
-        <v/>
-      </c>
+      <c r="E98" s="62" t="n"/>
+      <c r="F98" s="62" t="n"/>
+      <c r="G98" s="62" t="n"/>
+      <c r="H98" s="62" t="n"/>
+      <c r="I98" s="62" t="n"/>
+      <c r="J98" s="62" t="n"/>
+      <c r="K98" s="62" t="n"/>
+      <c r="L98" s="62" t="n"/>
+      <c r="M98" s="62" t="n"/>
+      <c r="N98" s="62" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
@@ -5631,46 +5277,16 @@
           <t>Interest + Sched Prin</t>
         </is>
       </c>
-      <c r="E99" s="18">
-        <f>E97+E98</f>
-        <v/>
-      </c>
-      <c r="F99" s="18">
-        <f>F97+F98</f>
-        <v/>
-      </c>
-      <c r="G99" s="18">
-        <f>G97+G98</f>
-        <v/>
-      </c>
-      <c r="H99" s="18">
-        <f>H97+H98</f>
-        <v/>
-      </c>
-      <c r="I99" s="18">
-        <f>I97+I98</f>
-        <v/>
-      </c>
-      <c r="J99" s="18">
-        <f>J97+J98</f>
-        <v/>
-      </c>
-      <c r="K99" s="18">
-        <f>K97+K98</f>
-        <v/>
-      </c>
-      <c r="L99" s="18">
-        <f>L97+L98</f>
-        <v/>
-      </c>
-      <c r="M99" s="18">
-        <f>M97+M98</f>
-        <v/>
-      </c>
-      <c r="N99" s="18">
-        <f>N97+N98</f>
-        <v/>
-      </c>
+      <c r="E99" s="62" t="n"/>
+      <c r="F99" s="62" t="n"/>
+      <c r="G99" s="62" t="n"/>
+      <c r="H99" s="62" t="n"/>
+      <c r="I99" s="62" t="n"/>
+      <c r="J99" s="62" t="n"/>
+      <c r="K99" s="62" t="n"/>
+      <c r="L99" s="62" t="n"/>
+      <c r="M99" s="62" t="n"/>
+      <c r="N99" s="62" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
@@ -5745,46 +5361,16 @@
           <t>MIN(Excess×Sweep%, Beg-Sched)</t>
         </is>
       </c>
-      <c r="E101" s="21">
-        <f>MIN(E100*$D$54,MAX(0,E96-E98))</f>
-        <v/>
-      </c>
-      <c r="F101" s="21">
-        <f>MIN(F100*$D$54,MAX(0,F96-F98))</f>
-        <v/>
-      </c>
-      <c r="G101" s="21">
-        <f>MIN(G100*$D$54,MAX(0,G96-G98))</f>
-        <v/>
-      </c>
-      <c r="H101" s="21">
-        <f>MIN(H100*$D$54,MAX(0,H96-H98))</f>
-        <v/>
-      </c>
-      <c r="I101" s="21">
-        <f>MIN(I100*$D$54,MAX(0,I96-I98))</f>
-        <v/>
-      </c>
-      <c r="J101" s="21">
-        <f>MIN(J100*$D$54,MAX(0,J96-J98))</f>
-        <v/>
-      </c>
-      <c r="K101" s="21">
-        <f>MIN(K100*$D$54,MAX(0,K96-K98))</f>
-        <v/>
-      </c>
-      <c r="L101" s="21">
-        <f>MIN(L100*$D$54,MAX(0,L96-L98))</f>
-        <v/>
-      </c>
-      <c r="M101" s="21">
-        <f>MIN(M100*$D$54,MAX(0,M96-M98))</f>
-        <v/>
-      </c>
-      <c r="N101" s="21">
-        <f>MIN(N100*$D$54,MAX(0,N96-N98))</f>
-        <v/>
-      </c>
+      <c r="E101" s="62" t="n"/>
+      <c r="F101" s="62" t="n"/>
+      <c r="G101" s="62" t="n"/>
+      <c r="H101" s="62" t="n"/>
+      <c r="I101" s="62" t="n"/>
+      <c r="J101" s="62" t="n"/>
+      <c r="K101" s="62" t="n"/>
+      <c r="L101" s="62" t="n"/>
+      <c r="M101" s="62" t="n"/>
+      <c r="N101" s="62" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
@@ -5802,46 +5388,16 @@
           <t>Scheduled + Sweep</t>
         </is>
       </c>
-      <c r="E102" s="18">
-        <f>E98+E101</f>
-        <v/>
-      </c>
-      <c r="F102" s="18">
-        <f>F98+F101</f>
-        <v/>
-      </c>
-      <c r="G102" s="18">
-        <f>G98+G101</f>
-        <v/>
-      </c>
-      <c r="H102" s="18">
-        <f>H98+H101</f>
-        <v/>
-      </c>
-      <c r="I102" s="18">
-        <f>I98+I101</f>
-        <v/>
-      </c>
-      <c r="J102" s="18">
-        <f>J98+J101</f>
-        <v/>
-      </c>
-      <c r="K102" s="18">
-        <f>K98+K101</f>
-        <v/>
-      </c>
-      <c r="L102" s="18">
-        <f>L98+L101</f>
-        <v/>
-      </c>
-      <c r="M102" s="18">
-        <f>M98+M101</f>
-        <v/>
-      </c>
-      <c r="N102" s="18">
-        <f>N98+N101</f>
-        <v/>
-      </c>
+      <c r="E102" s="62" t="n"/>
+      <c r="F102" s="62" t="n"/>
+      <c r="G102" s="62" t="n"/>
+      <c r="H102" s="62" t="n"/>
+      <c r="I102" s="62" t="n"/>
+      <c r="J102" s="62" t="n"/>
+      <c r="K102" s="62" t="n"/>
+      <c r="L102" s="62" t="n"/>
+      <c r="M102" s="62" t="n"/>
+      <c r="N102" s="62" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
@@ -5863,46 +5419,16 @@
         <f>$D$66</f>
         <v/>
       </c>
-      <c r="E103" s="18">
-        <f>MAX(0,E96-E102)</f>
-        <v/>
-      </c>
-      <c r="F103" s="18">
-        <f>MAX(0,F96-F102)</f>
-        <v/>
-      </c>
-      <c r="G103" s="18">
-        <f>MAX(0,G96-G102)</f>
-        <v/>
-      </c>
-      <c r="H103" s="18">
-        <f>MAX(0,H96-H102)</f>
-        <v/>
-      </c>
-      <c r="I103" s="18">
-        <f>MAX(0,I96-I102)</f>
-        <v/>
-      </c>
-      <c r="J103" s="18">
-        <f>MAX(0,J96-J102)</f>
-        <v/>
-      </c>
-      <c r="K103" s="18">
-        <f>MAX(0,K96-K102)</f>
-        <v/>
-      </c>
-      <c r="L103" s="18">
-        <f>MAX(0,L96-L102)</f>
-        <v/>
-      </c>
-      <c r="M103" s="18">
-        <f>MAX(0,M96-M102)</f>
-        <v/>
-      </c>
-      <c r="N103" s="18">
-        <f>MAX(0,N96-N102)</f>
-        <v/>
-      </c>
+      <c r="E103" s="62" t="n"/>
+      <c r="F103" s="62" t="n"/>
+      <c r="G103" s="62" t="n"/>
+      <c r="H103" s="62" t="n"/>
+      <c r="I103" s="62" t="n"/>
+      <c r="J103" s="62" t="n"/>
+      <c r="K103" s="62" t="n"/>
+      <c r="L103" s="62" t="n"/>
+      <c r="M103" s="62" t="n"/>
+      <c r="N103" s="62" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
@@ -5920,46 +5446,16 @@
           <t>CFADS / Debt Service</t>
         </is>
       </c>
-      <c r="E104" s="30">
-        <f>IF(E99&gt;0,E92/E99,0)</f>
-        <v/>
-      </c>
-      <c r="F104" s="30">
-        <f>IF(F99&gt;0,F92/F99,0)</f>
-        <v/>
-      </c>
-      <c r="G104" s="30">
-        <f>IF(G99&gt;0,G92/G99,0)</f>
-        <v/>
-      </c>
-      <c r="H104" s="30">
-        <f>IF(H99&gt;0,H92/H99,0)</f>
-        <v/>
-      </c>
-      <c r="I104" s="30">
-        <f>IF(I99&gt;0,I92/I99,0)</f>
-        <v/>
-      </c>
-      <c r="J104" s="30">
-        <f>IF(J99&gt;0,J92/J99,0)</f>
-        <v/>
-      </c>
-      <c r="K104" s="30">
-        <f>IF(K99&gt;0,K92/K99,0)</f>
-        <v/>
-      </c>
-      <c r="L104" s="30">
-        <f>IF(L99&gt;0,L92/L99,0)</f>
-        <v/>
-      </c>
-      <c r="M104" s="30">
-        <f>IF(M99&gt;0,M92/M99,0)</f>
-        <v/>
-      </c>
-      <c r="N104" s="30">
-        <f>IF(N99&gt;0,N92/N99,0)</f>
-        <v/>
-      </c>
+      <c r="E104" s="64" t="n"/>
+      <c r="F104" s="64" t="n"/>
+      <c r="G104" s="64" t="n"/>
+      <c r="H104" s="64" t="n"/>
+      <c r="I104" s="64" t="n"/>
+      <c r="J104" s="64" t="n"/>
+      <c r="K104" s="64" t="n"/>
+      <c r="L104" s="64" t="n"/>
+      <c r="M104" s="64" t="n"/>
+      <c r="N104" s="64" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
@@ -6280,46 +5776,16 @@
         <f>D97+D98</f>
         <v/>
       </c>
-      <c r="E111" s="18">
-        <f>E109+E110</f>
-        <v/>
-      </c>
-      <c r="F111" s="18">
-        <f>F109+F110</f>
-        <v/>
-      </c>
-      <c r="G111" s="18">
-        <f>G109+G110</f>
-        <v/>
-      </c>
-      <c r="H111" s="18">
-        <f>H109+H110</f>
-        <v/>
-      </c>
-      <c r="I111" s="18">
-        <f>I109+I110</f>
-        <v/>
-      </c>
-      <c r="J111" s="18">
-        <f>J109+J110</f>
-        <v/>
-      </c>
-      <c r="K111" s="18">
-        <f>K109+K110</f>
-        <v/>
-      </c>
-      <c r="L111" s="18">
-        <f>L109+L110</f>
-        <v/>
-      </c>
-      <c r="M111" s="18">
-        <f>M109+M110</f>
-        <v/>
-      </c>
-      <c r="N111" s="18">
-        <f>N109+N110</f>
-        <v/>
-      </c>
+      <c r="E111" s="62" t="n"/>
+      <c r="F111" s="62" t="n"/>
+      <c r="G111" s="62" t="n"/>
+      <c r="H111" s="62" t="n"/>
+      <c r="I111" s="62" t="n"/>
+      <c r="J111" s="62" t="n"/>
+      <c r="K111" s="62" t="n"/>
+      <c r="L111" s="62" t="n"/>
+      <c r="M111" s="62" t="n"/>
+      <c r="N111" s="62" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="5" t="n"/>
@@ -6485,46 +5951,16 @@
           <t>If PASS, MAX(0, Cash Avail)</t>
         </is>
       </c>
-      <c r="E117" s="7">
-        <f>IF(E116="PASS",MAX(0,E115),0)</f>
-        <v/>
-      </c>
-      <c r="F117" s="7">
-        <f>IF(F116="PASS",MAX(0,F115),0)</f>
-        <v/>
-      </c>
-      <c r="G117" s="7">
-        <f>IF(G116="PASS",MAX(0,G115),0)</f>
-        <v/>
-      </c>
-      <c r="H117" s="7">
-        <f>IF(H116="PASS",MAX(0,H115),0)</f>
-        <v/>
-      </c>
-      <c r="I117" s="7">
-        <f>IF(I116="PASS",MAX(0,I115),0)</f>
-        <v/>
-      </c>
-      <c r="J117" s="7">
-        <f>IF(J116="PASS",MAX(0,J115),0)</f>
-        <v/>
-      </c>
-      <c r="K117" s="7">
-        <f>IF(K116="PASS",MAX(0,K115),0)</f>
-        <v/>
-      </c>
-      <c r="L117" s="7">
-        <f>IF(L116="PASS",MAX(0,L115),0)</f>
-        <v/>
-      </c>
-      <c r="M117" s="7">
-        <f>IF(M116="PASS",MAX(0,M115),0)</f>
-        <v/>
-      </c>
-      <c r="N117" s="7">
-        <f>IF(N116="PASS",MAX(0,N115),0)</f>
-        <v/>
-      </c>
+      <c r="E117" s="63" t="n"/>
+      <c r="F117" s="63" t="n"/>
+      <c r="G117" s="63" t="n"/>
+      <c r="H117" s="63" t="n"/>
+      <c r="I117" s="63" t="n"/>
+      <c r="J117" s="63" t="n"/>
+      <c r="K117" s="63" t="n"/>
+      <c r="L117" s="63" t="n"/>
+      <c r="M117" s="63" t="n"/>
+      <c r="N117" s="63" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="5" t="n"/>
@@ -6541,7 +5977,6 @@
       <c r="M118" s="7" t="n"/>
       <c r="N118" s="7" t="n"/>
     </row>
-    <row r="119"/>
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
@@ -6925,43 +6360,16 @@
         <f>-D129</f>
         <v/>
       </c>
-      <c r="E141" s="18">
-        <f>E117</f>
-        <v/>
-      </c>
-      <c r="F141" s="18">
-        <f>F117</f>
-        <v/>
-      </c>
-      <c r="G141" s="18">
-        <f>G117</f>
-        <v/>
-      </c>
-      <c r="H141" s="18">
-        <f>H117</f>
-        <v/>
-      </c>
-      <c r="I141" s="18">
-        <f>I117</f>
-        <v/>
-      </c>
-      <c r="J141" s="18">
-        <f>J117</f>
-        <v/>
-      </c>
-      <c r="K141" s="18">
-        <f>K117+D143</f>
-        <v/>
-      </c>
-      <c r="L141" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M141" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N141" s="18" t="n">
-        <v>0</v>
-      </c>
+      <c r="E141" s="62" t="n"/>
+      <c r="F141" s="62" t="n"/>
+      <c r="G141" s="62" t="n"/>
+      <c r="H141" s="62" t="n"/>
+      <c r="I141" s="62" t="n"/>
+      <c r="J141" s="62" t="n"/>
+      <c r="K141" s="62" t="n"/>
+      <c r="L141" s="62" t="n"/>
+      <c r="M141" s="62" t="n"/>
+      <c r="N141" s="62" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="5" t="inlineStr">
@@ -6979,10 +6387,7 @@
           <t>IRR of Equity CFs</t>
         </is>
       </c>
-      <c r="D142" s="31">
-        <f>IRR(D141:N141)</f>
-        <v/>
-      </c>
+      <c r="D142" s="65" t="n"/>
       <c r="E142" s="18" t="n"/>
       <c r="F142" s="18" t="n"/>
       <c r="G142" s="18" t="n"/>
@@ -7111,10 +6516,7 @@
           <t>IRR of Equity CFs</t>
         </is>
       </c>
-      <c r="D147" s="30">
-        <f>(SUM(E141:K141))/-D141</f>
-        <v/>
-      </c>
+      <c r="D147" s="64" t="n"/>
       <c r="E147" s="18" t="n"/>
       <c r="F147" s="18" t="n"/>
       <c r="G147" s="18" t="n"/>
@@ -7135,17 +6537,6 @@
         <v/>
       </c>
     </row>
-    <row r="149"/>
-    <row r="150"/>
-    <row r="151"/>
-    <row r="152"/>
-    <row r="153"/>
-    <row r="154"/>
-    <row r="155"/>
-    <row r="156"/>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
   </sheetData>
   <dataValidations count="3">
     <dataValidation sqref="D7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">

--- a/deliverables/deliverables-20260120-0030/Drill_1_CCGT.xlsx
+++ b/deliverables/deliverables-20260120-0030/Drill_1_CCGT.xlsx
@@ -3592,10 +3592,7 @@
       </c>
       <c r="B22" s="6" t="n"/>
       <c r="C22" s="6" t="n"/>
-      <c r="D22" s="10">
-        <f>D132</f>
-        <v/>
-      </c>
+      <c r="D22" s="10" t="n"/>
       <c r="E22" s="4" t="n"/>
       <c r="F22" s="4" t="n"/>
       <c r="G22" s="4" t="n"/>
@@ -5803,7 +5800,6 @@
       <c r="M112" s="18" t="n"/>
       <c r="N112" s="18" t="n"/>
     </row>
-    <row r="113"/>
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>

--- a/deliverables/deliverables-20260120-0030/Drill_1_CCGT.xlsx
+++ b/deliverables/deliverables-20260120-0030/Drill_1_CCGT.xlsx
@@ -3373,10 +3373,25 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="49" t="n"/>
-      <c r="B6" s="49" t="n"/>
-      <c r="C6" s="49" t="n"/>
-      <c r="D6" s="49" t="n"/>
+      <c r="A6" s="49" t="inlineStr">
+        <is>
+          <t>Min DSCR</t>
+        </is>
+      </c>
+      <c r="B6" s="49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C6" s="49" t="inlineStr">
+        <is>
+          <t>Minimum debt service coverage ratio</t>
+        </is>
+      </c>
+      <c r="D6" s="60">
+        <f>IF(COUNTIF(E104:K104,"&gt;0")&gt;0,MINIFS(E104:K104,E104:K104,"&gt;0"),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="50" t="inlineStr">
@@ -3630,7 +3645,7 @@
         </is>
       </c>
       <c r="D24" s="10">
-        <f>IF(MIN(E104:K104)&gt;=1.25,"PASS","FAIL")</f>
+        <f>IF(D6&gt;=1.25,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
